--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W10</t>
+          <t>W14</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>4128</v>
+        <v>5432</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>3136</v>
+        <v>4131</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>824</v>
+        <v>1176</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>233</v>
+        <v>326</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>341</v>
+        <v>435</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>72</v>
+        <v>142</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>176</v>
+        <v>252</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>73</v>
+        <v>98</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>352</v>
+        <v>494</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>59</v>
+        <v>70</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>219</v>
+        <v>288</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>291</v>
+        <v>368</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>178</v>
+        <v>226</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>103</v>
+        <v>125</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>249</v>
+        <v>326</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>155</v>
+        <v>194</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>209</v>
+        <v>259</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>102</v>
+        <v>137</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>07171</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CIVITAVECCHIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -983,35 +983,35 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>138</v>
+        <v>193</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>121</v>
+        <v>214</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4</v>
+        <v>31</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>8</v>
+        <v>39</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>100</v>
+        <v>153</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>154</v>
+        <v>388</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>8</v>
+        <v>345</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>136</v>
+        <v>182</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>128</v>
+        <v>178</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>81</v>
+        <v>110</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>109</v>
+        <v>151</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1072,12 +1072,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>07171</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>CIVITAVECCHIA</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1087,35 +1087,35 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>110</v>
+        <v>165</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>48</v>
+        <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>70</v>
+        <v>43</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>69</v>
+        <v>211</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,39 +1141,39 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>130</v>
+        <v>159</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>24</v>
+        <v>68</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>104</v>
+        <v>137</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>277</v>
+        <v>89</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>245</v>
+        <v>12</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1199,31 +1199,31 @@
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>116</v>
+        <v>156</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>112</v>
+        <v>160</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>28</v>
+        <v>67</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>85</v>
+        <v>118</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>73</v>
+        <v>100</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>111</v>
+        <v>150</v>
       </c>
       <c r="F19" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <v>92</v>
+      </c>
+      <c r="H19" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I19" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="J19" s="12" t="n">
         <v>78</v>
       </c>
-      <c r="G19" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="H19" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I19" s="12" t="n">
-        <v>102</v>
-      </c>
-      <c r="J19" s="12" t="n">
-        <v>62</v>
-      </c>
       <c r="K19" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>157</v>
+        <v>203</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1307,31 +1307,31 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>109</v>
+        <v>133</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>75</v>
+        <v>104</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>81</v>
+        <v>103</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>79</v>
+        <v>104</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1361,31 +1361,31 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>106</v>
+        <v>132</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>74</v>
+        <v>105</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>103</v>
+        <v>123</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>121</v>
+        <v>164</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1415,47 +1415,47 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>104</v>
+        <v>132</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>79</v>
+        <v>158</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>14</v>
+        <v>82</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>76</v>
+        <v>152</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>41</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>97</v>
+        <v>128</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>10</v>
+        <v>45</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>154</v>
+        <v>105</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0</v>
+        <v>41</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,51 +1519,51 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>92</v>
+        <v>128</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>97</v>
+        <v>178</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>93</v>
+        <v>198</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>29</v>
+        <v>3</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>23</v>
+        <v>47</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>110</v>
+        <v>154</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,31 +1631,31 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>89</v>
+        <v>114</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>123</v>
+        <v>147</v>
       </c>
       <c r="G26" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H26" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I26" s="12" t="n">
+        <v>107</v>
+      </c>
+      <c r="J26" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K26" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L26" s="12" t="n">
+        <v>189</v>
+      </c>
+      <c r="M26" s="12" t="n">
         <v>9</v>
-      </c>
-      <c r="H26" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I26" s="12" t="n">
-        <v>85</v>
-      </c>
-      <c r="J26" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K26" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L26" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="M26" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,35 +1681,35 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="F27" s="12" t="n">
+        <v>113</v>
+      </c>
+      <c r="G27" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="K27" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G27" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H27" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="L27" s="12" t="n">
-        <v>91</v>
+        <v>122</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>43</v>
+        <v>4</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>80</v>
+        <v>125</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>86</v>
+        <v>118</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>98</v>
+        <v>37</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>2</v>
+        <v>43</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,51 +1843,51 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>73</v>
+        <v>99</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>39</v>
+        <v>116</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>29</v>
+        <v>107</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>19</v>
+        <v>74</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>20</v>
+        <v>109</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>40</v>
+        <v>81</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>11</v>
+        <v>39</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -2009,28 +2009,28 @@
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>64</v>
+        <v>93</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>78</v>
+        <v>108</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>52</v>
+        <v>75</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>0</v>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,51 +2059,51 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>64</v>
+        <v>89</v>
       </c>
       <c r="F34" s="12" t="n">
+        <v>99</v>
+      </c>
+      <c r="G34" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H34" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I34" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="G34" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="H34" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I34" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="J34" s="12" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,51 +2113,51 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>63</v>
+        <v>150</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>58</v>
+        <v>24</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>7</v>
+        <v>42</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>23</v>
+        <v>71</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15</v>
+        <v>67</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>58</v>
+        <v>80</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>89</v>
+        <v>15</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>12</v>
+        <v>41</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>55</v>
+        <v>76</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>73</v>
+        <v>102</v>
       </c>
       <c r="G38" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="H38" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="H38" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="I38" s="12" t="n">
-        <v>35</v>
+        <v>64</v>
       </c>
       <c r="J38" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="K38" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K38" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="L38" s="12" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,39 +2329,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>59</v>
+        <v>97</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>3</v>
+        <v>31</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="J39" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K39" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L39" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>64</v>
+        <v>86</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>44</v>
+        <v>61</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>148</v>
+        <v>193</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,51 +2437,51 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>50</v>
+        <v>67</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="G42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H42" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I42" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="J42" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K42" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>82</v>
+      </c>
+      <c r="M42" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H42" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I42" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K42" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>83</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>29</v>
+        <v>102</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>57</v>
+        <v>99</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>32</v>
+        <v>119</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="F45" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="I45" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="F45" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="G45" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="J45" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="M45" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K45" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L45" s="12" t="n">
-        <v>79</v>
-      </c>
-      <c r="M45" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="F46" s="12" t="n">
+        <v>94</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="I46" s="12" t="n">
         <v>42</v>
-      </c>
-      <c r="F46" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G46" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>34</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>13</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>82</v>
+        <v>119</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>41</v>
+        <v>53</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>20</v>
+        <v>3</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>84</v>
+        <v>52</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,35 +2869,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>14</v>
+        <v>35</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>8</v>
+        <v>28</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2927,47 +2927,47 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>47</v>
+        <v>62</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="F51" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>28</v>
-      </c>
       <c r="G51" s="12" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>25</v>
+        <v>59</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,39 +3031,39 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H52" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I52" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K52" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I52" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="L52" s="12" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3089,35 +3089,35 @@
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3143,28 +3143,28 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H54" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>3</v>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,32 +3193,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J55" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K55" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K55" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="L55" s="12" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3251,47 +3251,47 @@
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H56" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I56" s="12" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>32</v>
+        <v>98</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>85</v>
+        <v>35</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>19</v>
+        <v>34</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>74</v>
+        <v>36</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,32 +3355,32 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>60</v>
+        <v>73</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
@@ -3394,12 +3394,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F59" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="G59" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I59" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F59" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="G59" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H59" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I59" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="J59" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>31</v>
+        <v>77</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K60" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L60" s="12" t="n">
+        <v>66</v>
+      </c>
+      <c r="M60" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L60" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M60" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,51 +3517,51 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K61" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J63" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K63" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K63" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L63" s="12" t="n">
-        <v>104</v>
+        <v>39</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>22</v>
+        <v>134</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,46 +3733,46 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>27</v>
+        <v>62</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>27</v>
+        <v>37</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3787,32 +3787,32 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3841,23 +3841,23 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J67" s="12" t="n">
         <v>8</v>
@@ -3866,26 +3866,26 @@
         <v>3</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3899,47 +3899,47 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,46 +3949,46 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -4007,31 +4007,31 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J70" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K70" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K70" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="L70" s="12" t="n">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>33</v>
+        <v>52</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,51 +4111,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="I72" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="J72" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K73" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="L73" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>33</v>
+        <v>86</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,51 +4273,51 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L75" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="M75" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I75" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="M75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,32 +4327,32 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H76" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I76" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K76" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>48</v>
+        <v>19</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>0</v>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F77" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G77" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H77" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F77" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="G77" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="H77" s="12" t="n">
-        <v>20</v>
-      </c>
       <c r="I77" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
@@ -4420,12 +4420,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,35 +4435,35 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4474,12 +4474,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,35 +4489,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,51 +4543,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>13</v>
+        <v>71</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,32 +4651,32 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>55</v>
+        <v>28</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
@@ -4690,12 +4690,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,51 +4705,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>07164</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,11 +4759,11 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F84" s="12" t="n">
         <v>0</v>
@@ -4775,23 +4775,23 @@
         <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4838,7 +4838,7 @@
         <v>2</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>0</v>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>06947</t>
+          <t>53821</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,51 +4867,51 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G86" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F86" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="G86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
         <v>2</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>06947</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,20 +4921,20 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
         <v>2</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" s="12" t="n">
         <v>2</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
@@ -4982,13 +4982,13 @@
         <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>34</v>
+        <v>48</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -535,7 +535,7 @@
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
     <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
@@ -845,7 +845,7 @@
         <v>494</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>0.1417004048582996</v>
+        <v>70</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -899,7 +899,7 @@
         <v>326</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>0.3128834355828221</v>
+        <v>102</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>137</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>0.489051094890511</v>
+        <v>67</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>388</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>0.8891752577319587</v>
+        <v>345</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>151</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>0.2052980132450331</v>
+        <v>31</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1115,7 +1115,7 @@
         <v>211</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>0.08056872037914692</v>
+        <v>17</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1169,7 +1169,7 @@
         <v>89</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>0.1348314606741573</v>
+        <v>12</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>100</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>0.13</v>
+        <v>13</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1277,7 +1277,7 @@
         <v>203</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>0.7684729064039408</v>
+        <v>156</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1331,7 +1331,7 @@
         <v>161</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>0.6459627329192547</v>
+        <v>104</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>164</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>0.8780487804878049</v>
+        <v>144</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1439,7 +1439,7 @@
         <v>152</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>0.0131578947368421</v>
+        <v>2</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1493,7 +1493,7 @@
         <v>105</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>0.3904761904761905</v>
+        <v>41</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
@@ -1547,7 +1547,7 @@
         <v>198</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>0.005050505050505051</v>
+        <v>1</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>154</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>0.02597402597402598</v>
+        <v>4</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1655,7 +1655,7 @@
         <v>189</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>0.04761904761904762</v>
+        <v>9</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
         <v>122</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>0.03278688524590164</v>
+        <v>4</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1763,7 +1763,7 @@
         <v>118</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>0.02542372881355932</v>
+        <v>3</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>117</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0.3675213675213675</v>
+        <v>43</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1871,7 +1871,7 @@
         <v>107</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0.02803738317757009</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1925,7 +1925,7 @@
         <v>47</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>0.2127659574468085</v>
+        <v>10</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -2087,7 +2087,7 @@
         <v>96</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>0.01041666666666667</v>
+        <v>1</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2141,7 +2141,7 @@
         <v>71</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>0.2816901408450704</v>
+        <v>20</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2195,7 +2195,7 @@
         <v>29</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>0.2413793103448276</v>
+        <v>7</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
         <v>111</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>3</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2411,7 +2411,7 @@
         <v>193</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>0.02072538860103627</v>
+        <v>4</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2465,7 +2465,7 @@
         <v>37</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>1</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2519,7 +2519,7 @@
         <v>82</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>0.01219512195121951</v>
+        <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>102</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>0.08823529411764706</v>
+        <v>9</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
@@ -2627,7 +2627,7 @@
         <v>119</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>0.04201680672268908</v>
+        <v>5</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2681,7 +2681,7 @@
         <v>117</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>0.03418803418803419</v>
+        <v>4</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2897,7 +2897,7 @@
         <v>35</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0.6285714285714286</v>
+        <v>22</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -3005,7 +3005,7 @@
         <v>59</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>0.05084745762711865</v>
+        <v>3</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3167,7 +3167,7 @@
         <v>30</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0.1</v>
+        <v>3</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3275,7 +3275,7 @@
         <v>98</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0.01020408163265306</v>
+        <v>1</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
@@ -3491,7 +3491,7 @@
         <v>66</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0.01515151515151515</v>
+        <v>1</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
@@ -3599,7 +3599,7 @@
         <v>55</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>0.01818181818181818</v>
+        <v>1</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3653,7 +3653,7 @@
         <v>39</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>0.1538461538461539</v>
+        <v>6</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3707,7 +3707,7 @@
         <v>134</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>0.01492537313432836</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3761,7 +3761,7 @@
         <v>37</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>0.02702702702702703</v>
+        <v>1</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>80</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0.0125</v>
+        <v>1</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3977,7 +3977,7 @@
         <v>68</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>0.02941176470588235</v>
+        <v>2</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -4193,7 +4193,7 @@
         <v>46</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0.4782608695652174</v>
+        <v>22</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4247,7 +4247,7 @@
         <v>86</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>0.01162790697674419</v>
+        <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
@@ -4301,7 +4301,7 @@
         <v>42</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0.09523809523809523</v>
+        <v>4</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4517,7 +4517,7 @@
         <v>37</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>0.5945945945945946</v>
+        <v>22</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4787,7 +4787,7 @@
         <v>19</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>0.1052631578947368</v>
+        <v>2</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W14</t>
+          <t>W15</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>78</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5432</v>
+        <v>5717</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4131</v>
+        <v>4327</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1176</v>
+        <v>1258</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>435</v>
+        <v>475</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>142</v>
+        <v>152</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>96</v>
+        <v>106</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>252</v>
+        <v>266</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>494</v>
+        <v>519</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>288</v>
+        <v>301</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="J12" s="12" t="n">
         <v>125</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>102</v>
@@ -910,12 +910,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>17131</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>ORTONA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -925,35 +925,35 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>259</v>
+        <v>235</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>137</v>
+        <v>408</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>67</v>
+        <v>360</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -964,12 +964,12 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>17131</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORTONA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -979,35 +979,35 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>388</v>
+        <v>152</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>345</v>
+        <v>74</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>182</v>
+        <v>193</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>55</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,35 +1141,35 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>151</v>
+        <v>166</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>31</v>
+        <v>41</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>137</v>
+        <v>123</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>83</v>
+        <v>52</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,35 +1195,35 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>118</v>
+        <v>141</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>52</v>
+        <v>84</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>39</v>
+        <v>16</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
@@ -1253,47 +1253,47 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,39 +1303,39 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>104</v>
+        <v>194</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>103</v>
+        <v>94</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>161</v>
+        <v>212</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>104</v>
+        <v>2</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1361,10 +1361,10 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>2</v>
@@ -1373,19 +1373,19 @@
         <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>123</v>
+        <v>128</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
@@ -1396,12 +1396,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,39 +1411,39 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>132</v>
+        <v>137</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>158</v>
+        <v>108</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>82</v>
+        <v>28</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>152</v>
+        <v>172</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>2</v>
+        <v>109</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1469,47 +1469,47 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>41</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>178</v>
+        <v>168</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>198</v>
+        <v>161</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G25" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>4</v>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>147</v>
+        <v>118</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>107</v>
+        <v>90</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>189</v>
+        <v>127</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>113</v>
+        <v>156</v>
       </c>
       <c r="G27" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I27" s="12" t="n">
+        <v>110</v>
+      </c>
+      <c r="J27" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K27" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L27" s="12" t="n">
+        <v>195</v>
+      </c>
+      <c r="M27" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H27" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="I27" s="12" t="n">
-        <v>84</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K27" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="L27" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="M27" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J28" s="12" t="n">
         <v>17</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>3</v>
@@ -1793,10 +1793,10 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>3</v>
@@ -1805,19 +1805,19 @@
         <v>21</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>116</v>
+        <v>65</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="H30" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I30" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="J30" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K30" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="I30" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="J30" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K30" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="L30" s="12" t="n">
-        <v>107</v>
+        <v>50</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>82</v>
+        <v>122</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>74</v>
+        <v>35</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>109</v>
+        <v>35</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>47</v>
+        <v>113</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,35 +1951,35 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>13</v>
+        <v>77</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
@@ -1990,12 +1990,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,35 +2005,35 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F33" s="12" t="n">
         <v>108</v>
       </c>
       <c r="G33" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="H33" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I33" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="J33" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H33" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="I33" s="12" t="n">
-        <v>75</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="K33" s="12" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
@@ -2044,12 +2044,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>99</v>
+        <v>162</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>27</v>
+        <v>50</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>24</v>
+        <v>51</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>42</v>
+        <v>18</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>20</v>
+        <v>2</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>67</v>
+        <v>15</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>73</v>
+        <v>43</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>37</v>
+        <v>9</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>7</v>
+        <v>45</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,51 +2221,51 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>15</v>
+        <v>70</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>9</v>
+        <v>38</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>41</v>
+        <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>63</v>
+        <v>29</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>111</v>
+        <v>92</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2387,19 +2387,19 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="G40" s="12" t="n">
         <v>8</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="J40" s="12" t="n">
         <v>22</v>
@@ -2408,7 +2408,7 @@
         <v>13</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>193</v>
+        <v>205</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>4</v>
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G41" s="12" t="n">
         <v>5</v>
@@ -2453,16 +2453,16 @@
         <v>6</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="M41" s="12" t="n">
         <v>1</v>
@@ -2476,12 +2476,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -2491,35 +2491,35 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>3</v>
+        <v>29</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>18</v>
       </c>
       <c r="K42" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="L42" s="12" t="n">
+        <v>132</v>
+      </c>
+      <c r="M42" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="L42" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="M42" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2530,12 +2530,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,51 +2545,51 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>11</v>
+        <v>27</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>119</v>
+        <v>110</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,7 +2638,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2657,31 +2657,31 @@
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>69</v>
+        <v>102</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
@@ -2711,28 +2711,28 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>15</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2765,7 +2765,7 @@
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="F47" s="12" t="n">
         <v>30</v>
@@ -2777,23 +2777,23 @@
         <v>3</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="J47" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2819,28 +2819,28 @@
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -2876,13 +2876,13 @@
         <v>47</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="I49" s="12" t="n">
         <v>43</v>
@@ -2894,14 +2894,14 @@
         <v>2</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2927,16 +2927,16 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I50" s="12" t="n">
         <v>30</v>
@@ -2945,10 +2945,10 @@
         <v>12</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
@@ -2981,28 +2981,28 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F51" s="12" t="n">
         <v>35</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>27</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="M51" s="12" t="n">
         <v>3</v>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F52" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="G52" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H52" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="G52" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H52" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="I52" s="12" t="n">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>44</v>
+        <v>35</v>
       </c>
       <c r="G53" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H53" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H53" s="12" t="n">
-        <v>25</v>
-      </c>
       <c r="I53" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>70</v>
+        <v>33</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>35</v>
+        <v>113</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>30</v>
+        <v>105</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,32 +3193,32 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="G55" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H55" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H55" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="I55" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="M55" s="12" t="n">
         <v>0</v>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,39 +3247,39 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>107</v>
+        <v>56</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>98</v>
+        <v>64</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3308,13 +3308,13 @@
         <v>38</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>20</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="I57" s="12" t="n">
         <v>34</v>
@@ -3333,7 +3333,7 @@
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G58" s="12" t="n">
         <v>2</v>
@@ -3371,16 +3371,16 @@
         <v>19</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K58" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
@@ -3413,10 +3413,10 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G59" s="12" t="n">
         <v>0</v>
@@ -3425,16 +3425,16 @@
         <v>5</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>5</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
         <v>36</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>77</v>
+        <v>44</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>66</v>
+        <v>43</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3521,47 +3521,47 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="G61" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H61" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H61" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I61" s="12" t="n">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="K61" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L61" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="M61" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L61" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3629,42 +3629,42 @@
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3679,51 +3679,51 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="G64" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I64" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J64" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K64" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="L64" s="12" t="n">
+        <v>86</v>
+      </c>
+      <c r="M64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="J64" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="K64" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L64" s="12" t="n">
-        <v>134</v>
-      </c>
-      <c r="M64" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="G65" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H65" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K65" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L65" s="12" t="n">
+        <v>143</v>
+      </c>
+      <c r="M65" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H65" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="I65" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M65" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,46 +3787,46 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="F66" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="G66" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H66" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I66" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="F66" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="G66" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="H66" s="12" t="n">
+      <c r="J66" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="M66" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I66" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L66" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="G67" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H67" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H67" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="I67" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3899,47 +3899,47 @@
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I69" s="12" t="n">
         <v>25</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,51 +4003,51 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="M70" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>52</v>
+        <v>39</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,51 +4111,51 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K72" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L72" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L72" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="M72" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,39 +4165,39 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4223,28 +4223,28 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>1</v>
@@ -4277,28 +4277,28 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>4</v>
@@ -4331,19 +4331,19 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J76" s="12" t="n">
         <v>1</v>
@@ -4394,7 +4394,7 @@
         <v>2</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>9</v>
@@ -4406,7 +4406,7 @@
         <v>7</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>0</v>
@@ -4445,7 +4445,7 @@
         <v>19</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>12</v>
@@ -4460,10 +4460,10 @@
         <v>5</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4514,7 +4514,7 @@
         <v>0</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>22</v>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,51 +4543,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J81" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K81" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L81" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H81" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="I81" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J81" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K81" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L81" s="12" t="n">
-        <v>71</v>
-      </c>
       <c r="M81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,51 +4651,51 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,39 +4705,39 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
         <v>11</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>16</v>
+        <v>74</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4892,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>0</v>
@@ -4928,7 +4928,7 @@
         <v>2</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>0</v>
@@ -4982,13 +4982,13 @@
         <v>0</v>
       </c>
       <c r="F88" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N88" headerRowCount="1">
-  <autoFilter ref="A10:N88"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N111" headerRowCount="1">
+  <autoFilter ref="A10:N111"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N88"/>
+  <dimension ref="A1:N111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,16 +673,16 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5717</v>
+        <v>5889</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4327</v>
+        <v>4476</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1258</v>
+        <v>1321</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,35 +2869,35 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>46</v>
+        <v>3</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>43</v>
+        <v>5</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>28</v>
+        <v>12</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>37</v>
+        <v>100</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
@@ -2908,12 +2908,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,51 +2923,51 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H50" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="F50" s="12" t="n">
-        <v>68</v>
-      </c>
-      <c r="G50" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H50" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="I50" s="12" t="n">
-        <v>30</v>
-      </c>
       <c r="J50" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -2977,35 +2977,35 @@
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="F51" s="12" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>27</v>
+        <v>43</v>
       </c>
       <c r="I51" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J51" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="K51" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L51" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="J51" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="K51" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L51" s="12" t="n">
-        <v>61</v>
-      </c>
       <c r="M51" s="12" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
@@ -3016,12 +3016,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,32 +3031,32 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>37</v>
+        <v>13</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="M52" s="12" t="n">
         <v>0</v>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,51 +3085,51 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F53" s="12" t="n">
         <v>35</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>4</v>
+        <v>27</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,35 +3139,35 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>113</v>
+        <v>54</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>1</v>
+        <v>37</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>105</v>
+        <v>75</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>56</v>
+        <v>113</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H56" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="J56" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H56" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I56" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="K56" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>64</v>
+        <v>105</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>38</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
@@ -3340,12 +3340,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I58" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J58" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K58" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K58" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L58" s="12" t="n">
-        <v>148</v>
+        <v>64</v>
       </c>
       <c r="M58" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,51 +3409,51 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>69</v>
+        <v>38</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>43</v>
+        <v>148</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,35 +3517,35 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>78</v>
+        <v>69</v>
       </c>
       <c r="G61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H61" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="I61" s="12" t="n">
-        <v>17</v>
+        <v>30</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,35 +3571,35 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,32 +3679,32 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H64" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G64" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="H64" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I64" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="J64" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>86</v>
+        <v>50</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>1</v>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H65" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I65" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="J65" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="K65" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L65" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="M65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I65" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="J65" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="K65" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="L65" s="12" t="n">
-        <v>143</v>
-      </c>
-      <c r="M65" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,46 +3787,46 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>41</v>
+        <v>86</v>
       </c>
       <c r="M66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3841,51 +3841,51 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>69</v>
+        <v>143</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,35 +3895,35 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="F68" s="12" t="n">
         <v>67</v>
       </c>
       <c r="G68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K68" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L68" s="12" t="n">
+        <v>41</v>
+      </c>
+      <c r="M68" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J68" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="L68" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
         <v>27</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>0</v>
+        <v>43</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4010,44 +4010,44 @@
         <v>27</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G71" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K71" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J71" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K71" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L71" s="12" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,35 +4111,35 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>57</v>
+        <v>34</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,46 +4165,46 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>55</v>
+        <v>39</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="M73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4223,47 +4223,47 @@
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>91</v>
+        <v>57</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,35 +4273,35 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
@@ -4312,12 +4312,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -4327,35 +4327,35 @@
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="J76" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L76" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="M76" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="L76" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="M76" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
@@ -4366,12 +4366,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -4381,51 +4381,51 @@
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>13</v>
       </c>
       <c r="I77" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J77" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="L77" s="12" t="n">
-        <v>28</v>
+        <v>47</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -4435,23 +4435,23 @@
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="H78" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I78" s="12" t="n">
         <v>12</v>
-      </c>
-      <c r="I78" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>1</v>
@@ -4460,10 +4460,10 @@
         <v>5</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
@@ -4474,12 +4474,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,51 +4489,51 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="H79" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="J79" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4547,47 +4547,47 @@
         </is>
       </c>
       <c r="E80" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F80" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="G80" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H80" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="H80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I80" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="M80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,51 +4597,51 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F81" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>18</v>
+        <v>50</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,35 +4651,35 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
@@ -4690,12 +4690,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,51 +4705,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>74</v>
+        <v>30</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>PENNE</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,51 +4759,51 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J84" s="12" t="n">
         <v>2</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>06148</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>CAGLI</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,32 +4813,32 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="F85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J85" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K85" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="K85" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="L85" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>0</v>
@@ -4852,12 +4852,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>53821</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,32 +4867,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H86" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I86" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K86" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>0</v>
@@ -4906,7 +4906,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>06947</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4921,93 +4921,1335 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="F87" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G87" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H87" s="12" t="n">
-        <v>3</v>
+        <v>36</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>1</v>
+        <v>74</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>59309</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>MORLUPO</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>DELLA ROSA FABIO</t>
+        </is>
+      </c>
+      <c r="E88" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="F88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J88" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="M88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>16572</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>ORICOLA</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>PACI CLAUDIO</t>
+        </is>
+      </c>
+      <c r="E89" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F89" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G89" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H89" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I89" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J89" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K89" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L89" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="M89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>07164</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>CASTEL GANDOLFO</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>MARIANI MARIO</t>
+        </is>
+      </c>
+      <c r="E90" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="F90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K90" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="M90" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>58341</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>MARIANI MARIO</t>
+        </is>
+      </c>
+      <c r="E91" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="F91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J91" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L91" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>06607</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SAN SALVO</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>D'ANNIBALE EMANUELE</t>
+        </is>
+      </c>
+      <c r="E92" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J92" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L92" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>55843</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>LESTI LEONARDO</t>
+        </is>
+      </c>
+      <c r="E93" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="F93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L93" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="M93" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>06148</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>CAGLI</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>DI VIRGILIO DAVID</t>
+        </is>
+      </c>
+      <c r="E94" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J94" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K94" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="L94" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>53821</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>PESARO</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>DI VIRGILIO DAVID</t>
+        </is>
+      </c>
+      <c r="E95" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="F95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="K95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="M95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>06947</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>LESTI LEONARDO</t>
+        </is>
+      </c>
+      <c r="E96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="F96" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="G96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I96" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L96" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>Da seguire</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>05861</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>COPPARO</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>BASSI VALERIA</t>
+        </is>
+      </c>
+      <c r="E97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M97" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
           <t>06128</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>PESARO</t>
         </is>
       </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F88" s="12" t="n">
+      <c r="E98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F98" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="G88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H88" s="12" t="n">
+      <c r="G98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="I98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M98" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N98" s="2" t="inlineStr">
         <is>
           <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>06520</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SULMONA</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>COLOZZA STEFANO</t>
+        </is>
+      </c>
+      <c r="E99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F99" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="G99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>06812</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>MONTECOSARO</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>STROLOGO FRANCESCO</t>
+        </is>
+      </c>
+      <c r="E100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F100" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M100" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>06883</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>PESCARA</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>CAIMMI ANDREA</t>
+        </is>
+      </c>
+      <c r="E101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F101" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="G101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M101" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>06892</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>MANOPPELLO</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>D'ANNIBALE EMANUELE</t>
+        </is>
+      </c>
+      <c r="E102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="G102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>09297</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>LUCERA</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>CASCIANI GABRIELE</t>
+        </is>
+      </c>
+      <c r="E103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M103" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>19740</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>BAGHERIA</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>CASSATA FULVIA</t>
+        </is>
+      </c>
+      <c r="E104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M104" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>26646</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>FERENTINO</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>ERANDO FABIO</t>
+        </is>
+      </c>
+      <c r="E105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M105" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>27183</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>ROMA</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>GIOVANNINI DANIELE</t>
+        </is>
+      </c>
+      <c r="E106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F106" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="G106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M106" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>51486</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>CORRIDONIA</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
+        <is>
+          <t>MORETTI MARCO MARIA</t>
+        </is>
+      </c>
+      <c r="E107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F107" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="G107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N107" s="2" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>53792</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SIENA</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
+        <is>
+          <t>AMELIO ANTONIO FRANCESCO</t>
+        </is>
+      </c>
+      <c r="E108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F108" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M108" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N108" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>54055</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>POMEZIA</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
+        <is>
+          <t>ERANDO FABIO</t>
+        </is>
+      </c>
+      <c r="E109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F109" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M109" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N109" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>55012</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>REGGIO DI CALABRIA</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
+        <is>
+          <t>VERSACE RENATO</t>
+        </is>
+      </c>
+      <c r="E110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F110" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N110" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>55442</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>AMELIA</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
+        <is>
+          <t>CHIODI ROBERTO</t>
+        </is>
+      </c>
+      <c r="E111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="F111" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N111" s="2" t="inlineStr">
+        <is>
+          <t>Bene</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W15</t>
+          <t>W16</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>101</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>5889</v>
+        <v>6290</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4476</v>
+        <v>4733</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1321</v>
+        <v>1437</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>342</v>
+        <v>363</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>475</v>
+        <v>504</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="K11" s="12" t="n">
+        <v>81</v>
+      </c>
+      <c r="L11" s="12" t="n">
+        <v>542</v>
+      </c>
+      <c r="M11" s="12" t="n">
         <v>78</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>519</v>
-      </c>
-      <c r="M11" s="12" t="n">
-        <v>73</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,10 +875,10 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>301</v>
+        <v>323</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>388</v>
+        <v>399</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>40</v>
@@ -887,19 +887,19 @@
         <v>36</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>208</v>
+        <v>220</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>235</v>
+        <v>247</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>32</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>408</v>
+        <v>435</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>360</v>
+        <v>385</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>193</v>
+        <v>208</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H15" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I15" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="J15" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="K15" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="L15" s="12" t="n">
+        <v>169</v>
+      </c>
+      <c r="M15" s="12" t="n">
         <v>35</v>
-      </c>
-      <c r="I15" s="12" t="n">
-        <v>118</v>
-      </c>
-      <c r="J15" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="K15" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="L15" s="12" t="n">
-        <v>161</v>
-      </c>
-      <c r="M15" s="12" t="n">
-        <v>32</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,35 +1091,35 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>166</v>
+        <v>180</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="J16" s="12" t="n">
         <v>45</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>227</v>
+        <v>239</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1145,31 +1145,31 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>161</v>
+        <v>117</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>35</v>
+        <v>103</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>97</v>
+        <v>223</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>14</v>
+        <v>170</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,51 +1249,51 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>154</v>
+        <v>166</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>98</v>
+        <v>36</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>23</v>
+        <v>78</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>133</v>
+        <v>142</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>215</v>
+        <v>100</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>164</v>
+        <v>14</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>139</v>
+        <v>152</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>194</v>
+        <v>127</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>94</v>
+        <v>131</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>49</v>
+        <v>21</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>212</v>
+        <v>182</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>2</v>
+        <v>159</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,39 +1357,39 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>119</v>
+        <v>206</v>
       </c>
       <c r="G21" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H21" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="I21" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="J21" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="K21" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="L21" s="12" t="n">
+        <v>224</v>
+      </c>
+      <c r="M21" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H21" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I21" s="12" t="n">
-        <v>128</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>64</v>
-      </c>
-      <c r="K21" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L21" s="12" t="n">
-        <v>169</v>
-      </c>
-      <c r="M21" s="12" t="n">
-        <v>147</v>
-      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1415,31 +1415,31 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>137</v>
+        <v>145</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="J22" s="12" t="n">
         <v>54</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>172</v>
+        <v>183</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
@@ -1469,28 +1469,28 @@
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>41</v>
@@ -1523,28 +1523,28 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>168</v>
+        <v>178</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>95</v>
+        <v>108</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>96</v>
+        <v>101</v>
       </c>
       <c r="J24" s="12" t="n">
         <v>29</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>2</v>
@@ -1558,12 +1558,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>123</v>
+        <v>135</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>77</v>
+        <v>120</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>49</v>
+        <v>20</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>162</v>
+        <v>202</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1612,12 +1612,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -1627,51 +1627,51 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>127</v>
+        <v>171</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,39 +1681,39 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>156</v>
+        <v>127</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>195</v>
+        <v>137</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1739,28 +1739,28 @@
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>50</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>3</v>
@@ -1774,12 +1774,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,35 +1789,35 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>38</v>
+        <v>68</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>121</v>
+        <v>53</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>65</v>
+        <v>128</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>50</v>
+        <v>123</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>122</v>
+        <v>39</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>35</v>
+        <v>3</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>59</v>
+        <v>82</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>113</v>
+        <v>128</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>3</v>
+        <v>44</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>83</v>
+        <v>166</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>77</v>
+        <v>6</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>111</v>
+        <v>24</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>81</v>
+        <v>54</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>18</v>
+        <v>53</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,51 +2005,51 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>16</v>
+        <v>80</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>28</v>
+        <v>40</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>98</v>
+        <v>51</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -2059,35 +2059,35 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>162</v>
+        <v>127</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>5</v>
+        <v>31</v>
       </c>
       <c r="H34" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="I34" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="J34" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="I34" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J34" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="K34" s="12" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
@@ -2098,12 +2098,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -2113,35 +2113,35 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G35" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="H35" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="H35" s="12" t="n">
-        <v>51</v>
-      </c>
       <c r="I35" s="12" t="n">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>18</v>
+        <v>31</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>79</v>
+        <v>106</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
@@ -2171,19 +2171,19 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H36" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="J36" s="12" t="n">
         <v>9</v>
@@ -2192,14 +2192,14 @@
         <v>45</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2225,28 +2225,28 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>70</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>7</v>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,51 +2275,51 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>104</v>
+        <v>73</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>34</v>
+        <v>6</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,35 +2329,35 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>15</v>
+        <v>36</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>26</v>
+        <v>43</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
@@ -2368,12 +2368,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -2383,35 +2383,35 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>72</v>
+        <v>83</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>93</v>
+        <v>119</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>45</v>
+        <v>29</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K40" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>205</v>
+        <v>100</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,35 +2437,35 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="H41" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I41" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I41" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="J41" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="K41" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>38</v>
+        <v>119</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2495,47 +2495,47 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>69</v>
+        <v>96</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>46</v>
+        <v>72</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>132</v>
+        <v>219</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>4</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="J43" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="K43" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K43" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L43" s="12" t="n">
-        <v>90</v>
+        <v>38</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>1</v>
@@ -2584,12 +2584,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -2599,35 +2599,35 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>77</v>
+        <v>106</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>110</v>
+        <v>132</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,39 +2653,39 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>102</v>
+        <v>71</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2711,28 +2711,28 @@
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>19</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>15</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>0</v>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>79</v>
+        <v>33</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>3</v>
+        <v>60</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>39</v>
+        <v>53</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,39 +2923,39 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>49</v>
+        <v>1</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>48</v>
+        <v>63</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2981,47 +2981,47 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>51</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I51" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="J51" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>68</v>
+        <v>37</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,39 +3085,39 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>27</v>
+        <v>2</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="J53" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>61</v>
+        <v>109</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3143,28 +3143,28 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>0</v>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,51 +3193,51 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>35</v>
+        <v>69</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J55" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>33</v>
+        <v>64</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,39 +3247,39 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>113</v>
+        <v>36</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H56" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H56" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="I56" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>105</v>
+        <v>34</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F57" s="12" t="n">
         <v>38</v>
@@ -3317,7 +3317,7 @@
         <v>7</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="J57" s="12" t="n">
         <v>12</v>
@@ -3326,26 +3326,26 @@
         <v>2</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>56</v>
+        <v>81</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>64</v>
+        <v>76</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,32 +3409,32 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
@@ -3467,10 +3467,10 @@
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G60" s="12" t="n">
         <v>2</v>
@@ -3479,16 +3479,16 @@
         <v>19</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K60" s="12" t="n">
         <v>6</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>148</v>
+        <v>159</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
@@ -3521,7 +3521,7 @@
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="F61" s="12" t="n">
         <v>69</v>
@@ -3533,16 +3533,16 @@
         <v>5</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>0</v>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3575,47 +3575,47 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,39 +3625,39 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
         <v>36</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>78</v>
+        <v>46</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>69</v>
+        <v>45</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3704,7 +3704,7 @@
         <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M64" s="12" t="n">
         <v>1</v>
@@ -3740,7 +3740,7 @@
         <v>35</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>0</v>
@@ -3758,7 +3758,7 @@
         <v>13</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>1</v>
@@ -3772,12 +3772,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,35 +3787,35 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="J66" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K66" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L66" s="12" t="n">
-        <v>86</v>
+        <v>39</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3845,28 +3845,28 @@
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H67" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K67" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>143</v>
+        <v>156</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>2</v>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,46 +3895,46 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>67</v>
+        <v>43</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>41</v>
+        <v>75</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3949,35 +3949,35 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H69" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="K69" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L69" s="12" t="n">
+        <v>89</v>
+      </c>
+      <c r="M69" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="L69" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="M69" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
@@ -3988,12 +3988,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,35 +4003,35 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I70" s="12" t="n">
         <v>27</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>69</v>
+        <v>42</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
@@ -4042,12 +4042,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -4057,51 +4057,51 @@
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>0</v>
+        <v>67</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>47</v>
+        <v>71</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,7 +4111,7 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
@@ -4121,25 +4121,25 @@
         <v>0</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>34</v>
+        <v>58</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K73" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="L73" s="12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J74" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,39 +4273,39 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>66</v>
+        <v>51</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4331,19 +4331,19 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F76" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J76" s="12" t="n">
         <v>8</v>
@@ -4352,14 +4352,14 @@
         <v>0</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="M76" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4388,13 +4388,13 @@
         <v>20</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>11</v>
@@ -4406,7 +4406,7 @@
         <v>9</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>4</v>
@@ -4439,28 +4439,28 @@
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F78" s="12" t="n">
         <v>22</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>1</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,39 +4543,39 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
         <v>16</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="J80" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J80" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="K80" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4601,7 +4601,7 @@
         </is>
       </c>
       <c r="E81" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F81" s="12" t="n">
         <v>19</v>
@@ -4613,7 +4613,7 @@
         <v>12</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>1</v>
@@ -4622,7 +4622,7 @@
         <v>5</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M81" s="12" t="n">
         <v>2</v>
@@ -4636,12 +4636,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -4651,51 +4651,51 @@
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E82" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="F82" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="G82" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H82" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G82" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="H82" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I82" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,32 +4705,32 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>14</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
@@ -4744,12 +4744,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>PENNE</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,32 +4759,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J84" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" s="12" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
@@ -4823,41 +4823,41 @@
         <v>0</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>PENNE</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,32 +4867,32 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F86" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J86" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I86" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>0</v>
@@ -4925,7 +4925,7 @@
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F87" s="12" t="n">
         <v>31</v>
@@ -4934,10 +4934,10 @@
         <v>18</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>4</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>74</v>
+        <v>83</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
@@ -4979,7 +4979,7 @@
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F88" s="12" t="n">
         <v>0</v>
@@ -4991,7 +4991,7 @@
         <v>0</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J88" s="12" t="n">
         <v>3</v>
@@ -5000,14 +5000,14 @@
         <v>0</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5036,10 +5036,10 @@
         <v>9</v>
       </c>
       <c r="F89" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H89" s="12" t="n">
         <v>1</v>
@@ -5048,20 +5048,20 @@
         <v>11</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
         <v>8</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5216,14 +5216,14 @@
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
         <v>2</v>
       </c>
       <c r="F96" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="G96" s="12" t="n">
         <v>0</v>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>0</v>
@@ -5684,7 +5684,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>0</v>
@@ -5954,13 +5954,13 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I106" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W16</t>
+          <t>W17</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>101</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6290</v>
+        <v>6671</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>4733</v>
+        <v>5008</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1437</v>
+        <v>1557</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>363</v>
+        <v>394</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>504</v>
+        <v>536</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>81</v>
+        <v>94</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>542</v>
+        <v>584</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,31 +875,31 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>399</v>
+        <v>428</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>250</v>
+        <v>264</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
@@ -929,31 +929,31 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>247</v>
+        <v>268</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>172</v>
+        <v>182</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>385</v>
+        <v>409</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>220</v>
+        <v>237</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,31 +1037,31 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>126</v>
+        <v>138</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
@@ -1091,10 +1091,10 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G16" s="12" t="n">
         <v>12</v>
@@ -1103,19 +1103,19 @@
         <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>130</v>
+        <v>135</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>239</v>
+        <v>250</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1145,28 +1145,28 @@
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>175</v>
+        <v>185</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>124</v>
+        <v>129</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>14</v>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,51 +1195,51 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>117</v>
+        <v>184</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>103</v>
+        <v>41</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>23</v>
+        <v>82</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>143</v>
+        <v>153</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>223</v>
+        <v>106</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>170</v>
+        <v>14</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1249,35 +1249,35 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>171</v>
+        <v>122</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>36</v>
+        <v>105</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>78</v>
+        <v>23</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>84</v>
+        <v>89</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>100</v>
+        <v>237</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>14</v>
+        <v>180</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
@@ -1288,12 +1288,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1303,51 +1303,51 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>8</v>
+        <v>38</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -1357,51 +1357,51 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>206</v>
+        <v>130</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>96</v>
+        <v>138</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>39</v>
+        <v>65</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>224</v>
+        <v>194</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>2</v>
+        <v>160</v>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -1411,51 +1411,51 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>124</v>
+        <v>219</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>111</v>
+        <v>98</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>54</v>
+        <v>39</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>183</v>
+        <v>240</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>119</v>
+        <v>3</v>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>114</v>
+        <v>171</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H23" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I23" s="12" t="n">
+        <v>130</v>
+      </c>
+      <c r="J23" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I23" s="12" t="n">
-        <v>113</v>
-      </c>
-      <c r="J23" s="12" t="n">
-        <v>43</v>
-      </c>
       <c r="K23" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>117</v>
+        <v>213</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1523,47 +1523,47 @@
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>178</v>
+        <v>126</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>108</v>
+        <v>38</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>168</v>
+        <v>122</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>2</v>
+        <v>41</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -1573,35 +1573,35 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>135</v>
+        <v>145</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>165</v>
+        <v>187</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>20</v>
+        <v>42</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>202</v>
+        <v>178</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>143</v>
+        <v>148</v>
       </c>
       <c r="G26" s="12" t="n">
         <v>3</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J26" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>5</v>
@@ -1666,12 +1666,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -1681,51 +1681,51 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>127</v>
+        <v>153</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>36</v>
+        <v>21</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,35 +1735,35 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>18</v>
+        <v>48</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>69</v>
+        <v>97</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
@@ -1793,28 +1793,28 @@
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>112</v>
+        <v>126</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>74</v>
+        <v>88</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>0</v>
@@ -1828,12 +1828,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>128</v>
+        <v>39</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>36</v>
+        <v>3</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>37</v>
+        <v>22</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>61</v>
+        <v>85</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>18</v>
+        <v>44</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>3</v>
+        <v>45</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>39</v>
+        <v>137</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>82</v>
+        <v>65</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>27</v>
+        <v>48</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>166</v>
+        <v>86</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>24</v>
+        <v>117</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="K32" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="L32" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="L32" s="12" t="n">
-        <v>75</v>
-      </c>
       <c r="M32" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>84</v>
+        <v>179</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>80</v>
+        <v>6</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>113</v>
+        <v>25</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>83</v>
+        <v>57</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>20</v>
+        <v>53</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>51</v>
+        <v>81</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2063,28 +2063,28 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>101</v>
+        <v>107</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>2</v>
@@ -2117,10 +2117,10 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>17</v>
@@ -2129,16 +2129,16 @@
         <v>28</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>31</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
@@ -2171,16 +2171,16 @@
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>89</v>
+        <v>103</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>17</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>45</v>
@@ -2189,17 +2189,17 @@
         <v>9</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>45</v>
+        <v>59</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2225,31 +2225,31 @@
         </is>
       </c>
       <c r="E37" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="F37" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="F37" s="12" t="n">
-        <v>83</v>
-      </c>
       <c r="G37" s="12" t="n">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,39 +2329,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>85</v>
+        <v>95</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>109</v>
+        <v>78</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>36</v>
+        <v>6</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2387,31 +2387,31 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,39 +2437,39 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>80</v>
+        <v>111</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>12</v>
+        <v>37</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="J41" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="K41" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="L41" s="12" t="n">
+        <v>140</v>
+      </c>
+      <c r="M41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K41" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L41" s="12" t="n">
-        <v>119</v>
-      </c>
-      <c r="M41" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2495,28 +2495,28 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K42" s="12" t="n">
         <v>13</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>219</v>
+        <v>231</v>
       </c>
       <c r="M42" s="12" t="n">
         <v>4</v>
@@ -2549,35 +2549,35 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J43" s="12" t="n">
         <v>23</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2603,28 +2603,28 @@
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H44" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J44" s="12" t="n">
         <v>25</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>57</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>23</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>132</v>
+        <v>147</v>
       </c>
       <c r="M44" s="12" t="n">
         <v>5</v>
@@ -2638,12 +2638,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>71</v>
+        <v>0</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>94</v>
+        <v>58</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,51 +2707,51 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>100</v>
+        <v>41</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>70</v>
+        <v>6</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,51 +2761,51 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>39</v>
+        <v>76</v>
       </c>
       <c r="G47" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="H47" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H47" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="I47" s="12" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,51 +2815,51 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>3</v>
+        <v>79</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>122</v>
+        <v>136</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,39 +2869,39 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>55</v>
+        <v>126</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2927,28 +2927,28 @@
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J50" s="12" t="n">
         <v>10</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M50" s="12" t="n">
         <v>0</v>
@@ -2981,47 +2981,47 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F51" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>55</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="I51" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="G51" s="12" t="n">
-        <v>51</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>49</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>47</v>
-      </c>
       <c r="J51" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -3031,51 +3031,51 @@
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>37</v>
+        <v>61</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>65</v>
+        <v>80</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>115</v>
+        <v>71</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>109</v>
+        <v>64</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3124,12 +3124,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -3139,51 +3139,51 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>69</v>
+        <v>121</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>64</v>
+        <v>112</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3251,47 +3251,47 @@
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H56" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="M56" s="12" t="n">
         <v>3</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>38</v>
+        <v>85</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>5</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>37</v>
+        <v>78</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,39 +3355,39 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="J58" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K58" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K58" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="L58" s="12" t="n">
-        <v>76</v>
+        <v>41</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3413,28 +3413,28 @@
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H59" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="M59" s="12" t="n">
         <v>0</v>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,51 +3463,51 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="F60" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="F60" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="G60" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H60" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="K60" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H60" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I60" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L60" s="12" t="n">
-        <v>159</v>
+        <v>37</v>
       </c>
       <c r="M60" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,32 +3517,32 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>46</v>
+        <v>168</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>0</v>
@@ -3556,12 +3556,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -3571,51 +3571,51 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>42</v>
+        <v>73</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>27</v>
+        <v>5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,51 +3625,51 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>24</v>
+        <v>38</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>20</v>
+        <v>33</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,51 +3787,51 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
         <v>35</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="G66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H66" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I66" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,46 +3841,46 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F67" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>156</v>
+        <v>40</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3895,46 +3895,46 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F68" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="G68" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H68" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>43</v>
-      </c>
-      <c r="G68" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="H68" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I68" s="12" t="n">
-        <v>34</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>16</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>75</v>
+        <v>170</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3949,32 +3949,32 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
         <v>34</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G69" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="K69" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H69" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L69" s="12" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>1</v>
@@ -4007,10 +4007,10 @@
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G70" s="12" t="n">
         <v>2</v>
@@ -4019,7 +4019,7 @@
         <v>8</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>10</v>
@@ -4061,16 +4061,16 @@
         </is>
       </c>
       <c r="E71" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="F71" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G71" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>29</v>
@@ -4079,10 +4079,10 @@
         <v>11</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>2</v>
@@ -4096,12 +4096,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -4111,46 +4111,46 @@
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>0</v>
+        <v>58</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J72" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K72" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K72" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L72" s="12" t="n">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4169,31 +4169,31 @@
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J73" s="12" t="n">
         <v>7</v>
       </c>
       <c r="K73" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L73" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="M73" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>22</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,51 +4219,51 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>19</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="M74" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -4273,46 +4273,46 @@
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E75" s="12" t="n">
         <v>27</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="J75" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K75" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K75" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L75" s="12" t="n">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4331,35 +4331,35 @@
         </is>
       </c>
       <c r="E76" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="F76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G76" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="F76" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="G76" s="12" t="n">
+      <c r="H76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="J76" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="K76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H76" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I76" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J76" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="K76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L76" s="12" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
         <v>9</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M77" s="12" t="n">
         <v>4</v>
@@ -4442,13 +4442,13 @@
         <v>19</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I78" s="12" t="n">
         <v>13</v>
@@ -4460,7 +4460,7 @@
         <v>6</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
@@ -4474,12 +4474,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -4489,35 +4489,35 @@
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="E79" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="I79" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J79" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="M79" s="12" t="n">
         <v>3</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L79" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
@@ -4528,12 +4528,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -4543,51 +4543,51 @@
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="E80" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>43</v>
+        <v>14</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -4597,35 +4597,35 @@
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E81" s="12" t="n">
         <v>16</v>
       </c>
       <c r="F81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="H81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="G81" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="H81" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I81" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="J81" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
@@ -4658,13 +4658,13 @@
         <v>16</v>
       </c>
       <c r="F82" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="G82" s="12" t="n">
         <v>2</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>9</v>
@@ -4676,14 +4676,14 @@
         <v>7</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4712,13 +4712,13 @@
         <v>15</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>14</v>
@@ -4730,26 +4730,26 @@
         <v>4</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
@@ -4769,41 +4769,41 @@
         <v>0</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,17 +4813,17 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H85" s="12" t="n">
         <v>0</v>
@@ -4832,32 +4832,32 @@
         <v>14</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>PENNE</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,39 +4867,39 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K86" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="K86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L86" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="M86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4925,19 +4925,19 @@
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G87" s="12" t="n">
         <v>18</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J87" s="12" t="n">
         <v>4</v>
@@ -4946,7 +4946,7 @@
         <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
@@ -4960,12 +4960,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>PENNE</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -4975,32 +4975,32 @@
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E88" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="G88" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J88" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H88" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="J88" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M88" s="12" t="n">
         <v>0</v>
@@ -5169,7 +5169,7 @@
       </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5195,7 +5195,7 @@
         </is>
       </c>
       <c r="E92" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F92" s="12" t="n">
         <v>0</v>
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J92" s="12" t="n">
         <v>1</v>
@@ -5216,14 +5216,14 @@
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5249,7 +5249,7 @@
         </is>
       </c>
       <c r="E93" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F93" s="12" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="I93" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J93" s="12" t="n">
         <v>0</v>
@@ -5270,10 +5270,10 @@
         <v>3</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>0</v>
@@ -5684,13 +5684,13 @@
         <v>0</v>
       </c>
       <c r="F101" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G101" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H101" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I101" s="12" t="n">
         <v>0</v>
@@ -5954,7 +5954,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -607,7 +607,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W17</t>
+          <t>W18</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -676,13 +676,13 @@
         <v>101</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>6671</v>
+        <v>7020</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5008</v>
+        <v>5280</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1557</v>
+        <v>1690</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -821,31 +821,31 @@
         </is>
       </c>
       <c r="E11" s="12" t="n">
-        <v>394</v>
+        <v>413</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>536</v>
+        <v>553</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>584</v>
+        <v>617</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
@@ -875,28 +875,28 @@
         </is>
       </c>
       <c r="E12" s="12" t="n">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>428</v>
+        <v>455</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>264</v>
+        <v>278</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>105</v>
@@ -929,35 +929,35 @@
         </is>
       </c>
       <c r="E13" s="12" t="n">
-        <v>237</v>
+        <v>265</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>268</v>
+        <v>289</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>182</v>
+        <v>205</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>461</v>
+        <v>488</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>409</v>
+        <v>434</v>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -983,31 +983,31 @@
         </is>
       </c>
       <c r="E14" s="12" t="n">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
@@ -1037,35 +1037,35 @@
         </is>
       </c>
       <c r="E15" s="12" t="n">
-        <v>223</v>
+        <v>235</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>36</v>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1091,31 +1091,31 @@
         </is>
       </c>
       <c r="E16" s="12" t="n">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>189</v>
+        <v>200</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
@@ -1126,12 +1126,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1141,32 +1141,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E17" s="12" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>49</v>
+        <v>43</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>88</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>136</v>
+        <v>159</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>56</v>
+        <v>92</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>46</v>
+        <v>20</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="M17" s="12" t="n">
         <v>14</v>
@@ -1180,12 +1180,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1195,39 +1195,39 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E18" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>184</v>
+        <v>208</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>82</v>
+        <v>104</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>89</v>
+        <v>57</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>14</v>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1253,35 +1253,35 @@
         </is>
       </c>
       <c r="E19" s="12" t="n">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>23</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>237</v>
+        <v>244</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>180</v>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1307,35 +1307,35 @@
         </is>
       </c>
       <c r="E20" s="12" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>126</v>
+        <v>139</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1361,28 +1361,28 @@
         </is>
       </c>
       <c r="E21" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>160</v>
@@ -1415,28 +1415,28 @@
         </is>
       </c>
       <c r="E22" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>240</v>
+        <v>257</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>3</v>
@@ -1450,12 +1450,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -1465,51 +1465,51 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E23" s="12" t="n">
-        <v>147</v>
+        <v>158</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>171</v>
+        <v>128</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>35</v>
+        <v>57</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>213</v>
+        <v>127</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -1519,35 +1519,35 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E24" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>126</v>
+        <v>182</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>122</v>
+        <v>224</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
@@ -1577,28 +1577,28 @@
         </is>
       </c>
       <c r="E25" s="12" t="n">
-        <v>145</v>
+        <v>150</v>
       </c>
       <c r="F25" s="12" t="n">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>42</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="M25" s="12" t="n">
         <v>2</v>
@@ -1631,28 +1631,28 @@
         </is>
       </c>
       <c r="E26" s="12" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="F26" s="12" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="M26" s="12" t="n">
         <v>5</v>
@@ -1685,31 +1685,31 @@
         </is>
       </c>
       <c r="E27" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="J27" s="12" t="n">
         <v>21</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>133</v>
+        <v>143</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
@@ -1720,12 +1720,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -1735,51 +1735,51 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E28" s="12" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>145</v>
+        <v>76</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>48</v>
+        <v>26</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>145</v>
+        <v>60</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -1789,51 +1789,51 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E29" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>75</v>
+        <v>160</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>25</v>
+        <v>51</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>88</v>
+        <v>102</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>56</v>
+        <v>154</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -1843,35 +1843,35 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E30" s="12" t="n">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>39</v>
+        <v>141</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>44</v>
+        <v>18</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
@@ -1882,12 +1882,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -1897,35 +1897,35 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E31" s="12" t="n">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>137</v>
+        <v>42</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>38</v>
+        <v>22</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>18</v>
+        <v>46</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>48</v>
+        <v>30</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
@@ -1936,12 +1936,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -1951,51 +1951,51 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E32" s="12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="F32" s="12" t="n">
+        <v>184</v>
+      </c>
+      <c r="G32" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K32" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="L32" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G32" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="H32" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>87</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="L32" s="12" t="n">
-        <v>53</v>
-      </c>
       <c r="M32" s="12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2005,39 +2005,39 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E33" s="12" t="n">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>179</v>
+        <v>90</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>25</v>
+        <v>122</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>57</v>
+        <v>95</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>17</v>
+        <v>46</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>53</v>
+        <v>23</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2063,28 +2063,28 @@
         </is>
       </c>
       <c r="E34" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M34" s="12" t="n">
         <v>2</v>
@@ -2117,28 +2117,28 @@
         </is>
       </c>
       <c r="E35" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>1</v>
@@ -2152,12 +2152,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -2167,51 +2167,51 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="E36" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="G36" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K36" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="L36" s="12" t="n">
+        <v>137</v>
+      </c>
+      <c r="M36" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H36" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I36" s="12" t="n">
-        <v>45</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="K36" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L36" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="M36" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -2221,35 +2221,35 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E37" s="12" t="n">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>72</v>
+        <v>17</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>86</v>
+        <v>47</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>45</v>
+        <v>9</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>35</v>
+        <v>81</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
@@ -2260,12 +2260,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -2275,35 +2275,35 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E38" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>82</v>
+        <v>94</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>14</v>
+        <v>33</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>18</v>
+        <v>75</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>66</v>
+        <v>91</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>8</v>
+        <v>47</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>128</v>
+        <v>36</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
@@ -2314,12 +2314,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -2329,39 +2329,39 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="E39" s="12" t="n">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="F39" s="12" t="n">
-        <v>78</v>
+        <v>121</v>
       </c>
       <c r="G39" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="H39" s="12" t="n">
+        <v>53</v>
+      </c>
+      <c r="I39" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>153</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H39" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="I39" s="12" t="n">
-        <v>50</v>
-      </c>
-      <c r="J39" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>143</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2387,28 +2387,28 @@
         </is>
       </c>
       <c r="E40" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="F40" s="12" t="n">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>108</v>
+        <v>119</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>2</v>
@@ -2422,12 +2422,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -2437,39 +2437,39 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E41" s="12" t="n">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>37</v>
+        <v>6</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>27</v>
+        <v>46</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>140</v>
+        <v>155</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2495,19 +2495,19 @@
         </is>
       </c>
       <c r="E42" s="12" t="n">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="J42" s="12" t="n">
         <v>24</v>
@@ -2516,10 +2516,10 @@
         <v>13</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>231</v>
+        <v>250</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
@@ -2549,28 +2549,28 @@
         </is>
       </c>
       <c r="E43" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>6</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I43" s="12" t="n">
         <v>53</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>1</v>
@@ -2584,7 +2584,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2599,46 +2599,46 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E44" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>112</v>
+        <v>0</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>19</v>
+        <v>70</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="K44" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="M44" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L44" s="12" t="n">
-        <v>147</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2653,51 +2653,51 @@
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E45" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F45" s="12" t="n">
-        <v>0</v>
+        <v>117</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>58</v>
+        <v>153</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -2707,35 +2707,35 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="E46" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>111</v>
+        <v>104</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
@@ -2746,12 +2746,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -2761,35 +2761,35 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E47" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>76</v>
+        <v>44</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>57</v>
+        <v>42</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>4</v>
+        <v>24</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>99</v>
+        <v>121</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
@@ -2800,12 +2800,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -2815,32 +2815,32 @@
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="E48" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>104</v>
+        <v>85</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>79</v>
+        <v>31</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>136</v>
+        <v>69</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>0</v>
@@ -2854,12 +2854,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -2869,51 +2869,51 @@
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E49" s="12" t="n">
         <v>63</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>36</v>
+        <v>109</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>4</v>
+        <v>81</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -2923,39 +2923,39 @@
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="E50" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F50" s="12" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>65</v>
+        <v>129</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2981,35 +2981,35 @@
         </is>
       </c>
       <c r="E51" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="F51" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="G51" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I51" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="F51" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="G51" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>50</v>
-      </c>
       <c r="J51" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3035,31 +3035,31 @@
         </is>
       </c>
       <c r="E52" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F52" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
@@ -3070,12 +3070,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -3085,35 +3085,35 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E53" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>71</v>
+        <v>126</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="I53" s="12" t="n">
         <v>33</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>20</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>64</v>
+        <v>116</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="E54" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>17</v>
@@ -3155,16 +3155,16 @@
         <v>29</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>3</v>
@@ -3178,12 +3178,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -3193,35 +3193,35 @@
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E55" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="F55" s="12" t="n">
-        <v>121</v>
+        <v>73</v>
       </c>
       <c r="G55" s="12" t="n">
         <v>7</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>112</v>
+        <v>69</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
@@ -3232,12 +3232,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -3247,51 +3247,51 @@
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E56" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="F56" s="12" t="n">
-        <v>38</v>
+        <v>69</v>
       </c>
       <c r="G56" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H56" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="I56" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K56" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>38</v>
+        <v>77</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -3301,51 +3301,51 @@
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E57" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F57" s="12" t="n">
-        <v>85</v>
+        <v>56</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="J57" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="K57" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K57" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="L57" s="12" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -3355,51 +3355,51 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E58" s="12" t="n">
-        <v>45</v>
+        <v>49</v>
       </c>
       <c r="F58" s="12" t="n">
-        <v>43</v>
+        <v>87</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>4</v>
+        <v>30</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>41</v>
+        <v>84</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -3409,35 +3409,35 @@
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E59" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="F59" s="12" t="n">
-        <v>62</v>
+        <v>40</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>75</v>
+        <v>39</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
@@ -3448,12 +3448,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -3463,20 +3463,20 @@
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E60" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="F60" s="12" t="n">
-        <v>40</v>
+        <v>98</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="I60" s="12" t="n">
         <v>38</v>
@@ -3485,29 +3485,29 @@
         <v>12</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>37</v>
+        <v>177</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -3517,39 +3517,39 @@
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="E61" s="12" t="n">
         <v>42</v>
       </c>
       <c r="F61" s="12" t="n">
-        <v>84</v>
+        <v>43</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="J61" s="12" t="n">
         <v>12</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>168</v>
+        <v>37</v>
       </c>
       <c r="M61" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3575,10 +3575,10 @@
         </is>
       </c>
       <c r="E62" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F62" s="12" t="n">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>0</v>
@@ -3587,7 +3587,7 @@
         <v>5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J62" s="12" t="n">
         <v>13</v>
@@ -3596,7 +3596,7 @@
         <v>7</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M62" s="12" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -3625,35 +3625,35 @@
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E63" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F63" s="12" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
@@ -3664,12 +3664,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -3679,35 +3679,35 @@
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="E64" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F64" s="12" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>49</v>
+        <v>183</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
@@ -3718,12 +3718,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -3733,51 +3733,51 @@
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E65" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="F65" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>4</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="M65" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -3787,35 +3787,35 @@
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E66" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F66" s="12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
@@ -3826,12 +3826,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -3841,35 +3841,35 @@
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="E67" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="F67" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="G67" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="H67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="H67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="12" t="n">
+      <c r="J67" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J67" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K67" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="L67" s="12" t="n">
-        <v>40</v>
+        <v>83</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
@@ -3880,12 +3880,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -3895,51 +3895,51 @@
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="E68" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="F68" s="12" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>170</v>
+        <v>73</v>
       </c>
       <c r="M68" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -3949,51 +3949,51 @@
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="E69" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F69" s="12" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="G69" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="J69" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="K69" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H69" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K69" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="L69" s="12" t="n">
-        <v>80</v>
+        <v>43</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -4003,39 +4003,39 @@
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E70" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F70" s="12" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4070,7 +4070,7 @@
         <v>2</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I71" s="12" t="n">
         <v>29</v>
@@ -4082,7 +4082,7 @@
         <v>4</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="M71" s="12" t="n">
         <v>2</v>
@@ -4115,16 +4115,16 @@
         </is>
       </c>
       <c r="E72" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F72" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G72" s="12" t="n">
         <v>9</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>21</v>
@@ -4133,10 +4133,10 @@
         <v>8</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="M72" s="12" t="n">
         <v>0</v>
@@ -4150,12 +4150,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -4165,35 +4165,35 @@
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="E73" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F73" s="12" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
@@ -4204,12 +4204,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -4219,46 +4219,46 @@
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E74" s="12" t="n">
         <v>28</v>
       </c>
       <c r="F74" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="G74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H74" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="K74" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="L74" s="12" t="n">
+        <v>114</v>
+      </c>
+      <c r="M74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4277,35 +4277,35 @@
         </is>
       </c>
       <c r="E75" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F75" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>29</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>101</v>
+        <v>64</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4385,16 +4385,16 @@
         </is>
       </c>
       <c r="E77" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F77" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="G77" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>11</v>
@@ -4403,13 +4403,13 @@
         <v>6</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
@@ -4439,19 +4439,19 @@
         </is>
       </c>
       <c r="E78" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="F78" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J78" s="12" t="n">
         <v>1</v>
@@ -4460,7 +4460,7 @@
         <v>6</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="M78" s="12" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
         <v>19</v>
       </c>
       <c r="F79" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G79" s="12" t="n">
         <v>7</v>
@@ -4514,7 +4514,7 @@
         <v>7</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="M79" s="12" t="n">
         <v>3</v>
@@ -4550,13 +4550,13 @@
         <v>18</v>
       </c>
       <c r="F80" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>12</v>
@@ -4607,7 +4607,7 @@
         <v>0</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>0</v>
@@ -4622,14 +4622,14 @@
         <v>0</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4664,7 +4664,7 @@
         <v>2</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I82" s="12" t="n">
         <v>9</v>
@@ -4676,7 +4676,7 @@
         <v>7</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M82" s="12" t="n">
         <v>0</v>
@@ -4690,12 +4690,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -4705,51 +4705,51 @@
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="E83" s="12" t="n">
         <v>15</v>
       </c>
       <c r="F83" s="12" t="n">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>3</v>
+        <v>46</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>18</v>
+        <v>91</v>
       </c>
       <c r="M83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -4759,32 +4759,32 @@
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="E84" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F84" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>35</v>
+        <v>19</v>
       </c>
       <c r="M84" s="12" t="n">
         <v>0</v>
@@ -4798,12 +4798,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -4813,7 +4813,7 @@
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="E85" s="12" t="n">
@@ -4823,41 +4823,41 @@
         <v>0</v>
       </c>
       <c r="G85" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J85" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="J85" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>14</v>
+        <v>37</v>
       </c>
       <c r="M85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -4867,7 +4867,7 @@
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="E86" s="12" t="n">
@@ -4877,25 +4877,25 @@
         <v>0</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
@@ -4906,12 +4906,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -4921,39 +4921,39 @@
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="E87" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F87" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J87" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K87" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="L87" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="J87" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="K87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L87" s="12" t="n">
-        <v>87</v>
-      </c>
       <c r="M87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5033,7 @@
         </is>
       </c>
       <c r="E89" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F89" s="12" t="n">
         <v>7</v>
@@ -5051,10 +5051,10 @@
         <v>3</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="M89" s="12" t="n">
         <v>0</v>
@@ -5162,7 +5162,7 @@
         <v>0</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M91" s="12" t="n">
         <v>0</v>
@@ -5216,14 +5216,14 @@
         <v>0</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5270,14 +5270,14 @@
         <v>3</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M93" s="12" t="n">
         <v>2</v>
       </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5522,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G98" s="12" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G99" s="12" t="n">
         <v>0</v>
@@ -5954,13 +5954,13 @@
         <v>0</v>
       </c>
       <c r="F106" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G106" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H106" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I106" s="12" t="n">
         <v>0</v>
@@ -6008,7 +6008,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G107" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -209,8 +209,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N111" headerRowCount="1">
-  <autoFilter ref="A10:N111"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N96" headerRowCount="1">
+  <autoFilter ref="A10:N96"/>
   <tableColumns count="14">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
@@ -520,7 +520,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N111"/>
+  <dimension ref="A1:N96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -673,7 +673,7 @@
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
-        <v>101</v>
+        <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
         <v>7020</v>
@@ -5443,816 +5443,6 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
-        <is>
-          <t>05861</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>COPPARO</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
-        <is>
-          <t>BASSI VALERIA</t>
-        </is>
-      </c>
-      <c r="E97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F97" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H97" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M97" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N97" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
-        <is>
-          <t>06128</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>PESARO</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
-        <is>
-          <t>DI VIRGILIO DAVID</t>
-        </is>
-      </c>
-      <c r="E98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F98" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="G98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H98" s="12" t="n">
-        <v>12</v>
-      </c>
-      <c r="I98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M98" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N98" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
-        <is>
-          <t>06520</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>SULMONA</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
-        <is>
-          <t>COLOZZA STEFANO</t>
-        </is>
-      </c>
-      <c r="E99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F99" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="G99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H99" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M99" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N99" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
-        <is>
-          <t>06812</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>MONTECOSARO</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
-        <is>
-          <t>STROLOGO FRANCESCO</t>
-        </is>
-      </c>
-      <c r="E100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F100" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H100" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M100" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N100" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
-        <is>
-          <t>06883</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>PESCARA</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
-        <is>
-          <t>CAIMMI ANDREA</t>
-        </is>
-      </c>
-      <c r="E101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F101" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="G101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H101" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M101" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N101" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
-        <is>
-          <t>06892</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>MANOPPELLO</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
-        <is>
-          <t>D'ANNIBALE EMANUELE</t>
-        </is>
-      </c>
-      <c r="E102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F102" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="G102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M102" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N102" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
-        <is>
-          <t>09297</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>LUCERA</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
-        <is>
-          <t>CASCIANI GABRIELE</t>
-        </is>
-      </c>
-      <c r="E103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F103" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M103" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
-        <is>
-          <t>19740</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>BAGHERIA</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
-        <is>
-          <t>CASSATA FULVIA</t>
-        </is>
-      </c>
-      <c r="E104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F104" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M104" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>26646</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>FERENTINO</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
-        <is>
-          <t>ERANDO FABIO</t>
-        </is>
-      </c>
-      <c r="E105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="G105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H105" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M105" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
-        <is>
-          <t>27183</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>ROMA</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
-        <is>
-          <t>GIOVANNINI DANIELE</t>
-        </is>
-      </c>
-      <c r="E106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F106" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="G106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H106" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="I106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M106" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
-        <is>
-          <t>51486</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>CORRIDONIA</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
-        <is>
-          <t>MORETTI MARCO MARIA</t>
-        </is>
-      </c>
-      <c r="E107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F107" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="G107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H107" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M107" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" s="2" t="inlineStr">
-        <is>
-          <t>Male</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
-        <is>
-          <t>53792</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>SIENA</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
-        <is>
-          <t>AMELIO ANTONIO FRANCESCO</t>
-        </is>
-      </c>
-      <c r="E108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M108" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N108" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
-        <is>
-          <t>54055</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>POMEZIA</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
-        <is>
-          <t>ERANDO FABIO</t>
-        </is>
-      </c>
-      <c r="E109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F109" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H109" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M109" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N109" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
-        <is>
-          <t>55012</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>REGGIO DI CALABRIA</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
-        <is>
-          <t>VERSACE RENATO</t>
-        </is>
-      </c>
-      <c r="E110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F110" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="G110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N110" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
-        <is>
-          <t>55442</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>AMELIA</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>Marcelli Mirko</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
-        <is>
-          <t>CHIODI ROBERTO</t>
-        </is>
-      </c>
-      <c r="E111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F111" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="G111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N111" s="2" t="inlineStr">
-        <is>
-          <t>Bene</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -209,23 +209,24 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:N96" headerRowCount="1">
-  <autoFilter ref="A10:N96"/>
-  <tableColumns count="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Report" displayName="Report" ref="A10:O96" headerRowCount="1">
+  <autoFilter ref="A10:O96"/>
+  <tableColumns count="15">
     <tableColumn id="1" name="PDV"/>
     <tableColumn id="2" name="Città"/>
-    <tableColumn id="3" name="Agente"/>
-    <tableColumn id="4" name="CR"/>
-    <tableColumn id="5" name="Vend 2026"/>
-    <tableColumn id="6" name="Vend 2025"/>
-    <tableColumn id="7" name="Ass 2026"/>
-    <tableColumn id="8" name="Ass 2025"/>
-    <tableColumn id="9" name="Prospect"/>
-    <tableColumn id="10" name="Twin"/>
-    <tableColumn id="11" name="Business"/>
-    <tableColumn id="12" name="Sost anno"/>
-    <tableColumn id="13" name="UP EU"/>
-    <tableColumn id="14" name="Stato"/>
+    <tableColumn id="3" name="Indirizzo"/>
+    <tableColumn id="4" name="Agente"/>
+    <tableColumn id="5" name="CR"/>
+    <tableColumn id="6" name="Vend 2026"/>
+    <tableColumn id="7" name="Vend 2025"/>
+    <tableColumn id="8" name="Ass 2026"/>
+    <tableColumn id="9" name="Ass 2025"/>
+    <tableColumn id="10" name="Prospect"/>
+    <tableColumn id="11" name="Twin"/>
+    <tableColumn id="12" name="Business"/>
+    <tableColumn id="13" name="Sost anno"/>
+    <tableColumn id="14" name="UP EU"/>
+    <tableColumn id="15" name="Stato"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -520,23 +521,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N96"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="10" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="10" customWidth="1" min="13" max="13"/>
-    <col width="12" customWidth="1" min="14" max="14"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="11" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="12" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -558,6 +560,7 @@
       <c r="L1" s="2" t="n"/>
       <c r="M1" s="2" t="n"/>
       <c r="N1" s="2" t="n"/>
+      <c r="O1" s="2" t="n"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="n"/>
@@ -574,6 +577,7 @@
       <c r="L2" s="2" t="n"/>
       <c r="M2" s="2" t="n"/>
       <c r="N2" s="2" t="n"/>
+      <c r="O2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -598,6 +602,7 @@
       <c r="L3" s="2" t="n"/>
       <c r="M3" s="2" t="n"/>
       <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -622,6 +627,7 @@
       <c r="L4" s="2" t="n"/>
       <c r="M4" s="2" t="n"/>
       <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n"/>
@@ -638,6 +644,7 @@
       <c r="L5" s="2" t="n"/>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
+      <c r="O5" s="2" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -670,6 +677,7 @@
       <c r="L6" s="2" t="n"/>
       <c r="M6" s="2" t="n"/>
       <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -694,6 +702,7 @@
       <c r="L7" s="2" t="n"/>
       <c r="M7" s="2" t="n"/>
       <c r="N7" s="2" t="n"/>
+      <c r="O7" s="2" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -710,6 +719,7 @@
       <c r="L8" s="2" t="n"/>
       <c r="M8" s="2" t="n"/>
       <c r="N8" s="2" t="n"/>
+      <c r="O8" s="2" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -726,6 +736,7 @@
       <c r="L9" s="2" t="n"/>
       <c r="M9" s="2" t="n"/>
       <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -740,60 +751,65 @@
       </c>
       <c r="C10" s="11" t="inlineStr">
         <is>
+          <t>Indirizzo</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
           <t>Agente</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>CR</t>
         </is>
       </c>
-      <c r="E10" s="11" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>Vend 2026</t>
         </is>
       </c>
-      <c r="F10" s="11" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>Vend 2025</t>
         </is>
       </c>
-      <c r="G10" s="11" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>Ass 2026</t>
         </is>
       </c>
-      <c r="H10" s="11" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>Ass 2025</t>
         </is>
       </c>
-      <c r="I10" s="11" t="inlineStr">
+      <c r="J10" s="11" t="inlineStr">
         <is>
           <t>Prospect</t>
         </is>
       </c>
-      <c r="J10" s="11" t="inlineStr">
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>Twin</t>
         </is>
       </c>
-      <c r="K10" s="11" t="inlineStr">
+      <c r="L10" s="11" t="inlineStr">
         <is>
           <t>Business</t>
         </is>
       </c>
-      <c r="L10" s="11" t="inlineStr">
+      <c r="M10" s="11" t="inlineStr">
         <is>
           <t>Sost anno</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr">
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>UP EU</t>
         </is>
       </c>
-      <c r="N10" s="11" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>Stato</t>
         </is>
@@ -812,42 +828,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>TIBURTINA 0400</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E11" s="12" t="n">
+      <c r="F11" s="12" t="n">
         <v>413</v>
       </c>
-      <c r="F11" s="12" t="n">
+      <c r="G11" s="12" t="n">
         <v>553</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="H11" s="12" t="n">
         <v>197</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="I11" s="12" t="n">
         <v>123</v>
       </c>
-      <c r="I11" s="12" t="n">
+      <c r="J11" s="12" t="n">
         <v>318</v>
       </c>
-      <c r="J11" s="12" t="n">
+      <c r="K11" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="K11" s="12" t="n">
+      <c r="L11" s="12" t="n">
         <v>97</v>
       </c>
-      <c r="L11" s="12" t="n">
+      <c r="M11" s="12" t="n">
         <v>617</v>
       </c>
-      <c r="M11" s="12" t="n">
+      <c r="N11" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -866,42 +887,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA TIBURTINA KM 19,800 0145</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="F12" s="12" t="n">
         <v>354</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="G12" s="12" t="n">
         <v>455</v>
       </c>
-      <c r="G12" s="12" t="n">
+      <c r="H12" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="I12" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="J12" s="12" t="n">
         <v>278</v>
       </c>
-      <c r="J12" s="12" t="n">
+      <c r="K12" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="K12" s="12" t="n">
+      <c r="L12" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="M12" s="12" t="n">
         <v>403</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="N12" s="12" t="n">
         <v>105</v>
       </c>
-      <c r="N12" s="2" t="inlineStr">
+      <c r="O12" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -920,42 +946,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA LAURENTINA 453</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E13" s="12" t="n">
+      <c r="F13" s="12" t="n">
         <v>265</v>
       </c>
-      <c r="F13" s="12" t="n">
+      <c r="G13" s="12" t="n">
         <v>289</v>
       </c>
-      <c r="G13" s="12" t="n">
+      <c r="H13" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="H13" s="12" t="n">
+      <c r="I13" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="I13" s="12" t="n">
+      <c r="J13" s="12" t="n">
         <v>205</v>
       </c>
-      <c r="J13" s="12" t="n">
+      <c r="K13" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="K13" s="12" t="n">
+      <c r="L13" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="M13" s="12" t="n">
         <v>488</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="N13" s="12" t="n">
         <v>434</v>
       </c>
-      <c r="N13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -974,42 +1005,47 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>CONTRADA S. LIBERATA SS 16</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E14" s="12" t="n">
+      <c r="F14" s="12" t="n">
         <v>246</v>
       </c>
-      <c r="F14" s="12" t="n">
+      <c r="G14" s="12" t="n">
         <v>308</v>
       </c>
-      <c r="G14" s="12" t="n">
+      <c r="H14" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H14" s="12" t="n">
+      <c r="I14" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="I14" s="12" t="n">
+      <c r="J14" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="J14" s="12" t="n">
+      <c r="K14" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="K14" s="12" t="n">
+      <c r="L14" s="12" t="n">
         <v>62</v>
       </c>
-      <c r="L14" s="12" t="n">
+      <c r="M14" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M14" s="12" t="n">
+      <c r="N14" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="N14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1028,42 +1064,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA XXII MAGGIO 1944</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E15" s="12" t="n">
+      <c r="F15" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="F15" s="12" t="n">
+      <c r="G15" s="12" t="n">
         <v>219</v>
       </c>
-      <c r="G15" s="12" t="n">
+      <c r="H15" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="H15" s="12" t="n">
+      <c r="I15" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="I15" s="12" t="n">
+      <c r="J15" s="12" t="n">
         <v>147</v>
       </c>
-      <c r="J15" s="12" t="n">
+      <c r="K15" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="K15" s="12" t="n">
+      <c r="L15" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="L15" s="12" t="n">
+      <c r="M15" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="M15" s="12" t="n">
+      <c r="N15" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="N15" s="2" t="inlineStr">
+      <c r="O15" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1082,42 +1123,47 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S. AURELIA KM 68+885</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E16" s="12" t="n">
+      <c r="F16" s="12" t="n">
         <v>201</v>
       </c>
-      <c r="F16" s="12" t="n">
+      <c r="G16" s="12" t="n">
         <v>200</v>
       </c>
-      <c r="G16" s="12" t="n">
+      <c r="H16" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H16" s="12" t="n">
+      <c r="I16" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I16" s="12" t="n">
+      <c r="J16" s="12" t="n">
         <v>144</v>
       </c>
-      <c r="J16" s="12" t="n">
+      <c r="K16" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="K16" s="12" t="n">
+      <c r="L16" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L16" s="12" t="n">
+      <c r="M16" s="12" t="n">
         <v>266</v>
       </c>
-      <c r="M16" s="12" t="n">
+      <c r="N16" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1136,42 +1182,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E17" s="12" t="n">
+      <c r="F17" s="12" t="n">
         <v>185</v>
       </c>
-      <c r="F17" s="12" t="n">
+      <c r="G17" s="12" t="n">
         <v>193</v>
       </c>
-      <c r="G17" s="12" t="n">
+      <c r="H17" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="H17" s="12" t="n">
+      <c r="I17" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="I17" s="12" t="n">
+      <c r="J17" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="J17" s="12" t="n">
+      <c r="K17" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="K17" s="12" t="n">
+      <c r="L17" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L17" s="12" t="n">
+      <c r="M17" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M17" s="12" t="n">
+      <c r="N17" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1190,42 +1241,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA ANCONA 68</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E18" s="12" t="n">
+      <c r="F18" s="12" t="n">
         <v>185</v>
       </c>
-      <c r="F18" s="12" t="n">
+      <c r="G18" s="12" t="n">
         <v>208</v>
       </c>
-      <c r="G18" s="12" t="n">
+      <c r="H18" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="H18" s="12" t="n">
+      <c r="I18" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="I18" s="12" t="n">
+      <c r="J18" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="J18" s="12" t="n">
+      <c r="K18" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="K18" s="12" t="n">
+      <c r="L18" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L18" s="12" t="n">
+      <c r="M18" s="12" t="n">
         <v>138</v>
       </c>
-      <c r="M18" s="12" t="n">
+      <c r="N18" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1244,42 +1300,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
           <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
-      <c r="E19" s="12" t="n">
+      <c r="F19" s="12" t="n">
         <v>181</v>
       </c>
-      <c r="F19" s="12" t="n">
+      <c r="G19" s="12" t="n">
         <v>124</v>
       </c>
-      <c r="G19" s="12" t="n">
+      <c r="H19" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="H19" s="12" t="n">
+      <c r="I19" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="I19" s="12" t="n">
+      <c r="J19" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="J19" s="12" t="n">
+      <c r="K19" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="K19" s="12" t="n">
+      <c r="L19" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="L19" s="12" t="n">
+      <c r="M19" s="12" t="n">
         <v>244</v>
       </c>
-      <c r="M19" s="12" t="n">
+      <c r="N19" s="12" t="n">
         <v>180</v>
       </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="O19" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1298,42 +1359,47 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S.423 LOC.TORRACCIA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E20" s="12" t="n">
+      <c r="F20" s="12" t="n">
         <v>178</v>
       </c>
-      <c r="F20" s="12" t="n">
+      <c r="G20" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G20" s="12" t="n">
+      <c r="H20" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="H20" s="12" t="n">
+      <c r="I20" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="I20" s="12" t="n">
+      <c r="J20" s="12" t="n">
         <v>139</v>
       </c>
-      <c r="J20" s="12" t="n">
+      <c r="K20" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="K20" s="12" t="n">
+      <c r="L20" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L20" s="12" t="n">
+      <c r="M20" s="12" t="n">
         <v>203</v>
       </c>
-      <c r="M20" s="12" t="n">
+      <c r="N20" s="12" t="n">
         <v>130</v>
       </c>
-      <c r="N20" s="2" t="inlineStr">
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1352,42 +1418,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA DI ACILIA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
           <t>ERANDO FABIO</t>
         </is>
       </c>
-      <c r="E21" s="12" t="n">
+      <c r="F21" s="12" t="n">
         <v>167</v>
       </c>
-      <c r="F21" s="12" t="n">
+      <c r="G21" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="G21" s="12" t="n">
+      <c r="H21" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H21" s="12" t="n">
+      <c r="I21" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I21" s="12" t="n">
+      <c r="J21" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="J21" s="12" t="n">
+      <c r="K21" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="K21" s="12" t="n">
+      <c r="L21" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L21" s="12" t="n">
+      <c r="M21" s="12" t="n">
         <v>207</v>
       </c>
-      <c r="M21" s="12" t="n">
+      <c r="N21" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="N21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1406,42 +1477,47 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA CASILINA KM. 24+950</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E22" s="12" t="n">
+      <c r="F22" s="12" t="n">
         <v>163</v>
       </c>
-      <c r="F22" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>235</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="H22" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="H22" s="12" t="n">
+      <c r="I22" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I22" s="12" t="n">
+      <c r="J22" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="J22" s="12" t="n">
+      <c r="K22" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="K22" s="12" t="n">
+      <c r="L22" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="L22" s="12" t="n">
+      <c r="M22" s="12" t="n">
         <v>257</v>
       </c>
-      <c r="M22" s="12" t="n">
+      <c r="N22" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="O22" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1460,42 +1536,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E23" s="12" t="n">
+      <c r="F23" s="12" t="n">
         <v>158</v>
       </c>
-      <c r="F23" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>128</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="H23" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H23" s="12" t="n">
+      <c r="I23" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="I23" s="12" t="n">
+      <c r="J23" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="J23" s="12" t="n">
+      <c r="K23" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="K23" s="12" t="n">
+      <c r="L23" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L23" s="12" t="n">
+      <c r="M23" s="12" t="n">
         <v>127</v>
       </c>
-      <c r="M23" s="12" t="n">
+      <c r="N23" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -1514,42 +1595,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>CORSO DI FRANCIA 80</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E24" s="12" t="n">
+      <c r="F24" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="F24" s="12" t="n">
+      <c r="G24" s="12" t="n">
         <v>182</v>
       </c>
-      <c r="G24" s="12" t="n">
+      <c r="H24" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="H24" s="12" t="n">
+      <c r="I24" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="I24" s="12" t="n">
+      <c r="J24" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="J24" s="12" t="n">
+      <c r="K24" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="K24" s="12" t="n">
+      <c r="L24" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="L24" s="12" t="n">
+      <c r="M24" s="12" t="n">
         <v>224</v>
       </c>
-      <c r="M24" s="12" t="n">
+      <c r="N24" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1568,42 +1654,47 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E25" s="12" t="n">
+      <c r="F25" s="12" t="n">
         <v>150</v>
       </c>
-      <c r="F25" s="12" t="n">
+      <c r="G25" s="12" t="n">
         <v>192</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="H25" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H25" s="12" t="n">
+      <c r="I25" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="I25" s="12" t="n">
+      <c r="J25" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="K25" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="K25" s="12" t="n">
+      <c r="L25" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="L25" s="12" t="n">
+      <c r="M25" s="12" t="n">
         <v>186</v>
       </c>
-      <c r="M25" s="12" t="n">
+      <c r="N25" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1622,42 +1713,47 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E26" s="12" t="n">
+      <c r="F26" s="12" t="n">
         <v>146</v>
       </c>
-      <c r="F26" s="12" t="n">
+      <c r="G26" s="12" t="n">
         <v>164</v>
       </c>
-      <c r="G26" s="12" t="n">
+      <c r="H26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H26" s="12" t="n">
+      <c r="I26" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I26" s="12" t="n">
+      <c r="J26" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="K26" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K26" s="12" t="n">
+      <c r="L26" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="L26" s="12" t="n">
+      <c r="M26" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="M26" s="12" t="n">
+      <c r="N26" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N26" s="2" t="inlineStr">
+      <c r="O26" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1676,42 +1772,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA CASILINA SUD KM 140+200</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E27" s="12" t="n">
+      <c r="F27" s="12" t="n">
         <v>136</v>
       </c>
-      <c r="F27" s="12" t="n">
+      <c r="G27" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="G27" s="12" t="n">
+      <c r="H27" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H27" s="12" t="n">
+      <c r="I27" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I27" s="12" t="n">
+      <c r="J27" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="J27" s="12" t="n">
+      <c r="K27" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="K27" s="12" t="n">
+      <c r="L27" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="L27" s="12" t="n">
+      <c r="M27" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="M27" s="12" t="n">
+      <c r="N27" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N27" s="2" t="inlineStr">
+      <c r="O27" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1730,42 +1831,47 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E28" s="12" t="n">
+      <c r="F28" s="12" t="n">
         <v>134</v>
       </c>
-      <c r="F28" s="12" t="n">
+      <c r="G28" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G28" s="12" t="n">
+      <c r="H28" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H28" s="12" t="n">
+      <c r="I28" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I28" s="12" t="n">
+      <c r="J28" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="J28" s="12" t="n">
+      <c r="K28" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K28" s="12" t="n">
+      <c r="L28" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="L28" s="12" t="n">
+      <c r="M28" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="M28" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="2" t="inlineStr">
+      <c r="N28" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1784,42 +1890,47 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIALE DELLA CROCE ROSSA 42/D</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
           <t>COLOZZA STEFANO</t>
         </is>
       </c>
-      <c r="E29" s="12" t="n">
+      <c r="F29" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="F29" s="12" t="n">
+      <c r="G29" s="12" t="n">
         <v>160</v>
       </c>
-      <c r="G29" s="12" t="n">
+      <c r="H29" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H29" s="12" t="n">
+      <c r="I29" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="I29" s="12" t="n">
+      <c r="J29" s="12" t="n">
         <v>102</v>
       </c>
-      <c r="J29" s="12" t="n">
+      <c r="K29" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="K29" s="12" t="n">
+      <c r="L29" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L29" s="12" t="n">
+      <c r="M29" s="12" t="n">
         <v>154</v>
       </c>
-      <c r="M29" s="12" t="n">
+      <c r="N29" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="N29" s="2" t="inlineStr">
+      <c r="O29" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -1838,42 +1949,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E30" s="12" t="n">
+      <c r="F30" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="F30" s="12" t="n">
+      <c r="G30" s="12" t="n">
         <v>141</v>
       </c>
-      <c r="G30" s="12" t="n">
+      <c r="H30" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H30" s="12" t="n">
+      <c r="I30" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="I30" s="12" t="n">
+      <c r="J30" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="J30" s="12" t="n">
+      <c r="K30" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K30" s="12" t="n">
+      <c r="L30" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="L30" s="12" t="n">
+      <c r="M30" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M30" s="12" t="n">
+      <c r="N30" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1892,42 +2008,47 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S.4 DIR. KM. 3 + 400</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E31" s="12" t="n">
+      <c r="F31" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="F31" s="12" t="n">
+      <c r="G31" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G31" s="12" t="n">
+      <c r="H31" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H31" s="12" t="n">
+      <c r="I31" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="I31" s="12" t="n">
+      <c r="J31" s="12" t="n">
         <v>89</v>
       </c>
-      <c r="J31" s="12" t="n">
+      <c r="K31" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K31" s="12" t="n">
+      <c r="L31" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L31" s="12" t="n">
+      <c r="M31" s="12" t="n">
         <v>140</v>
       </c>
-      <c r="M31" s="12" t="n">
+      <c r="N31" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="N31" s="2" t="inlineStr">
+      <c r="O31" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -1946,42 +2067,47 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S. 80 KM. 93 + 490</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E32" s="12" t="n">
+      <c r="F32" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="F32" s="12" t="n">
+      <c r="G32" s="12" t="n">
         <v>184</v>
       </c>
-      <c r="G32" s="12" t="n">
+      <c r="H32" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H32" s="12" t="n">
+      <c r="I32" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I32" s="12" t="n">
+      <c r="J32" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="J32" s="12" t="n">
+      <c r="K32" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K32" s="12" t="n">
+      <c r="L32" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="L32" s="12" t="n">
+      <c r="M32" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="M32" s="12" t="n">
+      <c r="N32" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="N32" s="2" t="inlineStr">
+      <c r="O32" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2000,42 +2126,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E33" s="12" t="n">
+      <c r="F33" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="F33" s="12" t="n">
+      <c r="G33" s="12" t="n">
         <v>90</v>
       </c>
-      <c r="G33" s="12" t="n">
+      <c r="H33" s="12" t="n">
         <v>88</v>
       </c>
-      <c r="H33" s="12" t="n">
+      <c r="I33" s="12" t="n">
         <v>122</v>
       </c>
-      <c r="I33" s="12" t="n">
+      <c r="J33" s="12" t="n">
         <v>95</v>
       </c>
-      <c r="J33" s="12" t="n">
+      <c r="K33" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="K33" s="12" t="n">
+      <c r="L33" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="L33" s="12" t="n">
+      <c r="M33" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="M33" s="12" t="n">
+      <c r="N33" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="N33" s="2" t="inlineStr">
+      <c r="O33" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2054,42 +2185,47 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E34" s="12" t="n">
+      <c r="F34" s="12" t="n">
         <v>112</v>
       </c>
-      <c r="F34" s="12" t="n">
+      <c r="G34" s="12" t="n">
         <v>143</v>
       </c>
-      <c r="G34" s="12" t="n">
+      <c r="H34" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="H34" s="12" t="n">
+      <c r="I34" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="I34" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="K34" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="K34" s="12" t="n">
+      <c r="L34" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L34" s="12" t="n">
+      <c r="M34" s="12" t="n">
         <v>92</v>
       </c>
-      <c r="M34" s="12" t="n">
+      <c r="N34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N34" s="2" t="inlineStr">
+      <c r="O34" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2108,42 +2244,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E35" s="12" t="n">
+      <c r="F35" s="12" t="n">
         <v>108</v>
       </c>
-      <c r="F35" s="12" t="n">
+      <c r="G35" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="G35" s="12" t="n">
+      <c r="H35" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H35" s="12" t="n">
+      <c r="I35" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I35" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="K35" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="K35" s="12" t="n">
+      <c r="L35" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L35" s="12" t="n">
+      <c r="M35" s="12" t="n">
         <v>118</v>
       </c>
-      <c r="M35" s="12" t="n">
+      <c r="N35" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N35" s="2" t="inlineStr">
+      <c r="O35" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2162,42 +2303,47 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E36" s="12" t="n">
+      <c r="F36" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="F36" s="12" t="n">
+      <c r="G36" s="12" t="n">
         <v>86</v>
       </c>
-      <c r="G36" s="12" t="n">
+      <c r="H36" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="I36" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="J36" s="12" t="n">
         <v>72</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="K36" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K36" s="12" t="n">
+      <c r="L36" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="L36" s="12" t="n">
+      <c r="M36" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="M36" s="12" t="n">
+      <c r="N36" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="N36" s="2" t="inlineStr">
+      <c r="O36" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2216,42 +2362,47 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E37" s="12" t="n">
+      <c r="F37" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="F37" s="12" t="n">
+      <c r="G37" s="12" t="n">
         <v>99</v>
       </c>
-      <c r="G37" s="12" t="n">
+      <c r="H37" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="H37" s="12" t="n">
+      <c r="I37" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="I37" s="12" t="n">
+      <c r="J37" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J37" s="12" t="n">
+      <c r="K37" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K37" s="12" t="n">
+      <c r="L37" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="L37" s="12" t="n">
+      <c r="M37" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M37" s="12" t="n">
+      <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N37" s="2" t="inlineStr">
+      <c r="O37" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2270,42 +2421,47 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E38" s="12" t="n">
+      <c r="F38" s="12" t="n">
         <v>103</v>
       </c>
-      <c r="F38" s="12" t="n">
+      <c r="G38" s="12" t="n">
         <v>94</v>
       </c>
-      <c r="G38" s="12" t="n">
+      <c r="H38" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="H38" s="12" t="n">
+      <c r="I38" s="12" t="n">
         <v>75</v>
       </c>
-      <c r="I38" s="12" t="n">
+      <c r="J38" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="J38" s="12" t="n">
+      <c r="K38" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="K38" s="12" t="n">
+      <c r="L38" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="L38" s="12" t="n">
+      <c r="M38" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="M38" s="12" t="n">
+      <c r="N38" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="N38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2324,42 +2480,47 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
           <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
-      <c r="E39" s="12" t="n">
+      <c r="F39" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="F39" s="12" t="n">
+      <c r="G39" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="G39" s="12" t="n">
+      <c r="H39" s="12" t="n">
         <v>45</v>
       </c>
-      <c r="H39" s="12" t="n">
+      <c r="I39" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I39" s="12" t="n">
+      <c r="J39" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="J39" s="12" t="n">
+      <c r="K39" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="K39" s="12" t="n">
+      <c r="L39" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="L39" s="12" t="n">
+      <c r="M39" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="M39" s="12" t="n">
+      <c r="N39" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N39" s="2" t="inlineStr">
+      <c r="O39" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2378,42 +2539,47 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E40" s="12" t="n">
+      <c r="F40" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="F40" s="12" t="n">
+      <c r="G40" s="12" t="n">
         <v>133</v>
       </c>
-      <c r="G40" s="12" t="n">
+      <c r="H40" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H40" s="12" t="n">
+      <c r="I40" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="I40" s="12" t="n">
+      <c r="J40" s="12" t="n">
         <v>82</v>
       </c>
-      <c r="J40" s="12" t="n">
+      <c r="K40" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K40" s="12" t="n">
+      <c r="L40" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L40" s="12" t="n">
+      <c r="M40" s="12" t="n">
         <v>119</v>
       </c>
-      <c r="M40" s="12" t="n">
+      <c r="N40" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N40" s="2" t="inlineStr">
+      <c r="O40" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2432,42 +2598,47 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E41" s="12" t="n">
+      <c r="F41" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="F41" s="12" t="n">
+      <c r="G41" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G41" s="12" t="n">
+      <c r="H41" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H41" s="12" t="n">
+      <c r="I41" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I41" s="12" t="n">
+      <c r="J41" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="J41" s="12" t="n">
+      <c r="K41" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K41" s="12" t="n">
+      <c r="L41" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="L41" s="12" t="n">
+      <c r="M41" s="12" t="n">
         <v>155</v>
       </c>
-      <c r="M41" s="12" t="n">
+      <c r="N41" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="N41" s="2" t="inlineStr">
+      <c r="O41" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2486,42 +2657,47 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>CORSO FRANCIA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E42" s="12" t="n">
+      <c r="F42" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="F42" s="12" t="n">
+      <c r="G42" s="12" t="n">
         <v>101</v>
       </c>
-      <c r="G42" s="12" t="n">
+      <c r="H42" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H42" s="12" t="n">
+      <c r="I42" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="I42" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="J42" s="12" t="n">
+      <c r="K42" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K42" s="12" t="n">
+      <c r="L42" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L42" s="12" t="n">
+      <c r="M42" s="12" t="n">
         <v>250</v>
       </c>
-      <c r="M42" s="12" t="n">
+      <c r="N42" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N42" s="2" t="inlineStr">
+      <c r="O42" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2540,42 +2716,47 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
           <t>COLOZZA STEFANO</t>
         </is>
       </c>
-      <c r="E43" s="12" t="n">
+      <c r="F43" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="F43" s="12" t="n">
+      <c r="G43" s="12" t="n">
         <v>93</v>
       </c>
-      <c r="G43" s="12" t="n">
+      <c r="H43" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="H43" s="12" t="n">
+      <c r="I43" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="I43" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>53</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>24</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L43" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M43" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M43" s="12" t="n">
+      <c r="N43" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N43" s="2" t="inlineStr">
+      <c r="O43" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2594,42 +2775,47 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E44" s="12" t="n">
+      <c r="F44" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="F44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="12" t="n">
         <v>70</v>
       </c>
-      <c r="H44" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I44" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J44" s="12" t="n">
+      <c r="K44" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K44" s="12" t="n">
+      <c r="L44" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L44" s="12" t="n">
+      <c r="M44" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="M44" s="12" t="n">
+      <c r="N44" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="N44" s="2" t="inlineStr">
+      <c r="O44" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2648,42 +2834,47 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E45" s="12" t="n">
+      <c r="F45" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="F45" s="12" t="n">
+      <c r="G45" s="12" t="n">
         <v>117</v>
       </c>
-      <c r="G45" s="12" t="n">
+      <c r="H45" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H45" s="12" t="n">
+      <c r="I45" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I45" s="12" t="n">
+      <c r="J45" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="J45" s="12" t="n">
+      <c r="K45" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="K45" s="12" t="n">
+      <c r="L45" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L45" s="12" t="n">
+      <c r="M45" s="12" t="n">
         <v>153</v>
       </c>
-      <c r="M45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N45" s="2" t="inlineStr">
+      <c r="O45" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2702,42 +2893,47 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E46" s="12" t="n">
+      <c r="F46" s="12" t="n">
         <v>67</v>
       </c>
-      <c r="F46" s="12" t="n">
+      <c r="G46" s="12" t="n">
         <v>80</v>
       </c>
-      <c r="G46" s="12" t="n">
+      <c r="H46" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H46" s="12" t="n">
+      <c r="I46" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I46" s="12" t="n">
+      <c r="J46" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="J46" s="12" t="n">
+      <c r="K46" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="K46" s="12" t="n">
+      <c r="L46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L46" s="12" t="n">
+      <c r="M46" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="M46" s="12" t="n">
+      <c r="N46" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N46" s="2" t="inlineStr">
+      <c r="O46" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2756,42 +2952,47 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>TANGENZIALE OVEST N 15</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E47" s="12" t="n">
+      <c r="F47" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F47" s="12" t="n">
+      <c r="G47" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="G47" s="12" t="n">
+      <c r="H47" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H47" s="12" t="n">
+      <c r="I47" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I47" s="12" t="n">
+      <c r="J47" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J47" s="12" t="n">
+      <c r="K47" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K47" s="12" t="n">
+      <c r="L47" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L47" s="12" t="n">
+      <c r="M47" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="M47" s="12" t="n">
+      <c r="N47" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="N47" s="2" t="inlineStr">
+      <c r="O47" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2810,42 +3011,47 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E48" s="12" t="n">
+      <c r="F48" s="12" t="n">
         <v>65</v>
       </c>
-      <c r="F48" s="12" t="n">
+      <c r="G48" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G48" s="12" t="n">
+      <c r="H48" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H48" s="12" t="n">
+      <c r="I48" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="I48" s="12" t="n">
+      <c r="J48" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J48" s="12" t="n">
+      <c r="K48" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K48" s="12" t="n">
+      <c r="L48" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="L48" s="12" t="n">
+      <c r="M48" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="M48" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="2" t="inlineStr">
+      <c r="N48" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2864,42 +3070,47 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E49" s="12" t="n">
+      <c r="F49" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F49" s="12" t="n">
+      <c r="G49" s="12" t="n">
         <v>109</v>
       </c>
-      <c r="G49" s="12" t="n">
+      <c r="H49" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="H49" s="12" t="n">
+      <c r="I49" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="I49" s="12" t="n">
+      <c r="J49" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="J49" s="12" t="n">
+      <c r="K49" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K49" s="12" t="n">
+      <c r="L49" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="L49" s="12" t="n">
+      <c r="M49" s="12" t="n">
         <v>145</v>
       </c>
-      <c r="M49" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="2" t="inlineStr">
+      <c r="N49" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -2918,42 +3129,47 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
           <t>COLOZZA STEFANO</t>
         </is>
       </c>
-      <c r="E50" s="12" t="n">
+      <c r="F50" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="F50" s="12" t="n">
+      <c r="G50" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="G50" s="12" t="n">
+      <c r="H50" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H50" s="12" t="n">
+      <c r="I50" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I50" s="12" t="n">
+      <c r="J50" s="12" t="n">
         <v>46</v>
-      </c>
-      <c r="J50" s="12" t="n">
-        <v>17</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L50" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="M50" s="12" t="n">
         <v>129</v>
       </c>
-      <c r="M50" s="12" t="n">
+      <c r="N50" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N50" s="2" t="inlineStr">
+      <c r="O50" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -2972,42 +3188,47 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E51" s="12" t="n">
+      <c r="F51" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="F51" s="12" t="n">
+      <c r="G51" s="12" t="n">
         <v>61</v>
       </c>
-      <c r="G51" s="12" t="n">
+      <c r="H51" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="H51" s="12" t="n">
+      <c r="I51" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="I51" s="12" t="n">
+      <c r="J51" s="12" t="n">
         <v>54</v>
       </c>
-      <c r="J51" s="12" t="n">
+      <c r="K51" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="K51" s="12" t="n">
+      <c r="L51" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L51" s="12" t="n">
+      <c r="M51" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M51" s="12" t="n">
+      <c r="N51" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="N51" s="2" t="inlineStr">
+      <c r="O51" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3026,42 +3247,47 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
           <t>PROSPERI CHIARA</t>
         </is>
       </c>
-      <c r="E52" s="12" t="n">
+      <c r="F52" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F52" s="12" t="n">
+      <c r="G52" s="12" t="n">
         <v>66</v>
       </c>
-      <c r="G52" s="12" t="n">
+      <c r="H52" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H52" s="12" t="n">
+      <c r="I52" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="I52" s="12" t="n">
+      <c r="J52" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J52" s="12" t="n">
+      <c r="K52" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K52" s="12" t="n">
+      <c r="L52" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L52" s="12" t="n">
+      <c r="M52" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="M52" s="12" t="n">
+      <c r="N52" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N52" s="2" t="inlineStr">
+      <c r="O52" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3080,42 +3306,47 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E53" s="12" t="n">
+      <c r="F53" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="F53" s="12" t="n">
+      <c r="G53" s="12" t="n">
         <v>126</v>
       </c>
-      <c r="G53" s="12" t="n">
+      <c r="H53" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H53" s="12" t="n">
+      <c r="I53" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I53" s="12" t="n">
+      <c r="J53" s="12" t="n">
         <v>33</v>
       </c>
-      <c r="J53" s="12" t="n">
+      <c r="K53" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K53" s="12" t="n">
+      <c r="L53" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L53" s="12" t="n">
+      <c r="M53" s="12" t="n">
         <v>116</v>
       </c>
-      <c r="M53" s="12" t="n">
+      <c r="N53" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N53" s="2" t="inlineStr">
+      <c r="O53" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3134,42 +3365,47 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA CASILINA KM 104+320</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E54" s="12" t="n">
+      <c r="F54" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="F54" s="12" t="n">
+      <c r="G54" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G54" s="12" t="n">
+      <c r="H54" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="H54" s="12" t="n">
+      <c r="I54" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="I54" s="12" t="n">
+      <c r="J54" s="12" t="n">
         <v>40</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>11</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L54" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M54" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="M54" s="12" t="n">
+      <c r="N54" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N54" s="2" t="inlineStr">
+      <c r="O54" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3188,42 +3424,47 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E55" s="12" t="n">
+      <c r="F55" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="F55" s="12" t="n">
+      <c r="G55" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G55" s="12" t="n">
+      <c r="H55" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H55" s="12" t="n">
+      <c r="I55" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I55" s="12" t="n">
+      <c r="J55" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J55" s="12" t="n">
+      <c r="K55" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K55" s="12" t="n">
+      <c r="L55" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="L55" s="12" t="n">
+      <c r="M55" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="M55" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="2" t="inlineStr">
+      <c r="N55" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3242,42 +3483,47 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E56" s="12" t="n">
+      <c r="F56" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="F56" s="12" t="n">
+      <c r="G56" s="12" t="n">
         <v>69</v>
       </c>
-      <c r="G56" s="12" t="n">
+      <c r="H56" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="H56" s="12" t="n">
+      <c r="I56" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="I56" s="12" t="n">
+      <c r="J56" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J56" s="12" t="n">
+      <c r="K56" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="K56" s="12" t="n">
+      <c r="L56" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L56" s="12" t="n">
+      <c r="M56" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="M56" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="2" t="inlineStr">
+      <c r="N56" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3296,42 +3542,47 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E57" s="12" t="n">
+      <c r="F57" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F57" s="12" t="n">
+      <c r="G57" s="12" t="n">
         <v>56</v>
       </c>
-      <c r="G57" s="12" t="n">
+      <c r="H57" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="H57" s="12" t="n">
+      <c r="I57" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I57" s="12" t="n">
+      <c r="J57" s="12" t="n">
         <v>44</v>
       </c>
-      <c r="J57" s="12" t="n">
+      <c r="K57" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K57" s="12" t="n">
+      <c r="L57" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L57" s="12" t="n">
+      <c r="M57" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M57" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="2" t="inlineStr">
+      <c r="N57" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3350,42 +3601,47 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E58" s="12" t="n">
+      <c r="F58" s="12" t="n">
         <v>49</v>
       </c>
-      <c r="F58" s="12" t="n">
+      <c r="G58" s="12" t="n">
         <v>87</v>
       </c>
-      <c r="G58" s="12" t="n">
+      <c r="H58" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H58" s="12" t="n">
+      <c r="I58" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I58" s="12" t="n">
+      <c r="J58" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J58" s="12" t="n">
+      <c r="K58" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K58" s="12" t="n">
+      <c r="L58" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="L58" s="12" t="n">
+      <c r="M58" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="M58" s="12" t="n">
+      <c r="N58" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N58" s="2" t="inlineStr">
+      <c r="O58" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3404,42 +3660,47 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E59" s="12" t="n">
+      <c r="F59" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="F59" s="12" t="n">
+      <c r="G59" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="G59" s="12" t="n">
+      <c r="H59" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="H59" s="12" t="n">
+      <c r="I59" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I59" s="12" t="n">
+      <c r="J59" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="J59" s="12" t="n">
+      <c r="K59" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="K59" s="12" t="n">
+      <c r="L59" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L59" s="12" t="n">
+      <c r="M59" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="M59" s="12" t="n">
+      <c r="N59" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N59" s="2" t="inlineStr">
+      <c r="O59" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3458,42 +3719,47 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E60" s="12" t="n">
+      <c r="F60" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="F60" s="12" t="n">
+      <c r="G60" s="12" t="n">
         <v>98</v>
       </c>
-      <c r="G60" s="12" t="n">
+      <c r="H60" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="H60" s="12" t="n">
+      <c r="I60" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I60" s="12" t="n">
+      <c r="J60" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J60" s="12" t="n">
+      <c r="K60" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K60" s="12" t="n">
+      <c r="L60" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L60" s="12" t="n">
+      <c r="M60" s="12" t="n">
         <v>177</v>
       </c>
-      <c r="M60" s="12" t="n">
+      <c r="N60" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N60" s="2" t="inlineStr">
+      <c r="O60" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3512,42 +3778,47 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E61" s="12" t="n">
+      <c r="F61" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="F61" s="12" t="n">
+      <c r="G61" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="G61" s="12" t="n">
+      <c r="H61" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H61" s="12" t="n">
+      <c r="I61" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I61" s="12" t="n">
+      <c r="J61" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J61" s="12" t="n">
+      <c r="K61" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="K61" s="12" t="n">
+      <c r="L61" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L61" s="12" t="n">
+      <c r="M61" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="M61" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="2" t="inlineStr">
+      <c r="N61" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3566,42 +3837,47 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
-      <c r="E62" s="12" t="n">
+      <c r="F62" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="F62" s="12" t="n">
+      <c r="G62" s="12" t="n">
         <v>74</v>
       </c>
-      <c r="G62" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I62" s="12" t="n">
+      <c r="J62" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="J62" s="12" t="n">
+      <c r="K62" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="K62" s="12" t="n">
+      <c r="L62" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L62" s="12" t="n">
+      <c r="M62" s="12" t="n">
         <v>50</v>
       </c>
-      <c r="M62" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="2" t="inlineStr">
+      <c r="N62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3620,42 +3896,47 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E63" s="12" t="n">
+      <c r="F63" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="F63" s="12" t="n">
+      <c r="G63" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="G63" s="12" t="n">
+      <c r="H63" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H63" s="12" t="n">
+      <c r="I63" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I63" s="12" t="n">
+      <c r="J63" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J63" s="12" t="n">
+      <c r="K63" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K63" s="12" t="n">
+      <c r="L63" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L63" s="12" t="n">
+      <c r="M63" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="M63" s="12" t="n">
+      <c r="N63" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="N63" s="2" t="inlineStr">
+      <c r="O63" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3674,42 +3955,47 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
           <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
-      <c r="E64" s="12" t="n">
+      <c r="F64" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F64" s="12" t="n">
+      <c r="G64" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G64" s="12" t="n">
+      <c r="H64" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H64" s="12" t="n">
+      <c r="I64" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I64" s="12" t="n">
+      <c r="J64" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="J64" s="12" t="n">
+      <c r="K64" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="K64" s="12" t="n">
+      <c r="L64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L64" s="12" t="n">
+      <c r="M64" s="12" t="n">
         <v>183</v>
       </c>
-      <c r="M64" s="12" t="n">
+      <c r="N64" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N64" s="2" t="inlineStr">
+      <c r="O64" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -3728,42 +4014,47 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E65" s="12" t="n">
+      <c r="F65" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="F65" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="H65" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I65" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="J65" s="12" t="n">
+      <c r="K65" s="12" t="n">
         <v>17</v>
       </c>
-      <c r="K65" s="12" t="n">
+      <c r="L65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L65" s="12" t="n">
+      <c r="M65" s="12" t="n">
         <v>58</v>
       </c>
-      <c r="M65" s="12" t="n">
+      <c r="N65" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N65" s="2" t="inlineStr">
+      <c r="O65" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3782,42 +4073,47 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E66" s="12" t="n">
+      <c r="F66" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="F66" s="12" t="n">
+      <c r="G66" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G66" s="12" t="n">
+      <c r="H66" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H66" s="12" t="n">
+      <c r="I66" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="I66" s="12" t="n">
+      <c r="J66" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="J66" s="12" t="n">
+      <c r="K66" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K66" s="12" t="n">
+      <c r="L66" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L66" s="12" t="n">
+      <c r="M66" s="12" t="n">
         <v>104</v>
       </c>
-      <c r="M66" s="12" t="n">
+      <c r="N66" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N66" s="2" t="inlineStr">
+      <c r="O66" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3836,42 +4132,47 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
           <t>ERANDO FABIO</t>
         </is>
       </c>
-      <c r="E67" s="12" t="n">
+      <c r="F67" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F67" s="12" t="n">
+      <c r="G67" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="G67" s="12" t="n">
+      <c r="H67" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H67" s="12" t="n">
+      <c r="I67" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I67" s="12" t="n">
+      <c r="J67" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="J67" s="12" t="n">
+      <c r="K67" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="K67" s="12" t="n">
+      <c r="L67" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L67" s="12" t="n">
+      <c r="M67" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="M67" s="12" t="n">
+      <c r="N67" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N67" s="2" t="inlineStr">
+      <c r="O67" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -3890,42 +4191,47 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E68" s="12" t="n">
+      <c r="F68" s="12" t="n">
         <v>36</v>
       </c>
-      <c r="F68" s="12" t="n">
+      <c r="G68" s="12" t="n">
         <v>47</v>
       </c>
-      <c r="G68" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H68" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I68" s="12" t="n">
+      <c r="J68" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J68" s="12" t="n">
+      <c r="K68" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K68" s="12" t="n">
+      <c r="L68" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="L68" s="12" t="n">
+      <c r="M68" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="M68" s="12" t="n">
+      <c r="N68" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N68" s="2" t="inlineStr">
+      <c r="O68" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3944,42 +4250,47 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E69" s="12" t="n">
+      <c r="F69" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F69" s="12" t="n">
+      <c r="G69" s="12" t="n">
         <v>76</v>
       </c>
-      <c r="G69" s="12" t="n">
+      <c r="H69" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H69" s="12" t="n">
+      <c r="I69" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I69" s="12" t="n">
+      <c r="J69" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J69" s="12" t="n">
+      <c r="K69" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="K69" s="12" t="n">
+      <c r="L69" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L69" s="12" t="n">
+      <c r="M69" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M69" s="12" t="n">
+      <c r="N69" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N69" s="2" t="inlineStr">
+      <c r="O69" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -3998,42 +4309,47 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E70" s="12" t="n">
+      <c r="F70" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="F70" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H70" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J70" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="J70" s="12" t="n">
+      <c r="K70" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K70" s="12" t="n">
+      <c r="L70" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L70" s="12" t="n">
+      <c r="M70" s="12" t="n">
         <v>43</v>
       </c>
-      <c r="M70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="2" t="inlineStr">
+      <c r="N70" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4052,42 +4368,47 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E71" s="12" t="n">
+      <c r="F71" s="12" t="n">
         <v>31</v>
       </c>
-      <c r="F71" s="12" t="n">
+      <c r="G71" s="12" t="n">
         <v>73</v>
       </c>
-      <c r="G71" s="12" t="n">
+      <c r="H71" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H71" s="12" t="n">
+      <c r="I71" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I71" s="12" t="n">
+      <c r="J71" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J71" s="12" t="n">
+      <c r="K71" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="K71" s="12" t="n">
+      <c r="L71" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L71" s="12" t="n">
+      <c r="M71" s="12" t="n">
         <v>79</v>
       </c>
-      <c r="M71" s="12" t="n">
+      <c r="N71" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N71" s="2" t="inlineStr">
+      <c r="O71" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4106,42 +4427,47 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
           <t>CHIODI ROBERTO</t>
         </is>
       </c>
-      <c r="E72" s="12" t="n">
+      <c r="F72" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="F72" s="12" t="n">
+      <c r="G72" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="G72" s="12" t="n">
+      <c r="H72" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="H72" s="12" t="n">
+      <c r="I72" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="I72" s="12" t="n">
+      <c r="J72" s="12" t="n">
         <v>21</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L72" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M72" s="12" t="n">
         <v>81</v>
       </c>
-      <c r="M72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N72" s="2" t="inlineStr">
+      <c r="N72" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4160,42 +4486,47 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
-      <c r="E73" s="12" t="n">
+      <c r="F73" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="F73" s="12" t="n">
+      <c r="G73" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="G73" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I73" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J73" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="J73" s="12" t="n">
+      <c r="K73" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K73" s="12" t="n">
+      <c r="L73" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L73" s="12" t="n">
+      <c r="M73" s="12" t="n">
         <v>59</v>
       </c>
-      <c r="M73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N73" s="2" t="inlineStr">
+      <c r="N73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4214,42 +4545,47 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E74" s="12" t="n">
+      <c r="F74" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F74" s="12" t="n">
+      <c r="G74" s="12" t="n">
         <v>55</v>
       </c>
-      <c r="G74" s="12" t="n">
+      <c r="H74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H74" s="12" t="n">
+      <c r="I74" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I74" s="12" t="n">
+      <c r="J74" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="J74" s="12" t="n">
+      <c r="K74" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="K74" s="12" t="n">
+      <c r="L74" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L74" s="12" t="n">
+      <c r="M74" s="12" t="n">
         <v>114</v>
       </c>
-      <c r="M74" s="12" t="n">
+      <c r="N74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N74" s="2" t="inlineStr">
+      <c r="O74" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4268,20 +4604,22 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E75" s="12" t="n">
+      <c r="F75" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="F75" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
       </c>
@@ -4289,21 +4627,24 @@
         <v>0</v>
       </c>
       <c r="I75" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J75" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="J75" s="12" t="n">
+      <c r="K75" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K75" s="12" t="n">
+      <c r="L75" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L75" s="12" t="n">
+      <c r="M75" s="12" t="n">
         <v>64</v>
       </c>
-      <c r="M75" s="12" t="n">
+      <c r="N75" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N75" s="2" t="inlineStr">
+      <c r="O75" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4322,42 +4663,47 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E76" s="12" t="n">
+      <c r="F76" s="12" t="n">
         <v>27</v>
       </c>
-      <c r="F76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="H76" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I76" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J76" s="12" t="n">
         <v>25</v>
       </c>
-      <c r="J76" s="12" t="n">
+      <c r="K76" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="K76" s="12" t="n">
+      <c r="L76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L76" s="12" t="n">
+      <c r="M76" s="12" t="n">
         <v>51</v>
       </c>
-      <c r="M76" s="12" t="n">
+      <c r="N76" s="12" t="n">
         <v>22</v>
       </c>
-      <c r="N76" s="2" t="inlineStr">
+      <c r="O76" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4376,42 +4722,47 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
           <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
-      <c r="E77" s="12" t="n">
+      <c r="F77" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="F77" s="12" t="n">
+      <c r="G77" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="G77" s="12" t="n">
+      <c r="H77" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H77" s="12" t="n">
+      <c r="I77" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I77" s="12" t="n">
+      <c r="J77" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J77" s="12" t="n">
+      <c r="K77" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K77" s="12" t="n">
+      <c r="L77" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="L77" s="12" t="n">
+      <c r="M77" s="12" t="n">
         <v>52</v>
       </c>
-      <c r="M77" s="12" t="n">
+      <c r="N77" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="N77" s="2" t="inlineStr">
+      <c r="O77" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4430,42 +4781,47 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
           <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
-      <c r="E78" s="12" t="n">
+      <c r="F78" s="12" t="n">
         <v>20</v>
       </c>
-      <c r="F78" s="12" t="n">
+      <c r="G78" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="G78" s="12" t="n">
+      <c r="H78" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="H78" s="12" t="n">
+      <c r="I78" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I78" s="12" t="n">
+      <c r="J78" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J78" s="12" t="n">
+      <c r="K78" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K78" s="12" t="n">
+      <c r="L78" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L78" s="12" t="n">
+      <c r="M78" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="M78" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N78" s="2" t="inlineStr">
+      <c r="N78" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4484,42 +4840,47 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E79" s="12" t="n">
+      <c r="F79" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="F79" s="12" t="n">
+      <c r="G79" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G79" s="12" t="n">
+      <c r="H79" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="H79" s="12" t="n">
+      <c r="I79" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I79" s="12" t="n">
+      <c r="J79" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="J79" s="12" t="n">
+      <c r="K79" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K79" s="12" t="n">
+      <c r="L79" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L79" s="12" t="n">
+      <c r="M79" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="M79" s="12" t="n">
+      <c r="N79" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="N79" s="2" t="inlineStr">
+      <c r="O79" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4538,42 +4899,47 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
           <t>CASCIANI GABRIELE</t>
         </is>
       </c>
-      <c r="E80" s="12" t="n">
+      <c r="F80" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="F80" s="12" t="n">
+      <c r="G80" s="12" t="n">
         <v>32</v>
-      </c>
-      <c r="G80" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I80" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J80" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J80" s="12" t="n">
+      <c r="K80" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K80" s="12" t="n">
+      <c r="L80" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L80" s="12" t="n">
+      <c r="M80" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="M80" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N80" s="2" t="inlineStr">
+      <c r="N80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4592,42 +4958,47 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E81" s="12" t="n">
+      <c r="F81" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="H81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J81" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="J81" s="12" t="n">
+      <c r="K81" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="K81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L81" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M81" s="12" t="n">
         <v>48</v>
       </c>
-      <c r="M81" s="12" t="n">
+      <c r="N81" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="N81" s="2" t="inlineStr">
+      <c r="O81" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4646,42 +5017,47 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
           <t>LEUCCI ANTONIO</t>
         </is>
       </c>
-      <c r="E82" s="12" t="n">
+      <c r="F82" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="F82" s="12" t="n">
+      <c r="G82" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="G82" s="12" t="n">
+      <c r="H82" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H82" s="12" t="n">
+      <c r="I82" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="I82" s="12" t="n">
+      <c r="J82" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="J82" s="12" t="n">
+      <c r="K82" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K82" s="12" t="n">
+      <c r="L82" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L82" s="12" t="n">
+      <c r="M82" s="12" t="n">
         <v>32</v>
       </c>
-      <c r="M82" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" s="2" t="inlineStr">
+      <c r="N82" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4700,42 +5076,47 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
           <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
-      <c r="E83" s="12" t="n">
+      <c r="F83" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F83" s="12" t="n">
+      <c r="G83" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G83" s="12" t="n">
+      <c r="H83" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="H83" s="12" t="n">
+      <c r="I83" s="12" t="n">
         <v>46</v>
       </c>
-      <c r="I83" s="12" t="n">
+      <c r="J83" s="12" t="n">
         <v>23</v>
       </c>
-      <c r="J83" s="12" t="n">
+      <c r="K83" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="K83" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="12" t="n">
         <v>91</v>
       </c>
-      <c r="M83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="2" t="inlineStr">
+      <c r="N83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
         <is>
           <t>Male</t>
         </is>
@@ -4754,42 +5135,47 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
           <t>PACI CLAUDIO</t>
         </is>
       </c>
-      <c r="E84" s="12" t="n">
+      <c r="F84" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="F84" s="12" t="n">
+      <c r="G84" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G84" s="12" t="n">
+      <c r="H84" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H84" s="12" t="n">
+      <c r="I84" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I84" s="12" t="n">
+      <c r="J84" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L84" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L84" s="12" t="n">
+      <c r="M84" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N84" s="2" t="inlineStr">
+      <c r="N84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4808,42 +5194,47 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
           <t>LEUCCI ANTONIO</t>
         </is>
       </c>
-      <c r="E85" s="12" t="n">
+      <c r="F85" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J85" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="J85" s="12" t="n">
+      <c r="K85" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K85" s="12" t="n">
+      <c r="L85" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L85" s="12" t="n">
+      <c r="M85" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="M85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" s="2" t="inlineStr">
+      <c r="N85" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4862,42 +5253,47 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA FLAMINIA KM. 29,700 SNC</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
           <t>DELLA ROSA FABIO</t>
         </is>
       </c>
-      <c r="E86" s="12" t="n">
+      <c r="F86" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J86" s="12" t="n">
+      <c r="K86" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="K86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M86" s="12" t="n">
         <v>16</v>
       </c>
-      <c r="M86" s="12" t="n">
+      <c r="N86" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="N86" s="2" t="inlineStr">
+      <c r="O86" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -4916,20 +5312,22 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
           <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
-      <c r="E87" s="12" t="n">
+      <c r="F87" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="F87" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G87" s="12" t="n">
         <v>0</v>
       </c>
@@ -4937,21 +5335,24 @@
         <v>0</v>
       </c>
       <c r="I87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J87" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J87" s="12" t="n">
+      <c r="K87" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K87" s="12" t="n">
+      <c r="L87" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="L87" s="12" t="n">
+      <c r="M87" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="M87" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N87" s="2" t="inlineStr">
+      <c r="N87" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -4970,42 +5371,47 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA G. ROSSA</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
           <t>CAIMMI ANDREA</t>
         </is>
       </c>
-      <c r="E88" s="12" t="n">
+      <c r="F88" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="F88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="H88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J88" s="12" t="n">
+      <c r="K88" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K88" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="N88" s="2" t="inlineStr">
+      <c r="N88" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -5024,42 +5430,47 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>S.S.TIBURTINA VALERIA KM. 68+300</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
           <t>PACI CLAUDIO</t>
         </is>
       </c>
-      <c r="E89" s="12" t="n">
+      <c r="F89" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="F89" s="12" t="n">
+      <c r="G89" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="G89" s="12" t="n">
+      <c r="H89" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H89" s="12" t="n">
+      <c r="I89" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I89" s="12" t="n">
+      <c r="J89" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="J89" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L89" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M89" s="12" t="n">
         <v>29</v>
       </c>
-      <c r="M89" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N89" s="2" t="inlineStr">
+      <c r="N89" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -5078,20 +5489,22 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA APPIA KM 24,600 SNC 0012</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E90" s="12" t="n">
+      <c r="F90" s="12" t="n">
         <v>9</v>
       </c>
-      <c r="F90" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G90" s="12" t="n">
         <v>0</v>
       </c>
@@ -5099,21 +5512,24 @@
         <v>0</v>
       </c>
       <c r="I90" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J90" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J90" s="12" t="n">
+      <c r="K90" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="K90" s="12" t="n">
+      <c r="L90" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L90" s="12" t="n">
+      <c r="M90" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="M90" s="12" t="n">
+      <c r="N90" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N90" s="2" t="inlineStr">
+      <c r="O90" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -5132,20 +5548,22 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA ARDEATINA</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
           <t>MARIANI MARIO</t>
         </is>
       </c>
-      <c r="E91" s="12" t="n">
+      <c r="F91" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F91" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G91" s="12" t="n">
         <v>0</v>
       </c>
@@ -5153,21 +5571,24 @@
         <v>0</v>
       </c>
       <c r="I91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J91" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J91" s="12" t="n">
+      <c r="K91" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="K91" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M91" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="M91" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N91" s="2" t="inlineStr">
+      <c r="N91" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -5186,42 +5607,47 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>FRAZ-MARINELLE</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
           <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
-      <c r="E92" s="12" t="n">
+      <c r="F92" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="F92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J92" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="J92" s="12" t="n">
+      <c r="K92" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K92" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M92" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M92" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N92" s="2" t="inlineStr">
+      <c r="N92" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5240,42 +5666,47 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA DELLA MAGLIANA 242</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E93" s="12" t="n">
+      <c r="F93" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="F93" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H93" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J93" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J93" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K93" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L93" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="L93" s="12" t="n">
+      <c r="M93" s="12" t="n">
         <v>34</v>
       </c>
-      <c r="M93" s="12" t="n">
+      <c r="N93" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="N93" s="2" t="inlineStr">
+      <c r="O93" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>
@@ -5294,20 +5725,22 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA FLAMINIA</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E94" s="12" t="n">
+      <c r="F94" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="F94" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G94" s="12" t="n">
         <v>0</v>
       </c>
@@ -5315,21 +5748,24 @@
         <v>0</v>
       </c>
       <c r="I94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J94" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J94" s="12" t="n">
+      <c r="K94" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="K94" s="12" t="n">
+      <c r="L94" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="L94" s="12" t="n">
+      <c r="M94" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="M94" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N94" s="2" t="inlineStr">
+      <c r="N94" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -5348,42 +5784,47 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>SS 16 ADRIATICA KM 237+192 S.N.</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
           <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
-      <c r="E95" s="12" t="n">
+      <c r="F95" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="F95" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="G95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H95" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="I95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J95" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="J95" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="K95" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L95" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" s="12" t="n">
         <v>10</v>
       </c>
-      <c r="M95" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N95" s="2" t="inlineStr">
+      <c r="N95" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
         <is>
           <t>Bene</t>
         </is>
@@ -5402,42 +5843,47 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Marcelli Mirko</t>
+          <t>VIA OSTIENSE 333</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
         <is>
+          <t>Marcelli Mirko</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
           <t>LESTI LEONARDO</t>
         </is>
       </c>
-      <c r="E96" s="12" t="n">
+      <c r="F96" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="F96" s="12" t="n">
+      <c r="G96" s="12" t="n">
         <v>21</v>
       </c>
-      <c r="G96" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="H96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I96" s="12" t="n">
+      <c r="J96" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="J96" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="K96" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M96" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M96" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N96" s="2" t="inlineStr">
+      <c r="N96" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
         <is>
           <t>Da seguire</t>
         </is>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W18</t>
+          <t>W19</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7020</v>
+        <v>7285</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5280</v>
+        <v>5485</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1690</v>
+        <v>1791</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>413</v>
+        <v>426</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>553</v>
+        <v>577</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>318</v>
+        <v>331</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="L11" s="12" t="n">
         <v>97</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>617</v>
+        <v>649</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>455</v>
+        <v>471</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>403</v>
+        <v>420</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>265</v>
+        <v>282</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>289</v>
+        <v>313</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>488</v>
+        <v>520</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>434</v>
+        <v>464</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ORTONA</t>
+          <t>CITTÀ SANT'ANGELO</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>CONTRADA S. LIBERATA SS 16</t>
+          <t>VIA XXII MAGGIO 1944</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,56 +1015,56 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>308</v>
+        <v>223</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>178</v>
+        <v>157</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>79</v>
+        <v>54</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>62</v>
+        <v>96</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>177</v>
+        <v>192</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>87</v>
+        <v>36</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>CITTÀ SANT'ANGELO</t>
+          <t>ORTONA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>VIA XXII MAGGIO 1944</t>
+          <t>CONTRADA S. LIBERATA SS 16</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,39 +1074,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>219</v>
+        <v>314</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>40</v>
+        <v>49</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>49</v>
+        <v>80</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>90</v>
+        <v>62</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="H16" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I16" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="I16" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="J16" s="12" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>50</v>
@@ -1158,14 +1158,14 @@
         <v>60</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>266</v>
+        <v>280</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,35 +1314,35 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>108</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>180</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1373,31 +1373,31 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA DI ACILIA</t>
+          <t>VIA CASILINA KM. 24+950</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,56 +1428,56 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>141</v>
+        <v>248</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>8</v>
+        <v>34</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>22</v>
+        <v>65</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>207</v>
+        <v>270</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>160</v>
+        <v>3</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM. 24+950</t>
+          <t>VIA DI ACILIA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,39 +1487,39 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>235</v>
+        <v>153</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>64</v>
+        <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>257</v>
+        <v>215</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>3</v>
+        <v>160</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>41</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1609,19 +1609,19 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>34</v>
@@ -1630,14 +1630,14 @@
         <v>22</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>224</v>
+        <v>236</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="G25" s="12" t="n">
+        <v>199</v>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="I25" s="12" t="n">
+        <v>126</v>
+      </c>
+      <c r="J25" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="K25" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L25" s="12" t="n">
+        <v>44</v>
+      </c>
+      <c r="M25" s="12" t="n">
         <v>192</v>
-      </c>
-      <c r="H25" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="I25" s="12" t="n">
-        <v>122</v>
-      </c>
-      <c r="J25" s="12" t="n">
-        <v>109</v>
-      </c>
-      <c r="K25" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="L25" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="M25" s="12" t="n">
-        <v>186</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>5</v>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>136</v>
+        <v>146</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>0</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>13</v>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
+          <t>S.S.4 DIR. KM. 3 + 400</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,35 +1959,35 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>141</v>
+        <v>45</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>66</v>
+        <v>94</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>18</v>
+        <v>47</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>4</v>
+        <v>45</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 DIR. KM. 3 + 400</t>
+          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2018,39 +2018,39 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>89</v>
+        <v>67</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>30</v>
+        <v>56</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2081,31 +2081,31 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="H32" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>90</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>10</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CORSO MAZZINI</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,35 +2195,35 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>143</v>
+        <v>134</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>68</v>
+        <v>34</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>92</v>
+        <v>124</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
@@ -2234,17 +2234,17 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,35 +2254,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>126</v>
+        <v>145</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>73</v>
+        <v>93</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2317,31 +2317,31 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>137</v>
+        <v>147</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,35 +2376,35 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
+        <v>109</v>
+      </c>
+      <c r="G37" s="12" t="n">
         <v>106</v>
-      </c>
-      <c r="G37" s="12" t="n">
-        <v>99</v>
       </c>
       <c r="H37" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2435,25 +2435,25 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>47</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>36</v>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA P. SORIANO</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,35 +2490,35 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>45</v>
+        <v>28</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>153</v>
+        <v>125</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,35 +2549,35 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>98</v>
+        <v>103</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="H40" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="I40" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="J40" s="12" t="n">
+        <v>69</v>
+      </c>
+      <c r="K40" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I40" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="J40" s="12" t="n">
-        <v>82</v>
-      </c>
-      <c r="K40" s="12" t="n">
-        <v>35</v>
-      </c>
       <c r="L40" s="12" t="n">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>119</v>
+        <v>161</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
@@ -2612,19 +2612,19 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="K41" s="12" t="n">
         <v>19</v>
@@ -2633,7 +2633,7 @@
         <v>46</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2647,17 +2647,17 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>CORSO FRANCIA</t>
+          <t>IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>53</v>
+        <v>10</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>77</v>
+        <v>62</v>
       </c>
       <c r="K42" s="12" t="n">
+        <v>28</v>
+      </c>
+      <c r="L42" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>13</v>
-      </c>
       <c r="M42" s="12" t="n">
-        <v>250</v>
+        <v>52</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>IV NOVEMBRE</t>
+          <t>CORSO FRANCIA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>105</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>77</v>
-      </c>
-      <c r="G43" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>53</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>50</v>
+        <v>261</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,35 +2785,35 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>0</v>
+        <v>86</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>70</v>
+        <v>5</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>65</v>
+        <v>115</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,7 +2824,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,56 +2844,56 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="G45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="K45" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L45" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M45" s="12" t="n">
         <v>68</v>
       </c>
-      <c r="G45" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>19</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>61</v>
-      </c>
-      <c r="K45" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="L45" s="12" t="n">
+      <c r="N45" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="M45" s="12" t="n">
-        <v>153</v>
-      </c>
-      <c r="N45" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SS 80 KM 77+842</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>80</v>
+        <v>121</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>3</v>
+        <v>32</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>59</v>
+        <v>65</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="L46" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M46" s="12" t="n">
+        <v>159</v>
+      </c>
+      <c r="N46" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="M46" s="12" t="n">
-        <v>104</v>
-      </c>
-      <c r="N46" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2966,19 +2966,19 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>12</v>
@@ -2987,7 +2987,7 @@
         <v>24</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>6</v>
@@ -3001,17 +3001,17 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
         <v>65</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>85</v>
+        <v>39</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>31</v>
+        <v>4</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L48" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>69</v>
+        <v>139</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MONTAGNOLA N.24</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,32 +3080,32 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>109</v>
+        <v>92</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>81</v>
+        <v>34</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>145</v>
+        <v>71</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>0</v>
@@ -3119,17 +3119,17 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,39 +3139,39 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>36</v>
+        <v>112</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>129</v>
+        <v>154</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3202,52 +3202,52 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="H51" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>62</v>
+      </c>
+      <c r="J51" s="12" t="n">
         <v>57</v>
       </c>
-      <c r="I51" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>54</v>
-      </c>
       <c r="K51" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="L51" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>66</v>
+        <v>131</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>52</v>
+        <v>3</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>87</v>
+        <v>128</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>VIA CASILINA KM 104+320</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="I53" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M53" s="12" t="n">
+        <v>71</v>
+      </c>
+      <c r="N53" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J53" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>116</v>
-      </c>
-      <c r="N53" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 104+320</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>46</v>
+        <v>67</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>29</v>
+        <v>56</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>71</v>
+        <v>93</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3438,52 +3438,52 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>73</v>
+        <v>60</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>7</v>
+        <v>28</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>69</v>
+        <v>48</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="H56" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I56" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J56" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K56" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I56" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="J56" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="K56" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="L56" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,32 +3552,32 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>37</v>
+        <v>8</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>0</v>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>87</v>
+        <v>42</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,39 +3670,39 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>40</v>
+        <v>88</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I59" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J59" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="K59" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J59" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K59" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L59" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3736,13 +3736,13 @@
         <v>46</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J60" s="12" t="n">
         <v>38</v>
@@ -3754,7 +3754,7 @@
         <v>6</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>1</v>
@@ -3851,19 +3851,19 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K62" s="12" t="n">
         <v>13</v>
@@ -3872,7 +3872,7 @@
         <v>7</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>0</v>
@@ -3910,10 +3910,10 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="H63" s="12" t="n">
         <v>5</v>
@@ -3922,7 +3922,7 @@
         <v>2</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K63" s="12" t="n">
         <v>6</v>
@@ -3931,14 +3931,14 @@
         <v>13</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>8</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>13</v>
@@ -3987,24 +3987,24 @@
         <v>18</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -4014,7 +4014,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4028,52 +4028,52 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>38</v>
+        <v>20</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,56 +4083,56 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>104</v>
+        <v>61</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L67" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="M67" s="12" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="N67" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,56 +4201,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>73</v>
+        <v>105</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="G69" s="12" t="n">
+        <v>52</v>
+      </c>
+      <c r="H69" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I69" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J69" s="12" t="n">
         <v>35</v>
       </c>
-      <c r="G69" s="12" t="n">
-        <v>76</v>
-      </c>
-      <c r="H69" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="I69" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J69" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="K69" s="12" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>43</v>
+        <v>85</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4323,52 +4323,52 @@
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>76</v>
       </c>
       <c r="H70" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I70" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J70" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K70" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="I70" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="K70" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="L70" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>43</v>
+        <v>83</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,32 +4378,32 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>73</v>
+        <v>49</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>2</v>
@@ -4441,16 +4441,16 @@
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J72" s="12" t="n">
         <v>21</v>
@@ -4459,10 +4459,10 @@
         <v>8</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>0</v>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>45</v>
+        <v>56</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I73" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L73" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N73" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J73" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="N73" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,39 +4555,39 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
@@ -4630,7 +4630,7 @@
         <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>7</v>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4698,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>22</v>
@@ -4712,17 +4712,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,56 +4732,56 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>52</v>
+        <v>59</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,56 +4791,56 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>26</v>
+        <v>39</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>34</v>
+        <v>1</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>46</v>
+        <v>16</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>26</v>
+        <v>55</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,35 +4850,35 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>7</v>
+        <v>34</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>57</v>
+        <v>27</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
@@ -4889,17 +4889,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,56 +4909,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
         <v>18</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="K80" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,56 +4968,56 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>48</v>
+        <v>14</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
         <v>16</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>29</v>
+        <v>38</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>32</v>
+        <v>96</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
@@ -5066,17 +5066,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5086,56 +5086,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>91</v>
+        <v>50</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0</v>
@@ -5184,17 +5184,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>PRENESTINA EST</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5208,52 +5208,52 @@
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA KM. 29,700 SNC</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,35 +5263,35 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
         <v>14</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J86" s="12" t="n">
         <v>14</v>
       </c>
       <c r="K86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="L86" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L86" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M86" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
@@ -5302,17 +5302,17 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>PENNE</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>VIA G. ROSSA</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
@@ -5332,22 +5332,22 @@
         <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
@@ -5361,17 +5361,17 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>PENNE</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>VIA G. ROSSA</t>
+          <t>VIA FLAMINIA KM. 29,700 SNC</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5381,35 +5381,35 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5465,31 +5465,31 @@
         <v>3</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>55843</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>VIA APPIA KM 24,600 SNC 0012</t>
+          <t>VIA DELLA MAGLIANA 242</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
@@ -5509,22 +5509,22 @@
         <v>0</v>
       </c>
       <c r="H90" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="N90" s="12" t="n">
         <v>2</v>
@@ -5538,17 +5538,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>07164</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>VIA ARDEATINA</t>
+          <t>VIA APPIA KM 24,600 SNC 0012</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>0</v>
@@ -5574,19 +5574,19 @@
         <v>0</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N91" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
@@ -5597,17 +5597,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>06607</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>SAN SALVO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-MARINELLE</t>
+          <t>VIA ARDEATINA</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5617,7 +5617,7 @@
       </c>
       <c r="E92" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F92" s="12" t="n">
@@ -5627,7 +5627,7 @@
         <v>0</v>
       </c>
       <c r="H92" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I92" s="12" t="n">
         <v>0</v>
@@ -5636,37 +5636,37 @@
         <v>8</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="N92" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>55843</t>
+          <t>06607</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN SALVO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MAGLIANA 242</t>
+          <t>FRAZ-MARINELLE</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5676,11 +5676,11 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
@@ -5692,23 +5692,23 @@
         <v>0</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="N93" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W19</t>
+          <t>W20</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7285</v>
+        <v>7603</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5485</v>
+        <v>5711</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1791</v>
+        <v>1923</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>426</v>
+        <v>452</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>205</v>
+        <v>226</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>649</v>
+        <v>686</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>362</v>
+        <v>369</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>471</v>
+        <v>501</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>420</v>
+        <v>437</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>107</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>313</v>
+        <v>326</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>520</v>
+        <v>554</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>464</v>
+        <v>494</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -995,17 +995,17 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26869</t>
+          <t>26608</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>CITTÀ SANT'ANGELO</t>
+          <t>ORTONA</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>VIA XXII MAGGIO 1944</t>
+          <t>CONTRADA S. LIBERATA SS 16</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1015,56 +1015,56 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>251</v>
+        <v>263</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>223</v>
+        <v>332</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>104</v>
+        <v>47</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>157</v>
+        <v>193</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>54</v>
+        <v>86</v>
       </c>
       <c r="L14" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="M14" s="12" t="n">
+        <v>194</v>
+      </c>
+      <c r="N14" s="12" t="n">
         <v>96</v>
       </c>
-      <c r="M14" s="12" t="n">
-        <v>192</v>
-      </c>
-      <c r="N14" s="12" t="n">
-        <v>36</v>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>26608</t>
+          <t>26869</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>ORTONA</t>
+          <t>CITTÀ SANT'ANGELO</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>CONTRADA S. LIBERATA SS 16</t>
+          <t>VIA XXII MAGGIO 1944</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1074,39 +1074,39 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>314</v>
+        <v>229</v>
       </c>
       <c r="H15" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="I15" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="I15" s="12" t="n">
-        <v>49</v>
-      </c>
       <c r="J15" s="12" t="n">
-        <v>182</v>
+        <v>164</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>80</v>
+        <v>57</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>62</v>
+        <v>101</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>91</v>
+        <v>37</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1172,17 +1172,17 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>S.S.423 LOC.TORRACCIA</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,39 +1192,39 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>197</v>
+        <v>160</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>93</v>
+        <v>48</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>120</v>
+        <v>218</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>15</v>
+        <v>135</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>15</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>131</v>
+        <v>202</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>108</v>
+        <v>46</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>25</v>
+        <v>99</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>256</v>
+        <v>125</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>S.S.423 LOC.TORRACCIA</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>45</v>
+        <v>110</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>43</v>
+        <v>25</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>212</v>
+        <v>272</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>133</v>
+        <v>180</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>248</v>
+        <v>262</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>65</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>3</v>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>215</v>
+        <v>226</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>160</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1550,52 +1550,52 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CORSO DI FRANCIA 80</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>188</v>
+        <v>212</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>26</v>
+        <v>132</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>140</v>
+        <v>114</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>22</v>
+        <v>47</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>236</v>
+        <v>206</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA CARDUCCI</t>
+          <t>CORSO DI FRANCIA 80</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>112</v>
+        <v>141</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>192</v>
+        <v>247</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1727,28 +1727,28 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>171</v>
+        <v>188</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>25</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>5</v>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA SUD KM 140+200</t>
+          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>168</v>
+        <v>85</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>92</v>
+        <v>112</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>154</v>
+        <v>70</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
+          <t>VIA CASILINA SUD KM 140+200</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,39 +1841,39 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>82</v>
+        <v>176</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>37</v>
+        <v>56</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>65</v>
+        <v>162</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>13</v>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 DIR. KM. 3 + 400</t>
+          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1959,56 +1959,56 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>126</v>
+        <v>135</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>45</v>
+        <v>161</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>5</v>
+        <v>40</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>47</v>
+        <v>18</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>30</v>
+        <v>62</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
+          <t>S.S. 80 KM. 93 + 490</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>156</v>
+        <v>197</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>39</v>
+        <v>8</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>141</v>
+        <v>94</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>S.S. 80 KM. 93 + 490</t>
+          <t>S.S.4 DIR. KM. 3 + 400</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,39 +2077,39 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>190</v>
+        <v>51</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>67</v>
+        <v>96</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>25</v>
+        <v>45</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>124</v>
+        <v>136</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>10</v>
@@ -2199,28 +2199,28 @@
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="N34" s="12" t="n">
         <v>1</v>
@@ -2258,28 +2258,28 @@
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>145</v>
+        <v>154</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>2</v>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>74</v>
+        <v>48</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>147</v>
+        <v>89</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I37" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="J37" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="M37" s="12" t="n">
+        <v>157</v>
+      </c>
+      <c r="N37" s="12" t="n">
         <v>18</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K37" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>86</v>
-      </c>
-      <c r="N37" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2435,22 +2435,22 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="L38" s="12" t="n">
         <v>11</v>
@@ -2494,28 +2494,28 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>2</v>
@@ -2553,28 +2553,28 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>125</v>
+        <v>134</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="N40" s="12" t="n">
         <v>6</v>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>7</v>
@@ -2683,23 +2683,23 @@
         <v>10</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="K42" s="12" t="n">
+        <v>29</v>
+      </c>
+      <c r="L42" s="12" t="n">
         <v>28</v>
       </c>
-      <c r="L42" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="M42" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2730,19 +2730,19 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>24</v>
@@ -2751,10 +2751,10 @@
         <v>13</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>261</v>
+        <v>273</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>SS 80 KM 77+842</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,39 +2785,39 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>86</v>
+        <v>132</v>
       </c>
       <c r="H44" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="N44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>63</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>115</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2848,52 +2848,52 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2966,52 +2966,52 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="I47" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>39</v>
+        <v>115</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>4</v>
+        <v>94</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>139</v>
+        <v>164</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,56 +3080,56 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>17</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MONTAGNOLA N.24</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,32 +3139,32 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>112</v>
+        <v>95</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>87</v>
+        <v>40</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>154</v>
+        <v>76</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>0</v>
@@ -3205,13 +3205,13 @@
         <v>61</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="J51" s="12" t="n">
         <v>57</v>
@@ -3223,31 +3223,31 @@
         <v>2</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>VIA CASILINA KM 104+320</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>131</v>
+        <v>52</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="I52" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="J52" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="K52" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L52" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M52" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="N52" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="J52" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="K52" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="L52" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="M52" s="12" t="n">
-        <v>128</v>
-      </c>
-      <c r="N52" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 104+320</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>71</v>
+        <v>131</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,35 +3375,35 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>67</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>93</v>
+        <v>52</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,56 +3434,56 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="G55" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="H55" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I55" s="12" t="n">
         <v>60</v>
       </c>
-      <c r="H55" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="I55" s="12" t="n">
-        <v>42</v>
-      </c>
       <c r="J55" s="12" t="n">
-        <v>47</v>
+        <v>41</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>48</v>
+        <v>96</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,39 +3552,39 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="H57" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I57" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="J57" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="K57" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I57" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="J57" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="K57" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="L57" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3615,10 +3615,10 @@
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>8</v>
@@ -3627,23 +3627,23 @@
         <v>4</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L58" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>3</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3674,19 +3674,19 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>4</v>
@@ -3695,7 +3695,7 @@
         <v>31</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>1</v>
@@ -3733,31 +3733,31 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="H60" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L60" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>S.P. LEUCIANA KM 2+670</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="G61" s="12" t="n">
         <v>43</v>
       </c>
       <c r="H61" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I61" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="J61" s="12" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="L61" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M61" s="12" t="n">
+        <v>200</v>
+      </c>
+      <c r="N61" s="12" t="n">
         <v>2</v>
-      </c>
-      <c r="M61" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="N61" s="12" t="n">
-        <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>SS 430 KM 0.525</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3854,49 +3854,49 @@
         <v>42</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>78</v>
+        <v>43</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,56 +3906,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="M63" s="12" t="n">
         <v>56</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,35 +3965,35 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>47</v>
+        <v>27</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>192</v>
+        <v>59</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,39 +4024,39 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>0</v>
+        <v>83</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="K65" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L65" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L65" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="M65" s="12" t="n">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4087,7 +4087,7 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G66" s="12" t="n">
         <v>0</v>
@@ -4099,16 +4099,16 @@
         <v>0</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>1</v>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,39 +4142,39 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>78</v>
+        <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="K67" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L67" s="12" t="n">
         <v>11</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="M67" s="12" t="n">
         <v>44</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4208,13 +4208,13 @@
         <v>37</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="H68" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J68" s="12" t="n">
         <v>34</v>
@@ -4226,7 +4226,7 @@
         <v>6</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>1</v>
@@ -4267,7 +4267,7 @@
         <v>36</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>5</v>
@@ -4285,7 +4285,7 @@
         <v>4</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
@@ -4326,13 +4326,13 @@
         <v>36</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="H70" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>32</v>
@@ -4344,10 +4344,10 @@
         <v>6</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4403,7 +4403,7 @@
         <v>15</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>2</v>
@@ -4441,28 +4441,28 @@
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I72" s="12" t="n">
         <v>35</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K72" s="12" t="n">
         <v>8</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>0</v>
@@ -4500,10 +4500,10 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="H73" s="12" t="n">
         <v>1</v>
@@ -4512,16 +4512,16 @@
         <v>7</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K73" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="N73" s="12" t="n">
         <v>1</v>
@@ -4535,17 +4535,17 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K74" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="L74" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M74" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="N74" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="J74" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L74" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M74" s="12" t="n">
-        <v>65</v>
-      </c>
-      <c r="N74" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,39 +4614,39 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>30</v>
+        <v>21</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4677,19 +4677,19 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K76" s="12" t="n">
         <v>7</v>
@@ -4698,7 +4698,7 @@
         <v>1</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>22</v>
@@ -4712,17 +4712,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,56 +4732,56 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>22</v>
+        <v>42</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="I77" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J77" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J77" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="K77" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,39 +4791,39 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>39</v>
+        <v>24</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4854,19 +4854,19 @@
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K79" s="12" t="n">
         <v>1</v>
@@ -4875,7 +4875,7 @@
         <v>6</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
@@ -4913,52 +4913,52 @@
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L80" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,56 +4968,56 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>1</v>
+        <v>62</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>14</v>
+        <v>101</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,39 +5027,39 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>96</v>
+        <v>14</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5090,31 +5090,31 @@
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L83" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -5149,28 +5149,28 @@
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L84" s="12" t="n">
         <v>5</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0</v>
@@ -5184,17 +5184,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5204,56 +5204,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
         <v>16</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,39 +5263,39 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="N86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5347,14 +5347,14 @@
         <v>0</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
         <v>0</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="N88" s="12" t="n">
         <v>1</v>
@@ -5472,24 +5472,24 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>55843</t>
+          <t>06607</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN SALVO</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MAGLIANA 242</t>
+          <t>FRAZ-MARINELLE</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5499,7 +5499,7 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
@@ -5515,19 +5515,19 @@
         <v>0</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>1</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="N90" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
@@ -5538,17 +5538,17 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>55843</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>VIA APPIA KM 24,600 SNC 0012</t>
+          <t>VIA DELLA MAGLIANA 242</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5558,56 +5558,56 @@
       </c>
       <c r="E91" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F91" s="12" t="n">
         <v>9</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H91" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I91" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L91" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="N91" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>07164</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>VIA ARDEATINA</t>
+          <t>VIA APPIA KM 24,600 SNC 0012</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5621,7 +5621,7 @@
         </is>
       </c>
       <c r="F92" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G92" s="12" t="n">
         <v>0</v>
@@ -5633,19 +5633,19 @@
         <v>0</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N92" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5656,17 +5656,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>06607</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>SAN SALVO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-MARINELLE</t>
+          <t>VIA ARDEATINA</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="E93" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F93" s="12" t="n">
@@ -5686,7 +5686,7 @@
         <v>0</v>
       </c>
       <c r="H93" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I93" s="12" t="n">
         <v>0</v>
@@ -5695,13 +5695,13 @@
         <v>8</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L93" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="N93" s="12" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W20</t>
+          <t>W21</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>7603</v>
+        <v>8017</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>5711</v>
+        <v>6024</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>1923</v>
+        <v>2079</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>452</v>
+        <v>475</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>602</v>
+        <v>634</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>686</v>
+        <v>730</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>501</v>
+        <v>535</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>290</v>
+        <v>309</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>437</v>
+        <v>454</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>297</v>
+        <v>322</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>231</v>
+        <v>255</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>88</v>
+        <v>99</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>554</v>
+        <v>587</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>494</v>
+        <v>517</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>263</v>
+        <v>280</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="L15" s="12" t="n">
         <v>101</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>37</v>
@@ -1113,17 +1113,17 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>07171</t>
+          <t>06038</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>CIVITAVECCHIA</t>
+          <t>PESARO</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>S.S. AURELIA KM 68+885</t>
+          <t>S.S.423 LOC.TORRACCIA</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1133,56 +1133,56 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>226</v>
+        <v>175</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>153</v>
+        <v>177</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>52</v>
+        <v>83</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>296</v>
+        <v>241</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>36</v>
+        <v>145</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>06038</t>
+          <t>07171</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>PESARO</t>
+          <t>CIVITAVECCHIA</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>S.S.423 LOC.TORRACCIA</t>
+          <t>S.S. AURELIA KM 68+885</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1192,39 +1192,39 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>160</v>
+        <v>241</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>48</v>
+        <v>17</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>218</v>
+        <v>314</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>135</v>
+        <v>39</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>128</v>
+        <v>144</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>15</v>
@@ -1290,17 +1290,17 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,35 +1310,35 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>202</v>
+        <v>156</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>46</v>
+        <v>111</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>99</v>
+        <v>31</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>95</v>
+        <v>100</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>125</v>
+        <v>282</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>15</v>
+        <v>180</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>139</v>
+        <v>207</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>110</v>
+        <v>48</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>25</v>
+        <v>101</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>272</v>
+        <v>129</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>180</v>
+        <v>15</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1432,28 +1432,28 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>262</v>
+        <v>276</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>36</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>288</v>
+        <v>305</v>
       </c>
       <c r="N21" s="12" t="n">
         <v>3</v>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="G22" s="12" t="n">
+        <v>166</v>
+      </c>
+      <c r="H22" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="I22" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>159</v>
       </c>
-      <c r="H22" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="I22" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>154</v>
-      </c>
       <c r="K22" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,31 +1550,31 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>28</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA CARDUCCI</t>
+          <t>CORSO DI FRANCIA 80</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>132</v>
+        <v>28</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>114</v>
+        <v>147</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>206</v>
+        <v>263</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>CORSO DI FRANCIA 80</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1664,35 +1664,35 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>197</v>
+        <v>224</v>
       </c>
       <c r="H25" s="12" t="n">
         <v>44</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>27</v>
+        <v>142</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>141</v>
+        <v>117</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>247</v>
+        <v>219</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>11</v>
+        <v>2</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA E. MATTEI, 28</t>
+          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>156</v>
+        <v>165</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>188</v>
+        <v>91</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>100</v>
+        <v>123</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>195</v>
+        <v>84</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,39 +1782,39 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>154</v>
+        <v>163</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>85</v>
+        <v>196</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>70</v>
+        <v>204</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>151</v>
+        <v>156</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>9</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>24</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>162</v>
+        <v>172</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>7</v>
@@ -1904,28 +1904,28 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G29" s="12" t="n">
+        <v>196</v>
+      </c>
+      <c r="H29" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I29" s="12" t="n">
+        <v>56</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>117</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>39</v>
+      </c>
+      <c r="M29" s="12" t="n">
         <v>171</v>
-      </c>
-      <c r="H29" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I29" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>111</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>166</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>13</v>
@@ -1939,17 +1939,17 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>17314</t>
+          <t>27364</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>CORROPOLI</t>
+          <t>MOSCIANO SANT'ANGELO</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
+          <t>S.S. 80 KM. 93 + 490</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>161</v>
+        <v>207</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>148</v>
+        <v>99</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>4</v>
+        <v>26</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -1998,17 +1998,17 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>27364</t>
+          <t>17314</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>MOSCIANO SANT'ANGELO</t>
+          <t>CORROPOLI</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>S.S. 80 KM. 93 + 490</t>
+          <t>V.LE ADRIATICO 168 SS259 KM 1</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2022,31 +2022,31 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>8</v>
+        <v>45</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>94</v>
+        <v>152</v>
       </c>
       <c r="N31" s="12" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>45</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>94</v>
+        <v>151</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>97</v>
+        <v>26</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>136</v>
+        <v>38</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>140</v>
+        <v>102</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>22</v>
+        <v>97</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>35</v>
+        <v>146</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>131</v>
+        <v>61</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>CORSO MAZZINI</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,32 +2254,32 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>154</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>71</v>
+        <v>40</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="L35" s="12" t="n">
         <v>20</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>95</v>
+        <v>140</v>
       </c>
       <c r="N35" s="12" t="n">
         <v>2</v>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>108</v>
+        <v>162</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>18</v>
+        <v>77</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>48</v>
+        <v>100</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>89</v>
+        <v>98</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>91</v>
+        <v>118</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>79</v>
+        <v>48</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>33</v>
+        <v>74</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>157</v>
+        <v>96</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>107</v>
+        <v>145</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>41</v>
+        <v>52</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>98</v>
+        <v>82</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>11</v>
+        <v>36</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>36</v>
+        <v>172</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,56 +2490,56 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>142</v>
+        <v>114</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>30</v>
+        <v>42</v>
       </c>
       <c r="I39" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="J39" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K39" s="12" t="n">
+        <v>50</v>
+      </c>
+      <c r="L39" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M39" s="12" t="n">
         <v>39</v>
       </c>
-      <c r="J39" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="K39" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="L39" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="M39" s="12" t="n">
-        <v>132</v>
-      </c>
       <c r="N39" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA P. SORIANO</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>134</v>
+        <v>96</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>47</v>
+        <v>22</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>56</v>
+        <v>22</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="M40" s="12" t="n">
         <v>166</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2671,10 +2671,10 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>105</v>
+        <v>113</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>7</v>
@@ -2683,19 +2683,19 @@
         <v>10</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
@@ -2730,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="G43" s="12" t="n">
+        <v>121</v>
+      </c>
+      <c r="H43" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="I43" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>85</v>
       </c>
-      <c r="G43" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="I43" s="12" t="n">
-        <v>58</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>78</v>
-      </c>
       <c r="K43" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>77</v>
+        <v>82</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2848,19 +2848,19 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>17</v>
@@ -2869,14 +2869,14 @@
         <v>12</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2907,28 +2907,28 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>91</v>
+        <v>101</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>9</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="N46" s="12" t="n">
         <v>2</v>
@@ -2942,17 +2942,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>54638</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>VITERBO</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>TANGENZIALE OVEST N 15</t>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,56 +2962,56 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>52</v>
+        <v>125</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>9</v>
+        <v>108</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>136</v>
+        <v>179</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MONTAGNOLA N.24</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,56 +3021,56 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>94</v>
+        <v>72</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>15</v>
+        <v>45</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>164</v>
+        <v>62</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>54638</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>VITERBO</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
+          <t>TANGENZIALE OVEST N 15</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3080,39 +3080,39 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>45</v>
+        <v>58</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J49" s="12" t="n">
         <v>48</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3143,7 +3143,7 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="G50" s="12" t="n">
         <v>95</v>
@@ -3155,16 +3155,16 @@
         <v>40</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>0</v>
@@ -3178,17 +3178,17 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,39 +3198,39 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>55</v>
+        <v>151</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3261,28 +3261,28 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L52" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>3</v>
@@ -3320,28 +3320,28 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>10</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>131</v>
+        <v>141</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>2</v>
@@ -3379,28 +3379,28 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>0</v>
@@ -3438,28 +3438,28 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H55" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>60</v>
+        <v>66</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K55" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>1</v>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>77</v>
+        <v>48</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>79</v>
+        <v>49</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,39 +3611,39 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>44</v>
+        <v>96</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3674,16 +3674,16 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>93</v>
+        <v>98</v>
       </c>
       <c r="H59" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J59" s="12" t="n">
         <v>20</v>
@@ -3692,10 +3692,10 @@
         <v>4</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3733,42 +3733,42 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>106</v>
+        <v>48</v>
       </c>
       <c r="H60" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K60" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L60" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>29</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M60" s="12" t="n">
-        <v>187</v>
+        <v>213</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3792,52 +3792,52 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>43</v>
+        <v>116</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>56</v>
+        <v>41</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>200</v>
+        <v>187</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>S.P. LEUCIANA KM 2+670</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3851,52 +3851,52 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SS 430 KM 0.525</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,56 +3906,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>87</v>
+        <v>62</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>57</v>
+        <v>1</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="N64" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>83</v>
+        <v>44</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I65" s="12" t="n">
         <v>9</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,46 +4083,46 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -4132,7 +4132,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4146,31 +4146,31 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="I67" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>44</v>
+        <v>66</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4181,17 +4181,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4205,31 +4205,31 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>113</v>
+        <v>71</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4264,28 +4264,28 @@
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L69" s="12" t="n">
         <v>4</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>1</v>
@@ -4299,17 +4299,17 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,35 +4319,35 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>85</v>
+        <v>49</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>87</v>
+        <v>117</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4358,17 +4358,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,35 +4378,35 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
         <v>36</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>49</v>
+        <v>89</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I71" s="12" t="n">
+        <v>10</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K71" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="J71" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K71" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L71" s="12" t="n">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>S.S.205 KM.52+330</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,35 +4496,35 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>7</v>
+        <v>35</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4535,7 +4535,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -4545,7 +4545,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4559,52 +4559,52 @@
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="H74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="K74" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>67</v>
+        <v>142</v>
       </c>
       <c r="N74" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,35 +4614,35 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="M75" s="12" t="n">
         <v>68</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4677,28 +4677,28 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I76" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L76" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>22</v>
@@ -4712,17 +4712,17 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,56 +4732,56 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>42</v>
+        <v>29</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>57</v>
+        <v>70</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,56 +4791,56 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="I78" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="J78" s="12" t="n">
         <v>14</v>
       </c>
-      <c r="J78" s="12" t="n">
-        <v>15</v>
-      </c>
       <c r="K78" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,32 +4850,32 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K79" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L79" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L79" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M79" s="12" t="n">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
@@ -4889,17 +4889,17 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PRENESTINA EST</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,32 +4909,32 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
@@ -4975,13 +4975,13 @@
         <v>19</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>42</v>
+        <v>49</v>
       </c>
       <c r="H81" s="12" t="n">
         <v>19</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="J81" s="12" t="n">
         <v>27</v>
@@ -4993,7 +4993,7 @@
         <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5034,7 +5034,7 @@
         <v>19</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>1</v>
@@ -5096,7 +5096,7 @@
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
@@ -5111,31 +5111,31 @@
         <v>1</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N83" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,56 +5145,56 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
         <v>18</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5204,32 +5204,32 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>0</v>
@@ -5243,17 +5243,17 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
+          <t>VIA FLAMINIA KM. 29,700 SNC</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,56 +5263,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>32</v>
+        <v>17</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>PENNE</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>VIA G. ROSSA</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5322,56 +5322,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>2</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>PENNE</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA KM. 29,700 SNC</t>
+          <t>VIA G. ROSSA</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>
@@ -5400,16 +5400,16 @@
         <v>14</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5420,17 +5420,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>16572</t>
+          <t>06607</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>ORICOLA</t>
+          <t>SAN SALVO</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>S.S.TIBURTINA VALERIA KM. 68+300</t>
+          <t>FRAZ-MARINELLE</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G89" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I89" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>3</v>
       </c>
       <c r="L89" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
@@ -5479,17 +5479,17 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>06607</t>
+          <t>16572</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>SAN SALVO</t>
+          <t>ORICOLA</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-MARINELLE</t>
+          <t>S.S.TIBURTINA VALERIA KM. 68+300</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5499,32 +5499,32 @@
       </c>
       <c r="E90" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I90" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K90" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L90" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>14</v>
+        <v>34</v>
       </c>
       <c r="N90" s="12" t="n">
         <v>0</v>
@@ -5565,7 +5565,7 @@
         <v>9</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>2</v>
@@ -5583,14 +5583,14 @@
         <v>3</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="N91" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>0</v>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W21</t>
+          <t>W22</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8017</v>
+        <v>8342</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6024</v>
+        <v>6298</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2079</v>
+        <v>2232</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>475</v>
+        <v>495</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>634</v>
+        <v>660</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>356</v>
+        <v>375</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>730</v>
+        <v>768</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>535</v>
+        <v>554</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="L12" s="12" t="n">
         <v>81</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>454</v>
+        <v>475</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>109</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>341</v>
+        <v>354</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="L13" s="12" t="n">
         <v>65</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>587</v>
+        <v>610</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>280</v>
+        <v>292</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>349</v>
+        <v>363</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>210</v>
+        <v>221</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>271</v>
+        <v>282</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>43</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>37</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="L16" s="12" t="n">
         <v>43</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>241</v>
+        <v>253</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>145</v>
+        <v>153</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>39</v>
+        <v>48</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,28 +1255,28 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>156</v>
+        <v>161</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="L18" s="12" t="n">
         <v>48</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N18" s="12" t="n">
         <v>15</v>
@@ -1314,28 +1314,28 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>31</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>100</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>180</v>
@@ -1373,28 +1373,28 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="L20" s="12" t="n">
         <v>22</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="N20" s="12" t="n">
         <v>15</v>
@@ -1432,31 +1432,31 @@
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>276</v>
+        <v>293</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="I21" s="12" t="n">
         <v>36</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L21" s="12" t="n">
         <v>68</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,52 +1491,52 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>11</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>23</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>161</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,35 +1546,35 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>148</v>
+        <v>98</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>55</v>
+        <v>32</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>153</v>
+        <v>88</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>43</v>
+        <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CORSO DI FRANCIA 80</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>207</v>
+        <v>155</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>47</v>
+        <v>66</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>263</v>
+        <v>162</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>2</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
+          <t>CORSO DI FRANCIA 80</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>165</v>
+        <v>170</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>91</v>
+        <v>212</v>
       </c>
       <c r="H26" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="I26" s="12" t="n">
         <v>30</v>
       </c>
-      <c r="I26" s="12" t="n">
-        <v>31</v>
-      </c>
       <c r="J26" s="12" t="n">
-        <v>123</v>
+        <v>150</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>84</v>
+        <v>265</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIA E. MATTEI, 28</t>
+          <t>VIALE DELLA CROCE ROSSA 42/D</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,35 +1782,35 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>6</v>
+        <v>25</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>26</v>
+        <v>53</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>63</v>
+        <v>40</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>204</v>
+        <v>178</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1821,17 +1821,17 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA SUD KM 140+200</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>187</v>
+        <v>208</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>172</v>
+        <v>216</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELLA CROCE ROSSA 42/D</t>
+          <t>VIA CASILINA SUD KM 140+200</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,35 +1900,35 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>39</v>
+        <v>58</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,28 +1963,28 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="N30" s="12" t="n">
         <v>26</v>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>66</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>4</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G32" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H32" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="I32" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J32" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="K32" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="H32" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I32" s="12" t="n">
-        <v>25</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>105</v>
-      </c>
-      <c r="K32" s="12" t="n">
-        <v>52</v>
-      </c>
       <c r="L32" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>45</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,35 +2136,35 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>102</v>
+        <v>161</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>97</v>
+        <v>27</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>146</v>
+        <v>41</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>61</v>
+        <v>147</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,39 +2254,39 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>154</v>
+        <v>103</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>31</v>
+        <v>99</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>40</v>
+        <v>148</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>140</v>
+        <v>64</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2317,28 +2317,28 @@
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="I36" s="12" t="n">
         <v>77</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="N36" s="12" t="n">
         <v>3</v>
@@ -2352,17 +2352,17 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,35 +2372,35 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
+        <v>125</v>
+      </c>
+      <c r="G37" s="12" t="n">
         <v>121</v>
       </c>
-      <c r="G37" s="12" t="n">
-        <v>118</v>
-      </c>
       <c r="H37" s="12" t="n">
-        <v>23</v>
+        <v>48</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>20</v>
+        <v>88</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>48</v>
+        <v>106</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>10</v>
+        <v>53</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>74</v>
+        <v>16</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>96</v>
+        <v>40</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
@@ -2411,17 +2411,17 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA P. SORIANO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>145</v>
+        <v>123</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>52</v>
+        <v>23</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>82</v>
+        <v>49</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>32</v>
+        <v>10</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>36</v>
+        <v>76</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>172</v>
+        <v>102</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,39 +2490,39 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>114</v>
+        <v>150</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>42</v>
+        <v>53</v>
       </c>
       <c r="I39" s="12" t="n">
+        <v>60</v>
+      </c>
+      <c r="J39" s="12" t="n">
         <v>84</v>
       </c>
-      <c r="J39" s="12" t="n">
-        <v>100</v>
-      </c>
       <c r="K39" s="12" t="n">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>11</v>
+        <v>38</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2553,35 +2553,35 @@
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="H40" s="12" t="n">
         <v>22</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L40" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>166</v>
+        <v>176</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="I41" s="12" t="n">
         <v>32</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L41" s="12" t="n">
         <v>47</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>4</v>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I42" s="12" t="n">
         <v>10</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>2</v>
@@ -2730,28 +2730,28 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L43" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>282</v>
+        <v>299</v>
       </c>
       <c r="N43" s="12" t="n">
         <v>9</v>
@@ -2789,19 +2789,19 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>31</v>
@@ -2810,7 +2810,7 @@
         <v>15</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="N44" s="12" t="n">
         <v>6</v>
@@ -2848,52 +2848,52 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>12</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>SS 80 KM 77+842</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,35 +2903,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
+        <v>83</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>93</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>78</v>
+      </c>
+      <c r="I46" s="12" t="n">
         <v>77</v>
       </c>
-      <c r="G46" s="12" t="n">
-        <v>101</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="J46" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>128</v>
+        <v>71</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>2</v>
+        <v>47</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2942,17 +2942,17 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MONTAGNOLA N.24</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,56 +2962,56 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>125</v>
+        <v>103</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>108</v>
+        <v>6</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>57</v>
+        <v>66</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>179</v>
+        <v>134</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,39 +3021,39 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>86</v>
+        <v>127</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>69</v>
+        <v>19</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>45</v>
+        <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>62</v>
+        <v>188</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>7</v>
@@ -3096,7 +3096,7 @@
         <v>10</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>14</v>
@@ -3105,7 +3105,7 @@
         <v>24</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>6</v>
@@ -3143,19 +3143,19 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>11</v>
@@ -3164,7 +3164,7 @@
         <v>19</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="N50" s="12" t="n">
         <v>0</v>
@@ -3202,35 +3202,35 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="G51" s="12" t="n">
+        <v>54</v>
+      </c>
+      <c r="H51" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I51" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J51" s="12" t="n">
         <v>49</v>
-      </c>
-      <c r="H51" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I51" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="J51" s="12" t="n">
-        <v>48</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>19</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3261,28 +3261,28 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L52" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>3</v>
@@ -3320,10 +3320,10 @@
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H53" s="12" t="n">
         <v>8</v>
@@ -3332,16 +3332,16 @@
         <v>6</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>2</v>
@@ -3355,17 +3355,17 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,35 +3375,35 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>31</v>
+        <v>10</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>55</v>
+        <v>107</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>8</v>
+        <v>31</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>103</v>
+        <v>55</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>81</v>
+        <v>50</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>83</v>
+        <v>51</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>48</v>
+        <v>84</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>49</v>
+        <v>98</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>0</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="H59" s="12" t="n">
         <v>7</v>
@@ -3692,10 +3692,10 @@
         <v>4</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3733,42 +3733,42 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>48</v>
+        <v>121</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>213</v>
+        <v>195</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3792,52 +3792,52 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>116</v>
+        <v>55</v>
       </c>
       <c r="H61" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I61" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K61" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="L61" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="I61" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="J61" s="12" t="n">
-        <v>41</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L61" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M61" s="12" t="n">
-        <v>187</v>
+        <v>222</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>SS 430 KM 0.525</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>91</v>
+        <v>1</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="I62" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J62" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="K62" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="J62" s="12" t="n">
-        <v>35</v>
-      </c>
-      <c r="K62" s="12" t="n">
+      <c r="L62" s="12" t="n">
         <v>13</v>
       </c>
-      <c r="L62" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="M62" s="12" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,56 +3906,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
         <v>44</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>62</v>
+        <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>1</v>
+        <v>92</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="I64" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="K64" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L64" s="12" t="n">
         <v>7</v>
       </c>
-      <c r="L64" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="M64" s="12" t="n">
-        <v>46</v>
+        <v>62</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>S.P. LEUCIANA KM 2+670</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,39 +4024,39 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>44</v>
+        <v>68</v>
       </c>
       <c r="H65" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>37</v>
+        <v>67</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4087,10 +4087,10 @@
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="H66" s="12" t="n">
         <v>4</v>
@@ -4099,7 +4099,7 @@
         <v>9</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K66" s="12" t="n">
         <v>11</v>
@@ -4108,7 +4108,7 @@
         <v>6</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="N66" s="12" t="n">
         <v>1</v>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,35 +4142,35 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="K67" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>40</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>19</v>
-      </c>
       <c r="L67" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4181,17 +4181,17 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4205,31 +4205,31 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>71</v>
+        <v>124</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>62</v>
+        <v>46</v>
       </c>
       <c r="H69" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>95</v>
+        <v>37</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,35 +4319,35 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J70" s="12" t="n">
         <v>34</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L70" s="12" t="n">
         <v>6</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>117</v>
+        <v>100</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
@@ -4358,17 +4358,17 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,39 +4378,39 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>89</v>
+        <v>0</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J71" s="12" t="n">
         <v>32</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4441,28 +4441,28 @@
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="H72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L72" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>2</v>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>S.S.205 KM.52+330</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>35</v>
+        <v>4</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,35 +4555,35 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>8</v>
+        <v>36</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>9</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>142</v>
+        <v>93</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4618,42 +4618,42 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L75" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4677,35 +4677,35 @@
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>29</v>
+        <v>1</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L76" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="M76" s="12" t="n">
+        <v>151</v>
+      </c>
+      <c r="N76" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M76" s="12" t="n">
-        <v>59</v>
-      </c>
-      <c r="N76" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4736,35 +4736,35 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L77" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4795,28 +4795,28 @@
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L78" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>5</v>
@@ -4830,17 +4830,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>PRENESTINA EST</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,56 +4850,56 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>0</v>
+        <v>69</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>41</v>
+        <v>105</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,32 +4909,32 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K80" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L80" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L80" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M80" s="12" t="n">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="N80" s="12" t="n">
         <v>0</v>
@@ -4948,17 +4948,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,32 +4968,32 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>19</v>
+        <v>35</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>27</v>
+        <v>15</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
@@ -5007,17 +5007,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,56 +5027,56 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K82" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L82" s="12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>14</v>
+        <v>28</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>VIA FLAMINIA KM. 29,700 SNC</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5086,35 +5086,35 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="K83" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="L83" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M83" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="N83" s="12" t="n">
         <v>1</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>54</v>
-      </c>
-      <c r="N83" s="12" t="n">
-        <v>32</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
@@ -5125,17 +5125,17 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="H84" s="12" t="n">
         <v>1</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="J84" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K84" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L84" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M84" s="12" t="n">
         <v>14</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L84" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="M84" s="12" t="n">
-        <v>19</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0</v>
@@ -5184,17 +5184,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5214,46 +5214,46 @@
         <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="I85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA KM. 29,700 SNC</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,39 +5263,39 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5329,7 +5329,7 @@
         <v>17</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H87" s="12" t="n">
         <v>2</v>
@@ -5347,7 +5347,7 @@
         <v>7</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
@@ -5385,19 +5385,19 @@
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K88" s="12" t="n">
         <v>2</v>
@@ -5465,14 +5465,14 @@
         <v>0</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5503,19 +5503,19 @@
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H90" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I90" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="I90" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="J90" s="12" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>3</v>
@@ -5524,7 +5524,7 @@
         <v>3</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N90" s="12" t="n">
         <v>0</v>
@@ -5562,10 +5562,10 @@
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>2</v>
@@ -5574,16 +5574,16 @@
         <v>0</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K91" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L91" s="12" t="n">
         <v>3</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="N91" s="12" t="n">
         <v>2</v>
@@ -5597,17 +5597,17 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>07164</t>
+          <t>58341</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>CASTEL GANDOLFO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>VIA APPIA KM 24,600 SNC 0012</t>
+          <t>VIA ARDEATINA</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5633,19 +5633,19 @@
         <v>0</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="K92" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L92" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="N92" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
@@ -5656,17 +5656,17 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>58341</t>
+          <t>07164</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTEL GANDOLFO</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>VIA ARDEATINA</t>
+          <t>VIA APPIA KM 24,600 SNC 0012</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
@@ -5692,19 +5692,19 @@
         <v>0</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K93" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L93" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="N93" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W22</t>
+          <t>W23</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8342</v>
+        <v>8768</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6298</v>
+        <v>6632</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2232</v>
+        <v>2427</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>495</v>
+        <v>515</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>660</v>
+        <v>687</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>249</v>
+        <v>260</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>768</v>
+        <v>806</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>554</v>
+        <v>576</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>325</v>
+        <v>338</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>475</v>
+        <v>499</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>331</v>
+        <v>375</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>354</v>
+        <v>367</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>67</v>
+        <v>79</v>
       </c>
       <c r="I13" s="12" t="n">
         <v>65</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>264</v>
+        <v>294</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>610</v>
+        <v>646</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>536</v>
+        <v>567</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,28 +1078,28 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>43</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="N15" s="12" t="n">
         <v>37</v>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>330</v>
+        <v>343</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,52 +1314,52 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="L19" s="12" t="n">
         <v>31</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>285</v>
+        <v>296</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>180</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>VIA CASILINA KM. 24+950</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,35 +1369,35 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>198</v>
+        <v>209</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>213</v>
+        <v>309</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>51</v>
+        <v>31</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>104</v>
+        <v>36</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>98</v>
+        <v>56</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>22</v>
+        <v>72</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>133</v>
+        <v>330</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
@@ -1408,17 +1408,17 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM. 24+950</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>293</v>
+        <v>220</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>29</v>
+        <v>53</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>132</v>
+        <v>174</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>52</v>
+        <v>100</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>68</v>
+        <v>24</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>310</v>
+        <v>138</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>243</v>
+        <v>254</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>161</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1550,28 +1550,28 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>37</v>
+        <v>44</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>137</v>
+        <v>149</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
@@ -1585,17 +1585,17 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1609,52 +1609,52 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>155</v>
+        <v>236</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>59</v>
+        <v>165</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>53</v>
+        <v>41</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>29</v>
+        <v>54</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>162</v>
+        <v>230</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>44</v>
+        <v>3</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>VIA CARDUCCI</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,35 +1668,35 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>232</v>
+        <v>166</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>154</v>
+        <v>65</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>123</v>
+        <v>146</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>53</v>
+        <v>30</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>223</v>
+        <v>168</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1727,31 +1727,31 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>212</v>
+        <v>223</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="I26" s="12" t="n">
         <v>30</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L26" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,31 +1845,31 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
         <v>39</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="H29" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>23</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>180</v>
+        <v>190</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="L31" s="12" t="n">
         <v>66</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>4</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>54</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="I32" s="12" t="n">
         <v>26</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>33</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>179</v>
+        <v>190</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>45</v>
@@ -2116,17 +2116,17 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,32 +2136,32 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>159</v>
+        <v>164</v>
       </c>
       <c r="H33" s="12" t="n">
         <v>35</v>
       </c>
       <c r="I33" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="J33" s="12" t="n">
+        <v>96</v>
+      </c>
+      <c r="K33" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="L33" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J33" s="12" t="n">
-        <v>110</v>
-      </c>
-      <c r="K33" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="L33" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="M33" s="12" t="n">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>2</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>161</v>
+        <v>125</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="I34" s="12" t="n">
+        <v>91</v>
+      </c>
+      <c r="J34" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="K34" s="12" t="n">
+        <v>61</v>
+      </c>
+      <c r="L34" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M34" s="12" t="n">
         <v>41</v>
       </c>
-      <c r="J34" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="K34" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="L34" s="12" t="n">
-        <v>37</v>
-      </c>
-      <c r="M34" s="12" t="n">
-        <v>147</v>
-      </c>
       <c r="N34" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>99</v>
+        <v>36</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>148</v>
+        <v>45</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>64</v>
+        <v>150</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>CORSO MAZZINI</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>163</v>
+        <v>109</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>77</v>
+        <v>154</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>101</v>
+        <v>70</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="J37" s="12" t="n">
+        <v>108</v>
+      </c>
+      <c r="K37" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="L37" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="M37" s="12" t="n">
         <v>106</v>
       </c>
-      <c r="K37" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="L37" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M37" s="12" t="n">
-        <v>40</v>
-      </c>
       <c r="N37" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>123</v>
+        <v>159</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>23</v>
+        <v>56</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>20</v>
+        <v>62</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>49</v>
+        <v>87</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>102</v>
+        <v>185</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA P. SORIANO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,56 +2490,56 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>150</v>
+        <v>127</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>84</v>
+        <v>50</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>33</v>
+        <v>10</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>38</v>
+        <v>76</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>180</v>
+        <v>104</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>99</v>
+        <v>113</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>33</v>
+        <v>48</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>176</v>
+        <v>207</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>SS SALARIA KM 14, 895 EST</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,56 +2608,56 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>47</v>
+        <v>34</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>IV NOVEMBRE</t>
+          <t>CORSO FRANCIA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,46 +2667,46 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>10</v>
+        <v>63</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>32</v>
+        <v>14</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>64</v>
+        <v>315</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CORSO FRANCIA</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2730,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>128</v>
+        <v>155</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>299</v>
+        <v>191</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,17 +2765,17 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,39 +2785,39 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>147</v>
+        <v>126</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>42</v>
+        <v>10</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="K44" s="12" t="n">
         <v>31</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>15</v>
+        <v>34</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>187</v>
+        <v>67</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -2848,28 +2848,28 @@
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="G45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="I45" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="L45" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>12</v>
@@ -2907,31 +2907,31 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
+        <v>87</v>
+      </c>
+      <c r="G46" s="12" t="n">
+        <v>97</v>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>85</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="J46" s="12" t="n">
         <v>83</v>
       </c>
-      <c r="G46" s="12" t="n">
-        <v>93</v>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>78</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>77</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>79</v>
-      </c>
       <c r="K46" s="12" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="L46" s="12" t="n">
         <v>2</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>6</v>
@@ -2978,16 +2978,16 @@
         <v>6</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>2</v>
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>127</v>
+        <v>132</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>17</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
@@ -3084,52 +3084,52 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="K49" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="L49" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="N49" s="12" t="n">
         <v>6</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
         <v>71</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>96</v>
+        <v>63</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>43</v>
+        <v>7</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>82</v>
+        <v>165</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,56 +3198,56 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>54</v>
+        <v>153</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 104+320</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,56 +3257,56 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>58</v>
+        <v>99</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>23</v>
+        <v>3</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>147</v>
+        <v>52</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="K53" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="L53" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L53" s="12" t="n">
-        <v>27</v>
-      </c>
       <c r="M53" s="12" t="n">
-        <v>147</v>
+        <v>53</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>VIA CASILINA KM 104+320</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L54" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>107</v>
+        <v>80</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>79</v>
+        <v>90</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>55</v>
+        <v>114</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,56 +3493,56 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>50</v>
+        <v>82</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>11</v>
+        <v>31</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>4</v>
+        <v>59</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,56 +3552,56 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>98</v>
+        <v>91</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="K58" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L58" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L58" s="12" t="n">
-        <v>22</v>
-      </c>
       <c r="M58" s="12" t="n">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="N58" s="12" t="n">
         <v>0</v>
@@ -3674,10 +3674,10 @@
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="H59" s="12" t="n">
         <v>7</v>
@@ -3686,7 +3686,7 @@
         <v>4</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K59" s="12" t="n">
         <v>4</v>
@@ -3695,7 +3695,7 @@
         <v>34</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>1</v>
@@ -3709,7 +3709,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3719,7 +3719,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3736,39 +3736,39 @@
         <v>52</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>121</v>
+        <v>58</v>
       </c>
       <c r="H60" s="12" t="n">
+        <v>21</v>
+      </c>
+      <c r="I60" s="12" t="n">
+        <v>24</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>59</v>
+      </c>
+      <c r="K60" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="L60" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I60" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="J60" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L60" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M60" s="12" t="n">
-        <v>195</v>
+        <v>228</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3778,7 +3778,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3792,35 +3792,35 @@
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>55</v>
+        <v>131</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3851,35 +3851,35 @@
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G62" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L62" s="12" t="n">
         <v>13</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N62" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3910,28 +3910,28 @@
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I63" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="L63" s="12" t="n">
         <v>1</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="N63" s="12" t="n">
         <v>1</v>
@@ -3969,10 +3969,10 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="H64" s="12" t="n">
         <v>0</v>
@@ -3981,16 +3981,16 @@
         <v>7</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L64" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>0</v>
@@ -4004,17 +4004,17 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,35 +4024,35 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
         <v>44</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>68</v>
+        <v>53</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="K65" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L65" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L65" s="12" t="n">
-        <v>16</v>
-      </c>
       <c r="M65" s="12" t="n">
-        <v>67</v>
+        <v>131</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="H66" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M66" s="12" t="n">
+        <v>112</v>
+      </c>
+      <c r="N66" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="I66" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="L66" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>62</v>
-      </c>
-      <c r="N66" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>61</v>
+        <v>87</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I67" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J67" s="12" t="n">
+        <v>36</v>
+      </c>
+      <c r="K67" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M67" s="12" t="n">
+        <v>67</v>
+      </c>
+      <c r="N67" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J67" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K67" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="L67" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="N67" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,35 +4201,35 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="H68" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I68" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>27</v>
+      </c>
+      <c r="K68" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="I68" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="J68" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>14</v>
-      </c>
       <c r="L68" s="12" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>124</v>
+        <v>70</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>S.P. LEUCIANA KM 2+670</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="N69" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,35 +4378,35 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G71" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="H71" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I71" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J71" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="12" t="n">
+      <c r="K71" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L71" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="M71" s="12" t="n">
         <v>37</v>
       </c>
-      <c r="I71" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="12" t="n">
-        <v>32</v>
-      </c>
-      <c r="K71" s="12" t="n">
-        <v>8</v>
-      </c>
-      <c r="L71" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="M71" s="12" t="n">
-        <v>63</v>
-      </c>
       <c r="N71" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I72" s="12" t="n">
         <v>38</v>
       </c>
-      <c r="G72" s="12" t="n">
-        <v>55</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="J72" s="12" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I73" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="L73" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>74</v>
+      </c>
+      <c r="N73" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J73" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>100</v>
-      </c>
-      <c r="N73" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>S.S.205 KM.52+330</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,35 +4555,35 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>71</v>
+        <v>58</v>
       </c>
       <c r="H74" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I74" s="12" t="n">
+        <v>23</v>
+      </c>
+      <c r="J74" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K74" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I74" s="12" t="n">
-        <v>36</v>
-      </c>
-      <c r="J74" s="12" t="n">
-        <v>24</v>
-      </c>
-      <c r="K74" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="L74" s="12" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4618,13 +4618,13 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>2</v>
+        <v>40</v>
       </c>
       <c r="I75" s="12" t="n">
         <v>0</v>
@@ -4636,17 +4636,17 @@
         <v>9</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>1</v>
+        <v>22</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -4680,7 +4680,7 @@
         <v>33</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>78</v>
+        <v>83</v>
       </c>
       <c r="H76" s="12" t="n">
         <v>1</v>
@@ -4698,7 +4698,7 @@
         <v>5</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>1</v>
@@ -4736,10 +4736,10 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="H77" s="12" t="n">
         <v>13</v>
@@ -4748,16 +4748,16 @@
         <v>17</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="L77" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>6</v>
@@ -4795,19 +4795,19 @@
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="H78" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K78" s="12" t="n">
         <v>7</v>
@@ -4816,7 +4816,7 @@
         <v>11</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="N78" s="12" t="n">
         <v>5</v>
@@ -4830,17 +4830,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,56 +4850,56 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="H79" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J79" s="12" t="n">
         <v>19</v>
       </c>
-      <c r="I79" s="12" t="n">
-        <v>69</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="K79" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>105</v>
+        <v>30</v>
       </c>
       <c r="N79" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>PRENESTINA EST</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,56 +4909,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>0</v>
+        <v>74</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="L80" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="M80" s="12" t="n">
+        <v>111</v>
+      </c>
+      <c r="N80" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="M80" s="12" t="n">
-        <v>43</v>
-      </c>
-      <c r="N80" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,56 +4968,56 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K81" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L81" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L81" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M81" s="12" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,39 +5027,39 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K82" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="L82" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="M82" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5090,19 +5090,19 @@
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>6</v>
@@ -5184,17 +5184,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5204,56 +5204,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="G85" s="12" t="n">
+        <v>33</v>
+      </c>
+      <c r="H85" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I85" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G85" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="H85" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="I85" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="J85" s="12" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>54</v>
+        <v>38</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,56 +5263,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
         <v>18</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>20</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="L86" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="I86" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="K86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L86" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="M86" s="12" t="n">
-        <v>19</v>
+        <v>56</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5322,39 +5322,39 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5385,19 +5385,19 @@
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="I88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K88" s="12" t="n">
         <v>2</v>
@@ -5444,22 +5444,22 @@
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L89" s="12" t="n">
         <v>0</v>
@@ -5472,7 +5472,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5524,14 +5524,14 @@
         <v>3</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="N90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5565,7 +5565,7 @@
         <v>10</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>2</v>
@@ -5583,14 +5583,14 @@
         <v>3</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N91" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W23</t>
+          <t>W24</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>8768</v>
+        <v>9241</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6632</v>
+        <v>6988</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2427</v>
+        <v>2635</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>515</v>
+        <v>547</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>687</v>
+        <v>722</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>260</v>
+        <v>279</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>387</v>
+        <v>418</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>158</v>
+        <v>172</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>806</v>
+        <v>856</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,31 +901,31 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>420</v>
+        <v>450</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>576</v>
+        <v>598</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>338</v>
+        <v>367</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>178</v>
+        <v>193</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>499</v>
+        <v>526</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,35 +960,35 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>375</v>
+        <v>404</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>367</v>
+        <v>401</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>294</v>
+        <v>321</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>116</v>
+        <v>129</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>646</v>
+        <v>677</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>567</v>
+        <v>588</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1019,35 +1019,35 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>304</v>
+        <v>328</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>369</v>
+        <v>382</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>65</v>
+        <v>79</v>
       </c>
       <c r="I14" s="12" t="n">
         <v>64</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>76</v>
+        <v>91</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>297</v>
+        <v>308</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>255</v>
+        <v>264</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1137,31 +1137,31 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>261</v>
+        <v>275</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>158</v>
+        <v>163</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I17" s="12" t="n">
         <v>17</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>171</v>
+        <v>181</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="L17" s="12" t="n">
         <v>71</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>343</v>
+        <v>371</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1255,31 +1255,31 @@
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="I18" s="12" t="n">
+        <v>177</v>
+      </c>
+      <c r="J18" s="12" t="n">
         <v>168</v>
       </c>
-      <c r="J18" s="12" t="n">
-        <v>163</v>
-      </c>
       <c r="K18" s="12" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>180</v>
+        <v>195</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>173</v>
+        <v>184</v>
       </c>
       <c r="H19" s="12" t="n">
         <v>117</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>104</v>
@@ -1335,31 +1335,31 @@
         <v>31</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>180</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM. 24+950</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>309</v>
+        <v>224</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>31</v>
+        <v>57</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>141</v>
+        <v>178</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>56</v>
+        <v>102</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>72</v>
+        <v>29</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>330</v>
+        <v>147</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>VIA CASILINA KM. 24+950</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,35 +1428,35 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>220</v>
+        <v>312</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>108</v>
+        <v>37</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>174</v>
+        <v>142</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>100</v>
+        <v>56</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>24</v>
+        <v>74</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>138</v>
+        <v>349</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,35 +1491,35 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>184</v>
+        <v>194</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I22" s="12" t="n">
         <v>12</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="L22" s="12" t="n">
         <v>24</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>254</v>
+        <v>268</v>
       </c>
       <c r="N22" s="12" t="n">
         <v>161</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1550,52 +1550,52 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06753</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>CIVITANOVA MARCHE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>VIA CARDUCCI</t>
+          <t>CORSO DI FRANCIA 80</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,35 +1605,35 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>56</v>
+        <v>67</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>165</v>
+        <v>33</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>230</v>
+        <v>289</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
@@ -1644,17 +1644,17 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06753</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CIVITANOVA MARCHE</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIA CARDUCCI</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -1668,52 +1668,52 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>166</v>
+        <v>244</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>65</v>
+        <v>170</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="L25" s="12" t="n">
-        <v>30</v>
+        <v>55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>168</v>
+        <v>237</v>
       </c>
       <c r="N25" s="12" t="n">
-        <v>45</v>
+        <v>3</v>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>CORSO DI FRANCIA 80</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,39 +1723,39 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>223</v>
+        <v>179</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>59</v>
+        <v>72</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>30</v>
+        <v>67</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>275</v>
+        <v>179</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1786,31 +1786,31 @@
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
@@ -1845,28 +1845,28 @@
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="H28" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>8</v>
@@ -1904,31 +1904,31 @@
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J29" s="12" t="n">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="N29" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>162</v>
+        <v>171</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I30" s="12" t="n">
         <v>35</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="H31" s="12" t="n">
         <v>46</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>22</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>4</v>
@@ -2081,52 +2081,52 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>45</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,32 +2136,32 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>96</v>
+        <v>123</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>40</v>
+        <v>53</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>2</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>125</v>
+        <v>172</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>91</v>
+        <v>84</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>61</v>
+        <v>36</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>41</v>
+        <v>113</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,56 +2254,56 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>166</v>
+        <v>117</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>36</v>
+        <v>108</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>45</v>
+        <v>165</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>150</v>
+        <v>73</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>109</v>
+        <v>179</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>104</v>
+        <v>35</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>154</v>
+        <v>49</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>53</v>
+        <v>40</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>70</v>
+        <v>165</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>CORSO MAZZINI</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>169</v>
+        <v>128</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>106</v>
+        <v>41</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>VIA P. SORIANO</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,35 +2431,35 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>159</v>
+        <v>116</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>56</v>
+        <v>11</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>62</v>
+        <v>37</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>42</v>
+        <v>63</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>185</v>
+        <v>214</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
@@ -2470,17 +2470,17 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,56 +2490,56 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>127</v>
+        <v>168</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>20</v>
+        <v>64</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>50</v>
+        <v>92</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>104</v>
+        <v>197</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>SS SALARIA KM 14, 895 EST</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>121</v>
+        <v>130</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>74</v>
+        <v>90</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,35 +2608,35 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>120</v>
+        <v>129</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>107</v>
+        <v>135</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>34</v>
+        <v>77</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>186</v>
+        <v>117</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
@@ -2671,28 +2671,28 @@
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>137</v>
+        <v>158</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="N42" s="12" t="n">
         <v>9</v>
@@ -2706,17 +2706,17 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,56 +2726,56 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>106</v>
+        <v>111</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>155</v>
+        <v>131</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>45</v>
+        <v>11</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>42</v>
+        <v>33</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>191</v>
+        <v>71</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>IV NOVEMBRE</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,46 +2785,46 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="H44" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="I44" s="12" t="n">
+        <v>46</v>
+      </c>
+      <c r="J44" s="12" t="n">
+        <v>100</v>
+      </c>
+      <c r="K44" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="L44" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="M44" s="12" t="n">
+        <v>201</v>
+      </c>
+      <c r="N44" s="12" t="n">
         <v>8</v>
       </c>
-      <c r="I44" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="K44" s="12" t="n">
-        <v>31</v>
-      </c>
-      <c r="L44" s="12" t="n">
-        <v>34</v>
-      </c>
-      <c r="M44" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="N44" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,35 +2844,35 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>0</v>
+        <v>103</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>22</v>
+        <v>63</v>
       </c>
       <c r="L45" s="12" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>78</v>
+        <v>92</v>
       </c>
       <c r="N45" s="12" t="n">
-        <v>12</v>
+        <v>63</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,39 +2903,39 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>87</v>
+        <v>96</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>85</v>
+        <v>94</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>2</v>
+        <v>19</v>
       </c>
       <c r="M46" s="12" t="n">
         <v>81</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>55</v>
+        <v>13</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2966,10 +2966,10 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>82</v>
+        <v>87</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>6</v>
@@ -2978,16 +2978,16 @@
         <v>6</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L47" s="12" t="n">
         <v>11</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>2</v>
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>132</v>
+        <v>141</v>
       </c>
       <c r="H48" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
@@ -3084,10 +3084,10 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H49" s="12" t="n">
         <v>9</v>
@@ -3096,40 +3096,40 @@
         <v>12</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>16</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>06560</t>
+          <t>07181</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>AVEZZANO</t>
+          <t>SUBIACO</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
+          <t>SUBLACENSE KM 72*883</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3139,56 +3139,56 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="L50" s="12" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>165</v>
+        <v>59</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>06560</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>AVEZZANO</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>SS 5 KM.113+309 (VIA ROMA 212-TIBURTINA VALERIA)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3198,39 +3198,39 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="H51" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I51" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="K51" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="L51" s="12" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="N51" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3261,19 +3261,19 @@
         </is>
       </c>
       <c r="F52" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I52" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="J52" s="12" t="n">
         <v>45</v>
-      </c>
-      <c r="J52" s="12" t="n">
-        <v>42</v>
       </c>
       <c r="K52" s="12" t="n">
         <v>11</v>
@@ -3282,7 +3282,7 @@
         <v>19</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>0</v>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07181</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>SUBIACO</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>SUBLACENSE KM 72*883</t>
+          <t>VIA CASILINA KM 104+320</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="I53" s="12" t="n">
+        <v>45</v>
+      </c>
+      <c r="J53" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="K53" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L53" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="M53" s="12" t="n">
+        <v>84</v>
+      </c>
+      <c r="N53" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J53" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="K53" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="L53" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M53" s="12" t="n">
-        <v>53</v>
-      </c>
-      <c r="N53" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 104+320</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,56 +3375,56 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>63</v>
+        <v>159</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="I54" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J54" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="J54" s="12" t="n">
-        <v>54</v>
-      </c>
       <c r="K54" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>80</v>
+        <v>162</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>72</v>
+        <v>59</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>114</v>
+        <v>62</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,35 +3493,35 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>82</v>
+        <v>96</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>57</v>
+        <v>121</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3532,17 +3532,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3552,35 +3552,35 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>91</v>
+        <v>117</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3591,17 +3591,17 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>87</v>
+        <v>1</v>
       </c>
       <c r="H58" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>43</v>
+        <v>60</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>17</v>
+        <v>29</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>102</v>
+        <v>75</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,35 +3670,35 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>21</v>
+        <v>35</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>116</v>
+        <v>98</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
@@ -3733,28 +3733,28 @@
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>228</v>
+        <v>250</v>
       </c>
       <c r="N60" s="12" t="n">
         <v>2</v>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>36</v>
+        <v>12</v>
       </c>
       <c r="J61" s="12" t="n">
         <v>44</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>205</v>
+        <v>105</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>1</v>
+        <v>144</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>49</v>
+        <v>218</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,56 +3906,56 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J63" s="12" t="n">
         <v>48</v>
       </c>
       <c r="K63" s="12" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="L63" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M63" s="12" t="n">
-        <v>73</v>
+        <v>136</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>SS 430 KM 0.525</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="G64" s="12" t="n">
-        <v>96</v>
+        <v>1</v>
       </c>
       <c r="H64" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="I64" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="I64" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="J64" s="12" t="n">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4024,56 +4024,56 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>44</v>
+        <v>51</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K65" s="12" t="n">
+        <v>17</v>
+      </c>
+      <c r="L65" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L65" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M65" s="12" t="n">
-        <v>131</v>
+        <v>93</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>112</v>
+        <v>65</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H67" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="I67" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="I67" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="J67" s="12" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="K67" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L67" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="M67" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="N67" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L67" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="M67" s="12" t="n">
-        <v>67</v>
-      </c>
-      <c r="N67" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,56 +4201,56 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>73</v>
+        <v>103</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="I68" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="J68" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="K68" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L68" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M68" s="12" t="n">
+        <v>115</v>
+      </c>
+      <c r="N68" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="J68" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K68" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L68" s="12" t="n">
-        <v>16</v>
-      </c>
-      <c r="M68" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="N68" s="12" t="n">
-        <v>8</v>
-      </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>63</v>
+        <v>0</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="M69" s="12" t="n">
         <v>74</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>67</v>
+        <v>95</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="N70" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>S.P. LEUCIANA KM 2+670</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J71" s="12" t="n">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="K71" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L71" s="12" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>37</v>
+        <v>79</v>
       </c>
       <c r="N71" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>S.S.205 KM.52+330</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,56 +4437,56 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
+        <v>43</v>
+      </c>
+      <c r="G72" s="12" t="n">
+        <v>72</v>
+      </c>
+      <c r="H72" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="I72" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J72" s="12" t="n">
         <v>42</v>
       </c>
-      <c r="G72" s="12" t="n">
-        <v>73</v>
-      </c>
-      <c r="H72" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="I72" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J72" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="K72" s="12" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>97</v>
+        <v>110</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="G73" s="12" t="n">
+        <v>75</v>
+      </c>
+      <c r="H73" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="I73" s="12" t="n">
+        <v>40</v>
+      </c>
+      <c r="J73" s="12" t="n">
+        <v>30</v>
+      </c>
+      <c r="K73" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L73" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="M73" s="12" t="n">
+        <v>98</v>
+      </c>
+      <c r="N73" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H73" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I73" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J73" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K73" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L73" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="M73" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="N73" s="12" t="n">
-        <v>4</v>
-      </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,46 +4555,46 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>12</v>
       </c>
       <c r="L74" s="12" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>90</v>
+        <v>37</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -4604,7 +4604,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4618,31 +4618,31 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G75" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H75" s="12" t="n">
-        <v>40</v>
+        <v>6</v>
       </c>
       <c r="I75" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="K75" s="12" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L75" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>22</v>
+        <v>6</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
@@ -4680,13 +4680,13 @@
         <v>33</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>83</v>
+        <v>92</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="J76" s="12" t="n">
         <v>33</v>
@@ -4698,7 +4698,7 @@
         <v>5</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="N76" s="12" t="n">
         <v>1</v>
@@ -4736,28 +4736,28 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="I77" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L77" s="12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="N77" s="12" t="n">
         <v>6</v>
@@ -4771,17 +4771,17 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,56 +4791,56 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>58</v>
+        <v>0</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>66</v>
+        <v>33</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,39 +4850,39 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>0</v>
+        <v>63</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L79" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="M79" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="N79" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="M79" s="12" t="n">
-        <v>30</v>
-      </c>
-      <c r="N79" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -4916,13 +4916,13 @@
         <v>22</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="J80" s="12" t="n">
         <v>30</v>
@@ -4934,10 +4934,10 @@
         <v>0</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>111</v>
+        <v>120</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4948,17 +4948,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>PRENESTINA EST</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,56 +4968,56 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>3</v>
+        <v>37</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>2</v>
+        <v>37</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>0</v>
+        <v>62</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>46</v>
+        <v>31</v>
       </c>
       <c r="N81" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,39 +5027,39 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>34</v>
+        <v>4</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
       <c r="I82" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="K82" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L82" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L82" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="M82" s="12" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5090,7 +5090,7 @@
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G83" s="12" t="n">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K83" s="12" t="n">
         <v>6</v>
@@ -5111,31 +5111,31 @@
         <v>0</v>
       </c>
       <c r="M83" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,32 +5145,32 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0</v>
@@ -5184,17 +5184,17 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>06607</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>SAN SALVO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
+          <t>FRAZ-MARINELLE</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5204,56 +5204,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>38</v>
+        <v>16</v>
       </c>
       <c r="N85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,56 +5263,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G86" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I86" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J86" s="12" t="n">
+        <v>13</v>
+      </c>
+      <c r="K86" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="L86" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="M86" s="12" t="n">
+        <v>14</v>
+      </c>
+      <c r="N86" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H86" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="I86" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="K86" s="12" t="n">
-        <v>9</v>
-      </c>
-      <c r="L86" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="M86" s="12" t="n">
-        <v>56</v>
-      </c>
-      <c r="N86" s="12" t="n">
-        <v>34</v>
-      </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5322,56 +5322,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="G87" s="12" t="n">
+        <v>34</v>
+      </c>
+      <c r="H87" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="I87" s="12" t="n">
         <v>18</v>
       </c>
-      <c r="G87" s="12" t="n">
-        <v>33</v>
-      </c>
-      <c r="H87" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I87" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="J87" s="12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>26866</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>PENNE</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>VIA G. ROSSA</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5381,35 +5381,35 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
@@ -5420,17 +5420,17 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>06607</t>
+          <t>26866</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>SAN SALVO</t>
+          <t>PENNE</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-MARINELLE</t>
+          <t>VIA G. ROSSA</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5440,32 +5440,32 @@
       </c>
       <c r="E89" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F89" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H89" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="I89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="K89" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
@@ -5506,7 +5506,7 @@
         <v>12</v>
       </c>
       <c r="G90" s="12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H90" s="12" t="n">
         <v>3</v>
@@ -5524,14 +5524,14 @@
         <v>3</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5565,13 +5565,13 @@
         <v>10</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>9</v>
@@ -5583,14 +5583,14 @@
         <v>3</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N91" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -612,7 +612,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>W24</t>
+          <t>W25</t>
         </is>
       </c>
       <c r="C4" s="2" t="n"/>
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9241</v>
+        <v>9737</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>6988</v>
+        <v>7384</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2635</v>
+        <v>2863</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,31 +842,31 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>547</v>
+        <v>569</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>722</v>
+        <v>752</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>418</v>
+        <v>437</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>856</v>
+        <v>908</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,28 +901,28 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>526</v>
+        <v>569</v>
       </c>
       <c r="N12" s="12" t="n">
         <v>113</v>
@@ -960,31 +960,31 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>404</v>
+        <v>428</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>401</v>
+        <v>424</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>321</v>
+        <v>342</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>677</v>
+        <v>706</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>588</v>
+        <v>609</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,31 +1019,31 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>382</v>
+        <v>389</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>231</v>
+        <v>242</v>
       </c>
       <c r="K14" s="12" t="n">
-        <v>102</v>
+        <v>108</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>247</v>
+        <v>261</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,35 +1078,35 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>264</v>
+        <v>271</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>136</v>
+        <v>148</v>
       </c>
       <c r="I15" s="12" t="n">
         <v>47</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>113</v>
+        <v>122</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>262</v>
+        <v>284</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1137,35 +1137,35 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>81</v>
+        <v>91</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>205</v>
+        <v>219</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1196,31 +1196,31 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="H17" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>371</v>
+        <v>399</v>
       </c>
       <c r="N17" s="12" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>59243</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>JESI</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA ANCONA 68</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,56 +1251,56 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>268</v>
+        <v>227</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>177</v>
+        <v>112</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>168</v>
+        <v>192</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>68</v>
+        <v>109</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>56</v>
+        <v>30</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>36959</t>
+          <t>59243</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>JESI</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>VIA DI TOR VERGATA</t>
+          <t>VIA ANCONA 68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1310,56 +1310,56 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>184</v>
+        <v>276</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>34</v>
+        <v>188</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="K19" s="12" t="n">
-        <v>104</v>
+        <v>69</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>31</v>
+        <v>56</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>306</v>
+        <v>201</v>
       </c>
       <c r="N19" s="12" t="n">
-        <v>180</v>
+        <v>18</v>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>VIA CASILINA KM. 24+950</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,56 +1369,56 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>224</v>
+        <v>323</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>102</v>
+        <v>59</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>29</v>
+        <v>80</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>147</v>
+        <v>368</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>36993</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM. 24+950</t>
+          <t>VIA DI ACILIA</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -1428,46 +1428,46 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F21" s="12" t="n">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>312</v>
+        <v>198</v>
       </c>
       <c r="H21" s="12" t="n">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="I21" s="12" t="n">
-        <v>37</v>
+        <v>12</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="K21" s="12" t="n">
-        <v>56</v>
+        <v>89</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>74</v>
+        <v>24</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>349</v>
+        <v>279</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>5</v>
+        <v>162</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>36993</t>
+          <t>36959</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>VIA DI ACILIA</t>
+          <t>VIA DI TOR VERGATA</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -1487,35 +1487,35 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="H22" s="12" t="n">
-        <v>21</v>
+        <v>120</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>12</v>
+        <v>35</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K22" s="12" t="n">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>268</v>
+        <v>321</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>161</v>
+        <v>181</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
@@ -1550,35 +1550,35 @@
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>159</v>
+        <v>173</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="L23" s="12" t="n">
         <v>39</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="N23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1609,28 +1609,28 @@
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I24" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="N24" s="12" t="n">
         <v>15</v>
@@ -1668,28 +1668,28 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="K25" s="12" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="L25" s="12" t="n">
         <v>55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>237</v>
+        <v>249</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>3</v>
@@ -1703,17 +1703,17 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06556</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>L'AQUILA</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIALE DELLA CROCE ROSSA 42/D</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -1723,56 +1723,56 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>179</v>
+        <v>231</v>
       </c>
       <c r="H26" s="12" t="n">
-        <v>72</v>
+        <v>34</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="K26" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="L26" s="12" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>179</v>
+        <v>205</v>
       </c>
       <c r="N26" s="12" t="n">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06556</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>L'AQUILA</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>VIALE DELLA CROCE ROSSA 42/D</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>220</v>
+        <v>181</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>33</v>
+        <v>72</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>21</v>
+        <v>46</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA E. MATTEI, 28</t>
+          <t>VIA CASILINA SUD KM 140+200</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,35 +1841,35 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>225</v>
+        <v>218</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>247</v>
+        <v>226</v>
       </c>
       <c r="N28" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA SUD KM 140+200</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,32 +1900,32 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="I29" s="12" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="J29" s="12" t="n">
         <v>112</v>
       </c>
       <c r="K29" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>64</v>
+        <v>70</v>
       </c>
       <c r="M29" s="12" t="n">
-        <v>205</v>
+        <v>257</v>
       </c>
       <c r="N29" s="12" t="n">
         <v>9</v>
@@ -1963,31 +1963,31 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K30" s="12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,28 +2022,28 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>153</v>
+        <v>162</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="K31" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>4</v>
@@ -2081,28 +2081,28 @@
         </is>
       </c>
       <c r="F32" s="12" t="n">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="L32" s="12" t="n">
         <v>34</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="N32" s="12" t="n">
         <v>45</v>
@@ -2140,28 +2140,28 @@
         </is>
       </c>
       <c r="F33" s="12" t="n">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="L33" s="12" t="n">
         <v>25</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>161</v>
+        <v>172</v>
       </c>
       <c r="N33" s="12" t="n">
         <v>2</v>
@@ -2175,17 +2175,17 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06598</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>VASTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>CORSO MAZZINI</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>172</v>
+        <v>128</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>53</v>
+        <v>16</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>118</v>
+        <v>86</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>24</v>
+        <v>69</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>113</v>
+        <v>230</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,35 +2254,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>108</v>
+        <v>65</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>165</v>
+        <v>95</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>56</v>
+        <v>69</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>73</v>
+        <v>48</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06791</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>VIA ROMA</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,56 +2313,56 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>141</v>
+        <v>151</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>179</v>
+        <v>118</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>35</v>
+        <v>115</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>96</v>
+        <v>118</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>40</v>
+        <v>57</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>165</v>
+        <v>77</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06598</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>VASTO</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>CORSO MAZZINI</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2372,56 +2372,56 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>128</v>
+        <v>176</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="K37" s="12" t="n">
-        <v>61</v>
+        <v>38</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>41</v>
+        <v>119</v>
       </c>
       <c r="N37" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>06791</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>SS SALARIA KM 14, 895 EST</t>
+          <t>VIA ROMA</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2431,56 +2431,56 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="G38" s="12" t="n">
-        <v>116</v>
+        <v>183</v>
       </c>
       <c r="H38" s="12" t="n">
-        <v>11</v>
+        <v>37</v>
       </c>
       <c r="I38" s="12" t="n">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="K38" s="12" t="n">
-        <v>30</v>
+        <v>41</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>214</v>
+        <v>174</v>
       </c>
       <c r="N38" s="12" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>54396</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>CHIETI</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>VIA P. SORIANO</t>
+          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -2490,56 +2490,56 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>168</v>
+        <v>123</v>
       </c>
       <c r="H39" s="12" t="n">
-        <v>59</v>
+        <v>28</v>
       </c>
       <c r="I39" s="12" t="n">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="K39" s="12" t="n">
-        <v>38</v>
+        <v>18</v>
       </c>
       <c r="L39" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>197</v>
+        <v>208</v>
       </c>
       <c r="N39" s="12" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>CHIETI</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>V.LE B.CROCE 270B LOC.CHIETI SCALO</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,39 +2549,39 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="G40" s="12" t="n">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="H40" s="12" t="n">
-        <v>26</v>
+        <v>61</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>28</v>
+        <v>74</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>192</v>
+        <v>209</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2612,28 +2612,28 @@
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>135</v>
+        <v>140</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="N41" s="12" t="n">
         <v>1</v>
@@ -2647,7 +2647,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>CORSO FRANCIA</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,56 +2667,56 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>24</v>
+        <v>116</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>331</v>
+        <v>86</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>07270</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>CAMPOBASSO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>IV NOVEMBRE</t>
+          <t>CORSO FRANCIA</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2726,39 +2726,39 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>COLOZZA STEFANO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>131</v>
+        <v>166</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>11</v>
+        <v>71</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>76</v>
+        <v>110</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>33</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>71</v>
+        <v>353</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -2789,31 +2789,31 @@
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
@@ -2824,17 +2824,17 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>07224</t>
+          <t>07270</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CAMPOBASSO</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
+          <t>IV NOVEMBRE</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -2844,46 +2844,46 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>COLOZZA STEFANO</t>
         </is>
       </c>
       <c r="F45" s="12" t="n">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="G45" s="12" t="n">
-        <v>103</v>
+        <v>135</v>
       </c>
       <c r="H45" s="12" t="n">
-        <v>92</v>
+        <v>11</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>85</v>
+        <v>11</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="K45" s="12" t="n">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="L45" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="M45" s="12" t="n">
+        <v>79</v>
+      </c>
+      <c r="N45" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="M45" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="N45" s="12" t="n">
-        <v>63</v>
-      </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>07224</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>CIRCONVALLAZIONE GIANICOLENSE 340</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -2903,35 +2903,35 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>111</v>
       </c>
       <c r="H46" s="12" t="n">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>78</v>
+        <v>103</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>13</v>
+        <v>66</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
@@ -2966,28 +2966,28 @@
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>87</v>
+        <v>92</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="H47" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="N47" s="12" t="n">
         <v>2</v>
@@ -3025,28 +3025,28 @@
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>18</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>206</v>
+        <v>214</v>
       </c>
       <c r="N48" s="12" t="n">
         <v>0</v>
@@ -3084,19 +3084,19 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="G49" s="12" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="H49" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>16</v>
@@ -3105,14 +3105,14 @@
         <v>25</v>
       </c>
       <c r="M49" s="12" t="n">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="N49" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -3143,35 +3143,35 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H50" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I50" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="K50" s="12" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="L50" s="12" t="n">
         <v>14</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>7</v>
@@ -3214,7 +3214,7 @@
         <v>7</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>20</v>
@@ -3223,14 +3223,14 @@
         <v>22</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>1</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3264,13 +3264,13 @@
         <v>74</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H52" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J52" s="12" t="n">
         <v>45</v>
@@ -3282,7 +3282,7 @@
         <v>19</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="N52" s="12" t="n">
         <v>0</v>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>06622</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>CEPRANO</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 104+320</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,56 +3316,56 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>67</v>
+        <v>165</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>45</v>
+        <v>7</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>84</v>
+        <v>171</v>
       </c>
       <c r="N53" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>06622</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>CEPRANO</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>VIA CASILINA KM 104+320</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3375,39 +3375,39 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F54" s="12" t="n">
+        <v>73</v>
+      </c>
+      <c r="G54" s="12" t="n">
         <v>71</v>
       </c>
-      <c r="G54" s="12" t="n">
-        <v>159</v>
-      </c>
       <c r="H54" s="12" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="I54" s="12" t="n">
-        <v>6</v>
+        <v>47</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>42</v>
+        <v>59</v>
       </c>
       <c r="K54" s="12" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="N54" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3438,28 +3438,28 @@
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I55" s="12" t="n">
         <v>59</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="L55" s="12" t="n">
         <v>7</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N55" s="12" t="n">
         <v>0</v>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,32 +3493,32 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>96</v>
+        <v>111</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>75</v>
+        <v>5</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>15</v>
+        <v>39</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="N56" s="12" t="n">
         <v>1</v>
@@ -3532,17 +3532,17 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+          <t>S.PROV.ALLACCIANTE</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3556,52 +3556,52 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="G57" s="12" t="n">
-        <v>110</v>
+        <v>1</v>
       </c>
       <c r="H57" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="I57" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>23</v>
+        <v>65</v>
       </c>
       <c r="K57" s="12" t="n">
-        <v>5</v>
+        <v>32</v>
       </c>
       <c r="L57" s="12" t="n">
-        <v>38</v>
+        <v>1</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>117</v>
+        <v>82</v>
       </c>
       <c r="N57" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>17315</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>S.PROV.ALLACCIANTE</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,56 +3611,56 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>1</v>
+        <v>101</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>0</v>
+        <v>78</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>75</v>
+        <v>126</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>94</v>
+        <v>61</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>35</v>
+        <v>68</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>26</v>
+        <v>5</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>98</v>
+        <v>266</v>
       </c>
       <c r="N59" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,56 +3729,56 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>59</v>
+        <v>101</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="I60" s="12" t="n">
-        <v>27</v>
+        <v>12</v>
       </c>
       <c r="J60" s="12" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="K60" s="12" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="L60" s="12" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>250</v>
+        <v>117</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,32 +3788,32 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I61" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J61" s="12" t="n">
+        <v>35</v>
+      </c>
+      <c r="K61" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J61" s="12" t="n">
-        <v>44</v>
-      </c>
-      <c r="K61" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="L61" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="N61" s="12" t="n">
         <v>0</v>
@@ -3827,7 +3827,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
+        <v>57</v>
+      </c>
+      <c r="G62" s="12" t="n">
+        <v>65</v>
+      </c>
+      <c r="H62" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="I62" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="J62" s="12" t="n">
         <v>53</v>
       </c>
-      <c r="G62" s="12" t="n">
-        <v>144</v>
-      </c>
-      <c r="H62" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I62" s="12" t="n">
-        <v>38</v>
-      </c>
-      <c r="J62" s="12" t="n">
-        <v>45</v>
-      </c>
       <c r="K62" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,39 +3906,39 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>60</v>
+        <v>104</v>
       </c>
       <c r="H63" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="I63" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J63" s="12" t="n">
+        <v>42</v>
+      </c>
+      <c r="K63" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="L63" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="I63" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J63" s="12" t="n">
-        <v>48</v>
-      </c>
-      <c r="K63" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="L63" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="M63" s="12" t="n">
-        <v>136</v>
+        <v>70</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -3969,35 +3969,35 @@
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="G64" s="12" t="n">
         <v>1</v>
       </c>
       <c r="H64" s="12" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="I64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4028,28 +4028,28 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="L65" s="12" t="n">
         <v>15</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N65" s="12" t="n">
         <v>2</v>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>SS 430 KM 0.525</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>101</v>
+        <v>153</v>
       </c>
       <c r="H66" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I66" s="12" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="J66" s="12" t="n">
-        <v>39</v>
+        <v>46</v>
       </c>
       <c r="K66" s="12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="L66" s="12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="M66" s="12" t="n">
-        <v>65</v>
+        <v>231</v>
       </c>
       <c r="N66" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4146,31 +4146,31 @@
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
@@ -4205,28 +4205,28 @@
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="L68" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="N68" s="12" t="n">
         <v>4</v>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>45</v>
+        <v>4</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>4</v>
+        <v>48</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="K70" s="12" t="n">
         <v>11</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>68</v>
+        <v>80</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>1</v>
+        <v>23</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,35 +4378,35 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I71" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J71" s="12" t="n">
+        <v>47</v>
+      </c>
+      <c r="K71" s="12" t="n">
         <v>24</v>
       </c>
-      <c r="K71" s="12" t="n">
+      <c r="L71" s="12" t="n">
         <v>4</v>
       </c>
-      <c r="L71" s="12" t="n">
-        <v>23</v>
-      </c>
       <c r="M71" s="12" t="n">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
@@ -4417,17 +4417,17 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,35 +4437,35 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="I72" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J72" s="12" t="n">
+        <v>26</v>
+      </c>
+      <c r="K72" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J72" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K72" s="12" t="n">
-        <v>21</v>
-      </c>
       <c r="L72" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="N72" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
@@ -4476,17 +4476,17 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>07431</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>ORVIETO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>S.S.205 KM.52+330</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4496,56 +4496,56 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>CHIODI ROBERTO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>75</v>
+        <v>3</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>40</v>
+        <v>1</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>06642</t>
+          <t>07431</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>CASTROCIELO</t>
+          <t>ORVIETO</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>S.P. LEUCIANA KM 2+670</t>
+          <t>S.S.205 KM.52+330</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4555,56 +4555,56 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>CHIODI ROBERTO</t>
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>49</v>
+        <v>77</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="I74" s="12" t="n">
-        <v>9</v>
+        <v>40</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="K74" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="L74" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="L74" s="12" t="n">
-        <v>2</v>
-      </c>
       <c r="M74" s="12" t="n">
-        <v>37</v>
+        <v>104</v>
       </c>
       <c r="N74" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>06642</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>CASTROCIELO</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>S.P. LEUCIANA KM 2+670</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4614,56 +4614,56 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="G75" s="12" t="n">
+        <v>49</v>
+      </c>
+      <c r="H75" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I75" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="J75" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="K75" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="L75" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="H75" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="I75" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="J75" s="12" t="n">
-        <v>42</v>
-      </c>
-      <c r="K75" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="L75" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="M75" s="12" t="n">
-        <v>78</v>
+        <v>37</v>
       </c>
       <c r="N75" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,39 +4673,39 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>92</v>
+        <v>0</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>171</v>
+        <v>36</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -4736,52 +4736,52 @@
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H77" s="12" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="I77" s="12" t="n">
         <v>18</v>
       </c>
       <c r="J77" s="12" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="K77" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="L77" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4791,56 +4791,56 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>0</v>
+        <v>96</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>33</v>
+        <v>195</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,56 +4850,56 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G79" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="H79" s="12" t="n">
+        <v>25</v>
+      </c>
+      <c r="I79" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J79" s="12" t="n">
+        <v>32</v>
+      </c>
+      <c r="K79" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="L79" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M79" s="12" t="n">
         <v>63</v>
       </c>
-      <c r="H79" s="12" t="n">
-        <v>4</v>
-      </c>
-      <c r="I79" s="12" t="n">
-        <v>23</v>
-      </c>
-      <c r="J79" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="K79" s="12" t="n">
-        <v>7</v>
-      </c>
-      <c r="L79" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="M79" s="12" t="n">
-        <v>68</v>
-      </c>
       <c r="N79" s="12" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,35 +4909,35 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>120</v>
+        <v>69</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
@@ -4948,17 +4948,17 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,35 +4968,35 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>37</v>
+        <v>72</v>
       </c>
       <c r="H81" s="12" t="n">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="I81" s="12" t="n">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="J81" s="12" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="K81" s="12" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="L81" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M81" s="12" t="n">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -5007,17 +5007,17 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>26619</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>SAN GIOVANNI TEATINO</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>PRENESTINA EST</t>
+          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5027,32 +5027,32 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>PACI CLAUDIO</t>
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="H82" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I82" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J82" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="K82" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J82" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="K82" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="L82" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="M82" s="12" t="n">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="N82" s="12" t="n">
         <v>0</v>
@@ -5066,17 +5066,17 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA KM. 29,700 SNC</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5086,56 +5086,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G83" s="12" t="n">
+        <v>38</v>
+      </c>
+      <c r="H83" s="12" t="n">
+        <v>37</v>
+      </c>
+      <c r="I83" s="12" t="n">
+        <v>64</v>
+      </c>
+      <c r="J83" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="K83" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="L83" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="M83" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H83" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="I83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="12" t="n">
-        <v>21</v>
-      </c>
-      <c r="K83" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="L83" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="N83" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>26619</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>SAN GIOVANNI TEATINO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>LOC. DRAGONARA VIA NENNI  SNC</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,56 +5145,56 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>PACI CLAUDIO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>33</v>
+        <v>4</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I84" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J84" s="12" t="n">
+        <v>22</v>
+      </c>
+      <c r="K84" s="12" t="n">
         <v>6</v>
       </c>
-      <c r="J84" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="K84" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="L84" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>06607</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>SAN SALVO</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>FRAZ-MARINELLE</t>
+          <t>VIA FLAMINIA KM. 29,700 SNC</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5204,23 +5204,23 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I85" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K85" s="12" t="n">
         <v>6</v>
@@ -5229,31 +5229,31 @@
         <v>0</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>09267</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>LESINA</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA PER RODI</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,56 +5263,56 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>CASCIANI GABRIELE</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>1</v>
+        <v>18</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K86" s="12" t="n">
         <v>4</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>14</v>
+        <v>44</v>
       </c>
       <c r="N86" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>06607</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>SAN SALVO</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
+          <t>FRAZ-MARINELLE</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5322,56 +5322,56 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F87" s="12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G87" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="H87" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="I87" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="K87" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="L87" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M87" s="12" t="n">
-        <v>38</v>
+        <v>17</v>
       </c>
       <c r="N87" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>09267</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>LESINA</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>SUPERSTRADA PER RODI</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5381,39 +5381,39 @@
       </c>
       <c r="E88" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASCIANI GABRIELE</t>
         </is>
       </c>
       <c r="F88" s="12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="H88" s="12" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="I88" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="K88" s="12" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="L88" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>61</v>
+        <v>14</v>
       </c>
       <c r="N88" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5465,14 +5465,14 @@
         <v>0</v>
       </c>
       <c r="M89" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N89" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
         <v>3</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="N90" s="12" t="n">
         <v>0</v>
@@ -5565,13 +5565,13 @@
         <v>10</v>
       </c>
       <c r="G91" s="12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="H91" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I91" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J91" s="12" t="n">
         <v>9</v>
@@ -5583,7 +5583,7 @@
         <v>3</v>
       </c>
       <c r="M91" s="12" t="n">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="N91" s="12" t="n">
         <v>2</v>
@@ -5642,7 +5642,7 @@
         <v>0</v>
       </c>
       <c r="M92" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="N92" s="12" t="n">
         <v>0</v>
@@ -5860,7 +5860,7 @@
         <v>2</v>
       </c>
       <c r="G96" s="12" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="H96" s="12" t="n">
         <v>0</v>

--- a/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
+++ b/docs/files/REPORT_FILTRI/Agente - Marcelli Mirko.xlsx
@@ -684,13 +684,13 @@
         <v>86</v>
       </c>
       <c r="B7" s="8" t="n">
-        <v>9737</v>
+        <v>9749</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7384</v>
+        <v>0</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>2863</v>
+        <v>2808</v>
       </c>
       <c r="E7" s="2" t="n"/>
       <c r="F7" s="2" t="n"/>
@@ -842,19 +842,19 @@
         </is>
       </c>
       <c r="F11" s="12" t="n">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="G11" s="12" t="n">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="H11" s="12" t="n">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="I11" s="12" t="n">
         <v>156</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>437</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>185</v>
@@ -863,10 +863,10 @@
         <v>134</v>
       </c>
       <c r="M11" s="12" t="n">
-        <v>908</v>
+        <v>903</v>
       </c>
       <c r="N11" s="12" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -901,10 +901,10 @@
         </is>
       </c>
       <c r="F12" s="12" t="n">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>91</v>
@@ -913,7 +913,7 @@
         <v>63</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>377</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>198</v>
@@ -922,10 +922,10 @@
         <v>86</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="N12" s="12" t="n">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
@@ -960,19 +960,19 @@
         </is>
       </c>
       <c r="F13" s="12" t="n">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>424</v>
+        <v>417</v>
       </c>
       <c r="H13" s="12" t="n">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>342</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>137</v>
@@ -981,10 +981,10 @@
         <v>84</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>706</v>
+        <v>687</v>
       </c>
       <c r="N13" s="12" t="n">
-        <v>609</v>
+        <v>592</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="F14" s="12" t="n">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>389</v>
+        <v>376</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="I14" s="12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="J14" s="12" t="n">
-        <v>242</v>
+        <v>0</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>108</v>
@@ -1040,10 +1040,10 @@
         <v>97</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="N14" s="12" t="n">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
@@ -1078,19 +1078,19 @@
         </is>
       </c>
       <c r="F15" s="12" t="n">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H15" s="12" t="n">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>204</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>75</v>
@@ -1099,10 +1099,10 @@
         <v>122</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="N15" s="12" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="F16" s="12" t="n">
-        <v>273</v>
+        <v>267</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="H16" s="12" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>219</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
         <v>104</v>
@@ -1158,14 +1158,14 @@
         <v>48</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="N16" s="12" t="n">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1196,10 +1196,10 @@
         </is>
       </c>
       <c r="F17" s="12" t="n">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>277</v>
+        <v>271</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>25</v>
@@ -1208,7 +1208,7 @@
         <v>18</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
         <v>64</v>
@@ -1217,7 +1217,7 @@
         <v>74</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="N17" s="12" t="n">
         <v>53</v>
@@ -1231,17 +1231,17 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>51887</t>
+          <t>57149</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>SAN CESAREO</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>VIA SALVO D'ACQUISTO 121</t>
+          <t>VIA CASILINA KM. 24+950</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1251,39 +1251,39 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F18" s="12" t="n">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G18" s="12" t="n">
-        <v>227</v>
+        <v>312</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>64</v>
+        <v>32</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>112</v>
+        <v>40</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>192</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
-        <v>109</v>
+        <v>59</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="M18" s="12" t="n">
-        <v>153</v>
+        <v>362</v>
       </c>
       <c r="N18" s="12" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -1314,19 +1314,19 @@
         </is>
       </c>
       <c r="F19" s="12" t="n">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="G19" s="12" t="n">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="H19" s="12" t="n">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="I19" s="12" t="n">
         <v>188</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>172</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>69</v>
@@ -1335,7 +1335,7 @@
         <v>56</v>
       </c>
       <c r="M19" s="12" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="N19" s="12" t="n">
         <v>18</v>
@@ -1349,17 +1349,17 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>57149</t>
+          <t>51887</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>SAN CESAREO</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM. 24+950</t>
+          <t>VIA SALVO D'ACQUISTO 121</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -1369,39 +1369,39 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>323</v>
+        <v>219</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>40</v>
+        <v>105</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>59</v>
+        <v>109</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>368</v>
+        <v>150</v>
       </c>
       <c r="N20" s="12" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1435,7 +1435,7 @@
         <v>221</v>
       </c>
       <c r="G21" s="12" t="n">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H21" s="12" t="n">
         <v>24</v>
@@ -1444,7 +1444,7 @@
         <v>12</v>
       </c>
       <c r="J21" s="12" t="n">
-        <v>197</v>
+        <v>0</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>89</v>
@@ -1453,10 +1453,10 @@
         <v>24</v>
       </c>
       <c r="M21" s="12" t="n">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="N21" s="12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
@@ -1491,10 +1491,10 @@
         </is>
       </c>
       <c r="F22" s="12" t="n">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G22" s="12" t="n">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H22" s="12" t="n">
         <v>120</v>
@@ -1503,7 +1503,7 @@
         <v>35</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>188</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>107</v>
@@ -1512,31 +1512,31 @@
         <v>31</v>
       </c>
       <c r="M22" s="12" t="n">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="N22" s="12" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>07268</t>
+          <t>07088</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>TERMOLI</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
+          <t>CORSO DI FRANCIA 80</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -1546,56 +1546,56 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>D'ANNIBALE EMANUELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F23" s="12" t="n">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>111</v>
+        <v>244</v>
       </c>
       <c r="H23" s="12" t="n">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>173</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
-        <v>63</v>
+        <v>46</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="M23" s="12" t="n">
-        <v>106</v>
+        <v>297</v>
       </c>
       <c r="N23" s="12" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>07088</t>
+          <t>07268</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>TERMOLI</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>CORSO DI FRANCIA 80</t>
+          <t>VIA MARTIRI DELLA RESISTENZA, 67</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -1605,39 +1605,39 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>D'ANNIBALE EMANUELE</t>
         </is>
       </c>
       <c r="F24" s="12" t="n">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="G24" s="12" t="n">
-        <v>250</v>
+        <v>106</v>
       </c>
       <c r="H24" s="12" t="n">
-        <v>71</v>
+        <v>56</v>
       </c>
       <c r="I24" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J24" s="12" t="n">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="K24" s="12" t="n">
-        <v>46</v>
+        <v>63</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="M24" s="12" t="n">
-        <v>301</v>
+        <v>106</v>
       </c>
       <c r="N24" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -1668,19 +1668,19 @@
         </is>
       </c>
       <c r="F25" s="12" t="n">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G25" s="12" t="n">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="H25" s="12" t="n">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="I25" s="12" t="n">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J25" s="12" t="n">
-        <v>144</v>
+        <v>0</v>
       </c>
       <c r="K25" s="12" t="n">
         <v>47</v>
@@ -1689,7 +1689,7 @@
         <v>55</v>
       </c>
       <c r="M25" s="12" t="n">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="N25" s="12" t="n">
         <v>3</v>
@@ -1727,19 +1727,19 @@
         </is>
       </c>
       <c r="F26" s="12" t="n">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G26" s="12" t="n">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="H26" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I26" s="12" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="J26" s="12" t="n">
-        <v>148</v>
+        <v>0</v>
       </c>
       <c r="K26" s="12" t="n">
         <v>62</v>
@@ -1748,7 +1748,7 @@
         <v>42</v>
       </c>
       <c r="M26" s="12" t="n">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="N26" s="12" t="n">
         <v>21</v>
@@ -1762,17 +1762,17 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>53854</t>
+          <t>06621</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>LORETO</t>
+          <t>CASSINO</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>MANZONI LOC. VILLA PAPA</t>
+          <t>VIA CASILINA SUD KM 140+200</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -1782,56 +1782,56 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F27" s="12" t="n">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G27" s="12" t="n">
-        <v>181</v>
+        <v>213</v>
       </c>
       <c r="H27" s="12" t="n">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="I27" s="12" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="J27" s="12" t="n">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="K27" s="12" t="n">
-        <v>58</v>
+        <v>27</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>31</v>
+        <v>66</v>
       </c>
       <c r="M27" s="12" t="n">
-        <v>191</v>
+        <v>224</v>
       </c>
       <c r="N27" s="12" t="n">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06621</t>
+          <t>53808</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>CASSINO</t>
+          <t>FANO</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA SUD KM 140+200</t>
+          <t>VIA E. MATTEI, 28</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -1841,32 +1841,32 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F28" s="12" t="n">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="G28" s="12" t="n">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="H28" s="12" t="n">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>119</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M28" s="12" t="n">
-        <v>226</v>
+        <v>257</v>
       </c>
       <c r="N28" s="12" t="n">
         <v>9</v>
@@ -1880,17 +1880,17 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>53808</t>
+          <t>53854</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>FANO</t>
+          <t>LORETO</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>VIA E. MATTEI, 28</t>
+          <t>MANZONI LOC. VILLA PAPA</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -1900,39 +1900,39 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F29" s="12" t="n">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="G29" s="12" t="n">
-        <v>230</v>
+        <v>173</v>
       </c>
       <c r="H29" s="12" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="I29" s="12" t="n">
+        <v>68</v>
+      </c>
+      <c r="J29" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="12" t="n">
+        <v>58</v>
+      </c>
+      <c r="L29" s="12" t="n">
+        <v>31</v>
+      </c>
+      <c r="M29" s="12" t="n">
+        <v>183</v>
+      </c>
+      <c r="N29" s="12" t="n">
         <v>40</v>
       </c>
-      <c r="J29" s="12" t="n">
-        <v>112</v>
-      </c>
-      <c r="K29" s="12" t="n">
-        <v>28</v>
-      </c>
-      <c r="L29" s="12" t="n">
-        <v>70</v>
-      </c>
-      <c r="M29" s="12" t="n">
-        <v>257</v>
-      </c>
-      <c r="N29" s="12" t="n">
-        <v>9</v>
-      </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -1963,19 +1963,19 @@
         </is>
       </c>
       <c r="F30" s="12" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G30" s="12" t="n">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="H30" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>84</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>25</v>
@@ -1984,10 +1984,10 @@
         <v>96</v>
       </c>
       <c r="M30" s="12" t="n">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="N30" s="12" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
@@ -2022,19 +2022,19 @@
         </is>
       </c>
       <c r="F31" s="12" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="G31" s="12" t="n">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H31" s="12" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="I31" s="12" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="J31" s="12" t="n">
-        <v>88</v>
+        <v>0</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>23</v>
@@ -2043,7 +2043,7 @@
         <v>71</v>
       </c>
       <c r="M31" s="12" t="n">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="N31" s="12" t="n">
         <v>4</v>
@@ -2057,17 +2057,17 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06965</t>
+          <t>16968</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>FIANO ROMANO</t>
+          <t>FIUMICINO</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>S.S.4 DIR. KM. 3 + 400</t>
+          <t>VIA PORTUENSE 2468</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2077,56 +2077,56 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F32" s="12" t="n">
         <v>156</v>
       </c>
       <c r="G32" s="12" t="n">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="H32" s="12" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="I32" s="12" t="n">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="J32" s="12" t="n">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="K32" s="12" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="M32" s="12" t="n">
-        <v>213</v>
+        <v>166</v>
       </c>
       <c r="N32" s="12" t="n">
-        <v>45</v>
+        <v>2</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>16968</t>
+          <t>17111</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>FIUMICINO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>VIA PORTUENSE 2468</t>
+          <t>SS SALARIA KM 14, 895 EST</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2136,56 +2136,56 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F33" s="12" t="n">
         <v>155</v>
       </c>
       <c r="G33" s="12" t="n">
-        <v>189</v>
+        <v>120</v>
       </c>
       <c r="H33" s="12" t="n">
-        <v>47</v>
+        <v>16</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>131</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>25</v>
+        <v>69</v>
       </c>
       <c r="M33" s="12" t="n">
-        <v>172</v>
+        <v>229</v>
       </c>
       <c r="N33" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>17111</t>
+          <t>06965</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FIANO ROMANO</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>SS SALARIA KM 14, 895 EST</t>
+          <t>S.S.4 DIR. KM. 3 + 400</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2195,56 +2195,56 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F34" s="12" t="n">
         <v>154</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>128</v>
+        <v>54</v>
       </c>
       <c r="H34" s="12" t="n">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>35</v>
+        <v>60</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>230</v>
+        <v>209</v>
       </c>
       <c r="N34" s="12" t="n">
-        <v>12</v>
+        <v>44</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07473</t>
+          <t>06669</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>MONTEFIASCONE</t>
+          <t>ANAGNI</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA KM 97+800</t>
+          <t>RACCORDO AUTOSOLE</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2254,35 +2254,35 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F35" s="12" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="G35" s="12" t="n">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="H35" s="12" t="n">
-        <v>65</v>
+        <v>113</v>
       </c>
       <c r="I35" s="12" t="n">
-        <v>95</v>
+        <v>171</v>
       </c>
       <c r="J35" s="12" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="K35" s="12" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="M35" s="12" t="n">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="N35" s="12" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
@@ -2293,17 +2293,17 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06669</t>
+          <t>07473</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>ANAGNI</t>
+          <t>MONTEFIASCONE</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>RACCORDO AUTOSOLE</t>
+          <t>SS 2 CASSIA KM 97+800</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2313,35 +2313,35 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F36" s="12" t="n">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="G36" s="12" t="n">
-        <v>118</v>
+        <v>131</v>
       </c>
       <c r="H36" s="12" t="n">
-        <v>115</v>
+        <v>63</v>
       </c>
       <c r="I36" s="12" t="n">
-        <v>171</v>
+        <v>95</v>
       </c>
       <c r="J36" s="12" t="n">
-        <v>118</v>
+        <v>0</v>
       </c>
       <c r="K36" s="12" t="n">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>34</v>
+        <v>16</v>
       </c>
       <c r="M36" s="12" t="n">
-        <v>77</v>
+        <v>46</v>
       </c>
       <c r="N36" s="12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
@@ -2376,19 +2376,19 @@
         </is>
       </c>
       <c r="F37" s="12" t="n">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G37" s="12" t="n">
-        <v>176</v>
+        <v>170</v>
       </c>
       <c r="H37" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="I37" s="12" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="J37" s="12" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>38</v>
@@ -2397,7 +2397,7 @@
         <v>24</v>
       </c>
       <c r="M37" s="12" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N37" s="12" t="n">
         <v>3</v>
@@ -2435,7 +2435,7 @@
         </is>
       </c>
       <c r="F38" s="12" t="n">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>183</v>
@@ -2447,7 +2447,7 @@
         <v>57</v>
       </c>
       <c r="J38" s="12" t="n">
-        <v>101</v>
+        <v>0</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>41</v>
@@ -2456,7 +2456,7 @@
         <v>42</v>
       </c>
       <c r="M38" s="12" t="n">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="N38" s="12" t="n">
         <v>2</v>
@@ -2494,10 +2494,10 @@
         </is>
       </c>
       <c r="F39" s="12" t="n">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="G39" s="12" t="n">
-        <v>123</v>
+        <v>116</v>
       </c>
       <c r="H39" s="12" t="n">
         <v>28</v>
@@ -2506,7 +2506,7 @@
         <v>35</v>
       </c>
       <c r="J39" s="12" t="n">
-        <v>96</v>
+        <v>0</v>
       </c>
       <c r="K39" s="12" t="n">
         <v>18</v>
@@ -2515,7 +2515,7 @@
         <v>43</v>
       </c>
       <c r="M39" s="12" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="N39" s="12" t="n">
         <v>29</v>
@@ -2529,17 +2529,17 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>24529</t>
+          <t>07364</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>PERUGIA</t>
+          <t>ROSETO DEGLI ABRUZZI</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>VIA P. SORIANO</t>
+          <t>VIA NAZIONALE SUD 617</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -2549,56 +2549,56 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>SCHIETROMA GIANLUCA</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F40" s="12" t="n">
+        <v>138</v>
+      </c>
+      <c r="G40" s="12" t="n">
         <v>137</v>
       </c>
-      <c r="G40" s="12" t="n">
-        <v>179</v>
-      </c>
       <c r="H40" s="12" t="n">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="I40" s="12" t="n">
-        <v>74</v>
+        <v>23</v>
       </c>
       <c r="J40" s="12" t="n">
-        <v>94</v>
+        <v>0</v>
       </c>
       <c r="K40" s="12" t="n">
-        <v>39</v>
+        <v>13</v>
       </c>
       <c r="L40" s="12" t="n">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="M40" s="12" t="n">
-        <v>209</v>
+        <v>121</v>
       </c>
       <c r="N40" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07364</t>
+          <t>24529</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>ROSETO DEGLI ABRUZZI</t>
+          <t>PERUGIA</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE SUD 617</t>
+          <t>VIA P. SORIANO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -2608,46 +2608,46 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>SCHIETROMA GIANLUCA</t>
         </is>
       </c>
       <c r="F41" s="12" t="n">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>140</v>
+        <v>172</v>
       </c>
       <c r="H41" s="12" t="n">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="I41" s="12" t="n">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="J41" s="12" t="n">
-        <v>57</v>
+        <v>0</v>
       </c>
       <c r="K41" s="12" t="n">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>81</v>
+        <v>42</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>124</v>
+        <v>208</v>
       </c>
       <c r="N41" s="12" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>57176</t>
+          <t>80008</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA KM 12+943, 1423</t>
+          <t>CORSO FRANCIA</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -2667,46 +2667,46 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F42" s="12" t="n">
-        <v>120</v>
+        <v>125</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>0</v>
+        <v>158</v>
       </c>
       <c r="H42" s="12" t="n">
-        <v>116</v>
+        <v>25</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>86</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>86</v>
+        <v>346</v>
       </c>
       <c r="N42" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>80008</t>
+          <t>07221</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2716,7 +2716,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>CORSO FRANCIA</t>
+          <t>VIA TAGLIAMENTO 0049</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -2730,31 +2730,31 @@
         </is>
       </c>
       <c r="F43" s="12" t="n">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="G43" s="12" t="n">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="H43" s="12" t="n">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="I43" s="12" t="n">
-        <v>71</v>
+        <v>48</v>
       </c>
       <c r="J43" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="K43" s="12" t="n">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M43" s="12" t="n">
-        <v>353</v>
+        <v>212</v>
       </c>
       <c r="N43" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07221</t>
+          <t>57176</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2775,7 +2775,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>VIA TAGLIAMENTO 0049</t>
+          <t>VIA CASILINA KM 12+943, 1423</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -2785,39 +2785,39 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F44" s="12" t="n">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>171</v>
+        <v>0</v>
       </c>
       <c r="H44" s="12" t="n">
-        <v>48</v>
+        <v>116</v>
       </c>
       <c r="I44" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="J44" s="12" t="n">
-        <v>107</v>
+        <v>0</v>
       </c>
       <c r="K44" s="12" t="n">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>217</v>
+        <v>86</v>
       </c>
       <c r="N44" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
@@ -2857,10 +2857,10 @@
         <v>11</v>
       </c>
       <c r="I45" s="12" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="J45" s="12" t="n">
-        <v>79</v>
+        <v>0</v>
       </c>
       <c r="K45" s="12" t="n">
         <v>34</v>
@@ -2869,7 +2869,7 @@
         <v>35</v>
       </c>
       <c r="M45" s="12" t="n">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="N45" s="12" t="n">
         <v>2</v>
@@ -2907,7 +2907,7 @@
         </is>
       </c>
       <c r="F46" s="12" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="G46" s="12" t="n">
         <v>111</v>
@@ -2919,7 +2919,7 @@
         <v>90</v>
       </c>
       <c r="J46" s="12" t="n">
-        <v>103</v>
+        <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
         <v>68</v>
@@ -2928,31 +2928,31 @@
         <v>3</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N46" s="12" t="n">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>07390</t>
+          <t>05712</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>TERAMO</t>
+          <t>ANCONA</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>SS 80 KM 77+842</t>
+          <t>VIA DELLA MONTAGNOLA N.24</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -2962,56 +2962,56 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>CAIMMI ANDREA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F47" s="12" t="n">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G47" s="12" t="n">
-        <v>113</v>
+        <v>146</v>
       </c>
       <c r="H47" s="12" t="n">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="I47" s="12" t="n">
-        <v>8</v>
+        <v>134</v>
       </c>
       <c r="J47" s="12" t="n">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="K47" s="12" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="M47" s="12" t="n">
-        <v>153</v>
+        <v>214</v>
       </c>
       <c r="N47" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>05712</t>
+          <t>07390</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>ANCONA</t>
+          <t>TERAMO</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA MONTAGNOLA N.24</t>
+          <t>SS 80 KM 77+842</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3021,35 +3021,35 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>CAIMMI ANDREA</t>
         </is>
       </c>
       <c r="F48" s="12" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G48" s="12" t="n">
-        <v>148</v>
+        <v>108</v>
       </c>
       <c r="H48" s="12" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>66</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="M48" s="12" t="n">
-        <v>214</v>
+        <v>151</v>
       </c>
       <c r="N48" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
@@ -3084,7 +3084,7 @@
         </is>
       </c>
       <c r="F49" s="12" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>70</v>
@@ -3096,7 +3096,7 @@
         <v>13</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>56</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>16</v>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3143,10 +3143,10 @@
         </is>
       </c>
       <c r="F50" s="12" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G50" s="12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="H50" s="12" t="n">
         <v>19</v>
@@ -3155,7 +3155,7 @@
         <v>6</v>
       </c>
       <c r="J50" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="K50" s="12" t="n">
         <v>27</v>
@@ -3164,10 +3164,10 @@
         <v>14</v>
       </c>
       <c r="M50" s="12" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="N50" s="12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
@@ -3202,10 +3202,10 @@
         </is>
       </c>
       <c r="F51" s="12" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G51" s="12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="H51" s="12" t="n">
         <v>7</v>
@@ -3214,7 +3214,7 @@
         <v>7</v>
       </c>
       <c r="J51" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="K51" s="12" t="n">
         <v>20</v>
@@ -3223,7 +3223,7 @@
         <v>22</v>
       </c>
       <c r="M51" s="12" t="n">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="N51" s="12" t="n">
         <v>1</v>
@@ -3237,17 +3237,17 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>27224</t>
+          <t>07299</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>CAMPAGNANO DI ROMA</t>
+          <t>GROTTAMMARE</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>SS 2 CASSIA BIS KM30</t>
+          <t>VIA BERNINI</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3257,35 +3257,35 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>MARIANI MARIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F52" s="12" t="n">
         <v>74</v>
       </c>
       <c r="G52" s="12" t="n">
-        <v>106</v>
+        <v>165</v>
       </c>
       <c r="H52" s="12" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="I52" s="12" t="n">
-        <v>49</v>
+        <v>7</v>
       </c>
       <c r="J52" s="12" t="n">
-        <v>45</v>
+        <v>0</v>
       </c>
       <c r="K52" s="12" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="L52" s="12" t="n">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="M52" s="12" t="n">
-        <v>92</v>
+        <v>169</v>
       </c>
       <c r="N52" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
@@ -3296,17 +3296,17 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07299</t>
+          <t>36953</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>GROTTAMMARE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>VIA BERNINI</t>
+          <t>VIA ELSA DE GIORGI</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3316,39 +3316,39 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F53" s="12" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G53" s="12" t="n">
-        <v>165</v>
+        <v>60</v>
       </c>
       <c r="H53" s="12" t="n">
-        <v>9</v>
+        <v>28</v>
       </c>
       <c r="I53" s="12" t="n">
-        <v>7</v>
+        <v>29</v>
       </c>
       <c r="J53" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K53" s="12" t="n">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>30</v>
+        <v>5</v>
       </c>
       <c r="M53" s="12" t="n">
-        <v>171</v>
+        <v>263</v>
       </c>
       <c r="N53" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -3379,19 +3379,19 @@
         </is>
       </c>
       <c r="F54" s="12" t="n">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="G54" s="12" t="n">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="H54" s="12" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="I54" s="12" t="n">
         <v>47</v>
       </c>
       <c r="J54" s="12" t="n">
-        <v>59</v>
+        <v>0</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>17</v>
@@ -3400,7 +3400,7 @@
         <v>13</v>
       </c>
       <c r="M54" s="12" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N54" s="12" t="n">
         <v>4</v>
@@ -3414,17 +3414,17 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>53866</t>
+          <t>17310</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>FALCONARA MARITTIMA</t>
+          <t>ASCOLI PICENO</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
+          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3434,35 +3434,35 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F55" s="12" t="n">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G55" s="12" t="n">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="H55" s="12" t="n">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="I55" s="12" t="n">
-        <v>59</v>
+        <v>4</v>
       </c>
       <c r="J55" s="12" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K55" s="12" t="n">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="L55" s="12" t="n">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="M55" s="12" t="n">
-        <v>64</v>
+        <v>123</v>
       </c>
       <c r="N55" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
@@ -3473,17 +3473,17 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>17310</t>
+          <t>53866</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>ASCOLI PICENO</t>
+          <t>FALCONARA MARITTIMA</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>SUPERSTRADA ASCOLI MARE KM.3</t>
+          <t>SS 16 KM 288+700 - VIA FLAMINIA  671 671</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3493,35 +3493,35 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F56" s="12" t="n">
         <v>67</v>
       </c>
       <c r="G56" s="12" t="n">
-        <v>111</v>
+        <v>89</v>
       </c>
       <c r="H56" s="12" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="I56" s="12" t="n">
-        <v>5</v>
+        <v>59</v>
       </c>
       <c r="J56" s="12" t="n">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="K56" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="L56" s="12" t="n">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="M56" s="12" t="n">
-        <v>124</v>
+        <v>63</v>
       </c>
       <c r="N56" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
         </is>
       </c>
       <c r="F57" s="12" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G57" s="12" t="n">
         <v>1</v>
@@ -3568,7 +3568,7 @@
         <v>0</v>
       </c>
       <c r="J57" s="12" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="K57" s="12" t="n">
         <v>32</v>
@@ -3577,31 +3577,31 @@
         <v>1</v>
       </c>
       <c r="M57" s="12" t="n">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="N57" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>06725</t>
+          <t>27224</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>LATINA</t>
+          <t>CAMPAGNANO DI ROMA</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>ISONZO</t>
+          <t>SS 2 CASSIA BIS KM30</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -3611,35 +3611,35 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>PROSPERI CHIARA</t>
+          <t>MARIANI MARIO</t>
         </is>
       </c>
       <c r="F58" s="12" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="G58" s="12" t="n">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="H58" s="12" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="I58" s="12" t="n">
-        <v>78</v>
+        <v>47</v>
       </c>
       <c r="J58" s="12" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="K58" s="12" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="L58" s="12" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="M58" s="12" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
       <c r="N58" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
@@ -3650,17 +3650,17 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>36953</t>
+          <t>06725</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>LATINA</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>VIA ELSA DE GIORGI</t>
+          <t>ISONZO</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -3670,56 +3670,56 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>PROSPERI CHIARA</t>
         </is>
       </c>
       <c r="F59" s="12" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G59" s="12" t="n">
-        <v>61</v>
+        <v>97</v>
       </c>
       <c r="H59" s="12" t="n">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="I59" s="12" t="n">
-        <v>29</v>
+        <v>78</v>
       </c>
       <c r="J59" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="K59" s="12" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="L59" s="12" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="M59" s="12" t="n">
-        <v>266</v>
+        <v>126</v>
       </c>
       <c r="N59" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>59331</t>
+          <t>05755</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>MONTALTO DI CASTRO</t>
+          <t>CAMERANO</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>S.S. 1 AURELIA SUD KM 107+200</t>
+          <t>FRAZ. ASPIO SS 16</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -3729,35 +3729,35 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F60" s="12" t="n">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="G60" s="12" t="n">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="H60" s="12" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I60" s="12" t="n">
+        <v>16</v>
+      </c>
+      <c r="J60" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="12" t="n">
         <v>12</v>
       </c>
-      <c r="J60" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K60" s="12" t="n">
-        <v>18</v>
-      </c>
       <c r="L60" s="12" t="n">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="M60" s="12" t="n">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="N60" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
@@ -3768,17 +3768,17 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>05755</t>
+          <t>58342</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>CAMERANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>FRAZ. ASPIO SS 16</t>
+          <t>VIA GROTTA PERFETTA 546</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -3788,35 +3788,35 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F61" s="12" t="n">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G61" s="12" t="n">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="H61" s="12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="I61" s="12" t="n">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="J61" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K61" s="12" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="L61" s="12" t="n">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="M61" s="12" t="n">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="N61" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
@@ -3827,17 +3827,17 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>58342</t>
+          <t>59331</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>MONTALTO DI CASTRO</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>VIA GROTTA PERFETTA 546</t>
+          <t>S.S. 1 AURELIA SUD KM 107+200</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -3847,56 +3847,56 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F62" s="12" t="n">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="G62" s="12" t="n">
-        <v>65</v>
+        <v>101</v>
       </c>
       <c r="H62" s="12" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="I62" s="12" t="n">
-        <v>26</v>
+        <v>12</v>
       </c>
       <c r="J62" s="12" t="n">
-        <v>53</v>
+        <v>0</v>
       </c>
       <c r="K62" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L62" s="12" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="M62" s="12" t="n">
-        <v>146</v>
+        <v>115</v>
       </c>
       <c r="N62" s="12" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>06659</t>
+          <t>05713</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>SAN VITTORE DEL LAZIO</t>
+          <t>OSIMO</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>SS 430 KM 0.525</t>
+          <t>VIA MARCO POLO 238</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -3906,35 +3906,35 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>PANZIRONI PATRIZIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F63" s="12" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G63" s="12" t="n">
-        <v>104</v>
+        <v>64</v>
       </c>
       <c r="H63" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="I63" s="12" t="n">
-        <v>7</v>
+        <v>31</v>
       </c>
       <c r="J63" s="12" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="K63" s="12" t="n">
+        <v>19</v>
+      </c>
+      <c r="L63" s="12" t="n">
         <v>15</v>
       </c>
-      <c r="L63" s="12" t="n">
-        <v>12</v>
-      </c>
       <c r="M63" s="12" t="n">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="N63" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
@@ -3945,17 +3945,17 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>07287</t>
+          <t>06659</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>SAN BENEDETTO DEL TRONTO</t>
+          <t>SAN VITTORE DEL LAZIO</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>VIA DELLA LIBERAZIONE SNC</t>
+          <t>SS 430 KM 0.525</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -3965,56 +3965,56 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>PANZIRONI PATRIZIO</t>
         </is>
       </c>
       <c r="F64" s="12" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G64" s="12" t="n">
+        <v>102</v>
+      </c>
+      <c r="H64" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="H64" s="12" t="n">
-        <v>29</v>
-      </c>
       <c r="I64" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J64" s="12" t="n">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="K64" s="12" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="L64" s="12" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="M64" s="12" t="n">
-        <v>54</v>
+        <v>63</v>
       </c>
       <c r="N64" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>05713</t>
+          <t>05766</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>OSIMO</t>
+          <t>FABRIANO</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>VIA MARCO POLO 238</t>
+          <t>PROV.LE ARCEVIESE</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4028,31 +4028,31 @@
         </is>
       </c>
       <c r="F65" s="12" t="n">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="G65" s="12" t="n">
-        <v>65</v>
+        <v>74</v>
       </c>
       <c r="H65" s="12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="I65" s="12" t="n">
-        <v>31</v>
+        <v>5</v>
       </c>
       <c r="J65" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K65" s="12" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L65" s="12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="M65" s="12" t="n">
-        <v>96</v>
+        <v>81</v>
       </c>
       <c r="N65" s="12" t="n">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>58258</t>
+          <t>53877</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>FERMO</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>VIA NOMENTANA, 850</t>
+          <t>VIA NAZIONALE 7 LOC.LIDO</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4083,35 +4083,35 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>ACHERMANN FRANCESCA</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F66" s="12" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="G66" s="12" t="n">
-        <v>153</v>
+        <v>101</v>
       </c>
       <c r="H66" s="12" t="n">
+        <v>9</v>
+      </c>
+      <c r="I66" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J66" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="L66" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="M66" s="12" t="n">
+        <v>120</v>
+      </c>
+      <c r="N66" s="12" t="n">
         <v>4</v>
-      </c>
-      <c r="I66" s="12" t="n">
-        <v>39</v>
-      </c>
-      <c r="J66" s="12" t="n">
-        <v>46</v>
-      </c>
-      <c r="K66" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="L66" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="M66" s="12" t="n">
-        <v>231</v>
-      </c>
-      <c r="N66" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
@@ -4122,17 +4122,17 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>05766</t>
+          <t>58258</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>FABRIANO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>PROV.LE ARCEVIESE</t>
+          <t>VIA NOMENTANA, 850</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4142,56 +4142,56 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>ACHERMANN FRANCESCA</t>
         </is>
       </c>
       <c r="F67" s="12" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G67" s="12" t="n">
-        <v>77</v>
+        <v>150</v>
       </c>
       <c r="H67" s="12" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="I67" s="12" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="J67" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K67" s="12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L67" s="12" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M67" s="12" t="n">
-        <v>81</v>
+        <v>221</v>
       </c>
       <c r="N67" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>53877</t>
+          <t>37019</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>FERMO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>VIA NAZIONALE 7 LOC.LIDO</t>
+          <t>VIA PARIDE STEFANINI 3</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4201,35 +4201,35 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>ERANDO FABIO</t>
         </is>
       </c>
       <c r="F68" s="12" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G68" s="12" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="H68" s="12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="I68" s="12" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="J68" s="12" t="n">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="K68" s="12" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="L68" s="12" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="M68" s="12" t="n">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N68" s="12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
@@ -4240,17 +4240,17 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>06101</t>
+          <t>55307</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>GABICCE MARE</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
+          <t>VIA CASILINA, 930</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4260,56 +4260,56 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>DI VIRGILIO DAVID</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F69" s="12" t="n">
         <v>50</v>
       </c>
       <c r="G69" s="12" t="n">
-        <v>100</v>
+        <v>3</v>
       </c>
       <c r="H69" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I69" s="12" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="J69" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K69" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L69" s="12" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="M69" s="12" t="n">
-        <v>72</v>
+        <v>84</v>
       </c>
       <c r="N69" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>27100</t>
+          <t>06101</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>GABICCE MARE</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA  110 110</t>
+          <t>S.S.16 KM 223+532 LOC.TA' PONTE TAVOLLO  S.N.</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4319,56 +4319,56 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>DI VIRGILIO DAVID</t>
         </is>
       </c>
       <c r="F70" s="12" t="n">
         <v>49</v>
       </c>
       <c r="G70" s="12" t="n">
-        <v>0</v>
+        <v>98</v>
       </c>
       <c r="H70" s="12" t="n">
-        <v>48</v>
+        <v>4</v>
       </c>
       <c r="I70" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J70" s="12" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="K70" s="12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L70" s="12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M70" s="12" t="n">
-        <v>80</v>
+        <v>71</v>
       </c>
       <c r="N70" s="12" t="n">
-        <v>23</v>
+        <v>1</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>37019</t>
+          <t>55811</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>POMEZIA</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>VIA PARIDE STEFANINI 3</t>
+          <t>VIA PONTINA KM 31+384</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4378,56 +4378,56 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>ERANDO FABIO</t>
+          <t>GIOVANNINI DANIELE</t>
         </is>
       </c>
       <c r="F71" s="12" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G71" s="12" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="H71" s="12" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="I71" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J71" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="J71" s="12" t="n">
-        <v>47</v>
-      </c>
-      <c r="K71" s="12" t="n">
-        <v>24</v>
-      </c>
       <c r="L71" s="12" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="M71" s="12" t="n">
-        <v>121</v>
+        <v>82</v>
       </c>
       <c r="N71" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>55811</t>
+          <t>07287</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>POMEZIA</t>
+          <t>SAN BENEDETTO DEL TRONTO</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>VIA PONTINA KM 31+384</t>
+          <t>VIA DELLA LIBERAZIONE SNC</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4437,46 +4437,46 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>GIOVANNINI DANIELE</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F72" s="12" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G72" s="12" t="n">
-        <v>68</v>
+        <v>0</v>
       </c>
       <c r="H72" s="12" t="n">
-        <v>2</v>
+        <v>27</v>
       </c>
       <c r="I72" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J72" s="12" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="K72" s="12" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L72" s="12" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="M72" s="12" t="n">
-        <v>84</v>
+        <v>54</v>
       </c>
       <c r="N72" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>55307</t>
+          <t>27100</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>VIA CASILINA, 930</t>
+          <t>VIA CASILINA  110 110</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4500,31 +4500,31 @@
         </is>
       </c>
       <c r="F73" s="12" t="n">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G73" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H73" s="12" t="n">
-        <v>7</v>
+        <v>47</v>
       </c>
       <c r="I73" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="12" t="n">
-        <v>47</v>
+        <v>0</v>
       </c>
       <c r="K73" s="12" t="n">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="L73" s="12" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="M73" s="12" t="n">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="N73" s="12" t="n">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="F74" s="12" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G74" s="12" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="H74" s="12" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="I74" s="12" t="n">
         <v>40</v>
       </c>
       <c r="J74" s="12" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="K74" s="12" t="n">
         <v>11</v>
@@ -4580,7 +4580,7 @@
         <v>12</v>
       </c>
       <c r="M74" s="12" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="N74" s="12" t="n">
         <v>1</v>
@@ -4618,7 +4618,7 @@
         </is>
       </c>
       <c r="F75" s="12" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="G75" s="12" t="n">
         <v>49</v>
@@ -4630,7 +4630,7 @@
         <v>9</v>
       </c>
       <c r="J75" s="12" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="K75" s="12" t="n">
         <v>12</v>
@@ -4639,31 +4639,31 @@
         <v>2</v>
       </c>
       <c r="M75" s="12" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N75" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>53882</t>
+          <t>36981</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>PORTO SAN GIORGIO</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>VIA ROSSELLI - SS 16  KM359+600</t>
+          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -4673,56 +4673,56 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>CASINI GIUSEPPE NICCOLO'</t>
         </is>
       </c>
       <c r="F76" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G76" s="12" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="H76" s="12" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="I76" s="12" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J76" s="12" t="n">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="K76" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L76" s="12" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M76" s="12" t="n">
-        <v>36</v>
+        <v>195</v>
       </c>
       <c r="N76" s="12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>16949</t>
+          <t>53882</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>PORTO SAN GIORGIO</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
+          <t>VIA ROSSELLI - SS 16  KM359+600</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -4732,46 +4732,46 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>LESTI LEONARDO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F77" s="12" t="n">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G77" s="12" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="H77" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="I77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="J77" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="12" t="n">
         <v>16</v>
-      </c>
-      <c r="I77" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="J77" s="12" t="n">
-        <v>27</v>
-      </c>
-      <c r="K77" s="12" t="n">
-        <v>9</v>
       </c>
       <c r="L77" s="12" t="n">
         <v>8</v>
       </c>
       <c r="M77" s="12" t="n">
-        <v>83</v>
+        <v>36</v>
       </c>
       <c r="N77" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>36981</t>
+          <t>07084</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>VIA COLLATINA 427, ANG. VIA PETITTI</t>
+          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -4795,31 +4795,31 @@
         </is>
       </c>
       <c r="F78" s="12" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G78" s="12" t="n">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="H78" s="12" t="n">
-        <v>2</v>
+        <v>25</v>
       </c>
       <c r="I78" s="12" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="J78" s="12" t="n">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="K78" s="12" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L78" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="M78" s="12" t="n">
-        <v>195</v>
+        <v>125</v>
       </c>
       <c r="N78" s="12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
@@ -4830,17 +4830,17 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>06761</t>
+          <t>16949</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>MACERATA</t>
+          <t>ROMA</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
+          <t>VIA DI PONTE GALERIA  SNC - VIA DI PONTE GALERIA SNC</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -4850,56 +4850,56 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>MORETTI MARCO MARIA</t>
+          <t>LESTI LEONARDO</t>
         </is>
       </c>
       <c r="F79" s="12" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="G79" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="H79" s="12" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="I79" s="12" t="n">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="J79" s="12" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="K79" s="12" t="n">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="L79" s="12" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="M79" s="12" t="n">
-        <v>63</v>
+        <v>83</v>
       </c>
       <c r="N79" s="12" t="n">
-        <v>36</v>
+        <v>7</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24526</t>
+          <t>06761</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>S.MARTINO IN CAMPO</t>
+          <t>MACERATA</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
+          <t>S.S.77 KM 84 LOC. SFORZACOSTA</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -4909,56 +4909,56 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>TEMPESTA ALESSIO</t>
+          <t>MORETTI MARCO MARIA</t>
         </is>
       </c>
       <c r="F80" s="12" t="n">
-        <v>28</v>
+        <v>33</v>
       </c>
       <c r="G80" s="12" t="n">
-        <v>66</v>
+        <v>2</v>
       </c>
       <c r="H80" s="12" t="n">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="I80" s="12" t="n">
-        <v>26</v>
+        <v>2</v>
       </c>
       <c r="J80" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="K80" s="12" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L80" s="12" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="M80" s="12" t="n">
-        <v>69</v>
+        <v>63</v>
       </c>
       <c r="N80" s="12" t="n">
-        <v>5</v>
+        <v>36</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Bene</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>07084</t>
+          <t>24526</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>ROMA</t>
+          <t>S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>VIA TUSCOLANA ANG CAVE, 0432</t>
+          <t>KM62+110 E 45, S.MARTINO IN CAMPO</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -4968,35 +4968,35 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>CASINI GIUSEPPE NICCOLO'</t>
+          <t>TEMPESTA ALESSIO</t>
         </is>
       </c>
       <c r="F81" s="12" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G81" s="12" t="n">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="H81" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="I81" s="12" t="n">
         <v>26</v>
       </c>
-      <c r="I81" s="12" t="n">
-        <v>94</v>
-      </c>
       <c r="J81" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="K81" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="L81" s="12" t="n">
         <v>11</v>
       </c>
-      <c r="L81" s="12" t="n">
-        <v>0</v>
-      </c>
       <c r="M81" s="12" t="n">
-        <v>127</v>
+        <v>68</v>
       </c>
       <c r="N81" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
@@ -5031,10 +5031,10 @@
         </is>
       </c>
       <c r="F82" s="12" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G82" s="12" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="H82" s="12" t="n">
         <v>3</v>
@@ -5043,7 +5043,7 @@
         <v>6</v>
       </c>
       <c r="J82" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K82" s="12" t="n">
         <v>0</v>
@@ -5059,24 +5059,24 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>05798</t>
+          <t>27195</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>MONTE ROBERTO</t>
+          <t>GALLICANO NEL LAZIO</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
+          <t>PRENESTINA EST</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5086,56 +5086,56 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>STROLOGO FRANCESCO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F83" s="12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G83" s="12" t="n">
-        <v>38</v>
+        <v>4</v>
       </c>
       <c r="H83" s="12" t="n">
-        <v>37</v>
+        <v>2</v>
       </c>
       <c r="I83" s="12" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="J83" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="K83" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="L83" s="12" t="n">
         <v>1</v>
       </c>
-      <c r="L83" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="M83" s="12" t="n">
-        <v>31</v>
+        <v>48</v>
       </c>
       <c r="N83" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>27195</t>
+          <t>05798</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>GALLICANO NEL LAZIO</t>
+          <t>MONTE ROBERTO</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>PRENESTINA EST</t>
+          <t>SS 76 KM 51+485 VARIANTE SNC KM51</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5145,56 +5145,56 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>STROLOGO FRANCESCO</t>
         </is>
       </c>
       <c r="F84" s="12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G84" s="12" t="n">
-        <v>4</v>
+        <v>38</v>
       </c>
       <c r="H84" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="I84" s="12" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="J84" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="K84" s="12" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L84" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="M84" s="12" t="n">
-        <v>50</v>
+        <v>31</v>
       </c>
       <c r="N84" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>59309</t>
+          <t>07429</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>MORLUPO</t>
+          <t>FABRO</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>VIA FLAMINIA KM. 29,700 SNC</t>
+          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5204,56 +5204,56 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>DELLA ROSA FABIO</t>
+          <t>LEUCCI ANTONIO</t>
         </is>
       </c>
       <c r="F85" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G85" s="12" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="H85" s="12" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I85" s="12" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="J85" s="12" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="K85" s="12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L85" s="12" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="M85" s="12" t="n">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="N85" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>07429</t>
+          <t>59309</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>FABRO</t>
+          <t>MORLUPO</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>AUT. A1 DIR.MILANO/ROMA KM 428</t>
+          <t>VIA FLAMINIA KM. 29,700 SNC</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5263,39 +5263,39 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>LEUCCI ANTONIO</t>
+          <t>DELLA ROSA FABIO</t>
         </is>
       </c>
       <c r="F86" s="12" t="n">
         <v>21</v>
       </c>
       <c r="G86" s="12" t="n">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="H86" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="I86" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="J86" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K86" s="12" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L86" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="M86" s="12" t="n">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="N86" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>Male</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5338,7 @@
         <v>0</v>
       </c>
       <c r="J87" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="K87" s="12" t="n">
         <v>6</v>
@@ -5388,7 +5388,7 @@
         <v>19</v>
       </c>
       <c r="G88" s="12" t="n">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="H88" s="12" t="n">
         <v>1</v>
@@ -5397,7 +5397,7 @@
         <v>1</v>
       </c>
       <c r="J88" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K88" s="12" t="n">
         <v>4</v>
@@ -5406,14 +5406,14 @@
         <v>6</v>
       </c>
       <c r="M88" s="12" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="N88" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>Da seguire</t>
+          <t>Male</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5456,7 @@
         <v>0</v>
       </c>
       <c r="J89" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="K89" s="12" t="n">
         <v>3</v>
@@ -5503,7 +5503,7 @@
         </is>
       </c>
       <c r="F90" s="12" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="G90" s="12" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
         <v>2</v>
       </c>
       <c r="J90" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K90" s="12" t="n">
         <v>3</v>
@@ -5524,14 +5524,14 @@
         <v>3</v>
       </c>
       <c r="M90" s="12" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="N90" s="12" t="n">
         <v>0</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
         </is>
       </c>
       <c r="F91" s="12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="G91" s="12" t="n">
         <v>14</v>
@@ -5574,7 +5574,7 @@
         <v>2</v>
       </c>
       <c r="J91" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K91" s="12" t="n">
         <v>2</v>
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
         <v>0</v>
       </c>
       <c r="J92" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="K92" s="12" t="n">
         <v>3</v>
@@ -5649,7 +5649,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5680,7 +5680,7 @@
         </is>
       </c>
       <c r="F93" s="12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G93" s="12" t="n">
         <v>0</v>
@@ -5692,7 +5692,7 @@
         <v>0</v>
       </c>
       <c r="J93" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K93" s="12" t="n">
         <v>2</v>
@@ -5701,14 +5701,14 @@
         <v>1</v>
       </c>
       <c r="M93" s="12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="N93" s="12" t="n">
         <v>2</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5751,7 +5751,7 @@
         <v>0</v>
       </c>
       <c r="J94" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K94" s="12" t="n">
         <v>1</v>
@@ -5767,7 +5767,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5804,13 +5804,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I95" s="12" t="n">
         <v>0</v>
       </c>
       <c r="J95" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K95" s="12" t="n">
         <v>1</v>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>Bene</t>
+          <t>Da seguire</t>
         </is>
       </c>
     </row>
@@ -5869,7 +5869,7 @@
         <v>3</v>
       </c>
       <c r="J96" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K96" s="12" t="n">
         <v>0</v>
